--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-24.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>64.02000000000001</t>
+          <t>64.58</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>65.04</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>126.32</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.05</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2341.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1845.8</t>
+          <t>1312.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1782.7</t>
+          <t>1731.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1386.18</t>
+          <t>1324.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-419</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>77.15000894233751</t>
+          <t>57.98550063978215</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>94.42627548221026</t>
+          <t>-47.41929502427229</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2341</v>
+        <v>69</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>-31.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.02000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>64.11</t>
+          <t>64.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.43</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>65.04</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>55.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.75</t>
+          <t>-105.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1135.0</t>
+          <t>2341.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2358.0</t>
+          <t>1845.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1797.1</t>
+          <t>1782.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1366.6</t>
+          <t>1386.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>74.00886957145156</t>
+          <t>77.15000894233751</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>50.26186636710622</t>
+          <t>94.42627548221026</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1135</v>
+        <v>2341</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-32.81</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,27 +1891,27 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1941,22 +1941,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>65.16</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.61</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>766.0</t>
+          <t>1135.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2282.4</t>
+          <t>2358.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1723.1</t>
+          <t>1797.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1383.56</t>
+          <t>1366.6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>78.32650651769616</t>
+          <t>74.00886957145156</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>114.589072403847</t>
+          <t>50.26186636710622</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>766</v>
+        <v>1135</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-33.85</t>
+          <t>-32.81</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,67 +2327,67 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>63.25999999999999</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>64.06</t>
+          <t>64.11</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-42.30</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.54</t>
+          <t>-105.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2250.0</t>
+          <t>766.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2218.4</t>
+          <t>2282.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1734.0</t>
+          <t>1723.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1409.4</t>
+          <t>1383.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>71.73331272021419</t>
+          <t>78.32650651769616</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>241.9283284419107</t>
+          <t>114.589072403847</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2250</v>
+        <v>766</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-25.21</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>63.5</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.38</t>
+          <t>-33.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,47 +2763,47 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>63.22000000000001</t>
+          <t>63.25999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.06</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2813,22 +2813,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-42.30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.95</t>
+          <t>-105.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2737.0</t>
+          <t>2250.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2150.8</t>
+          <t>2218.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1645.7</t>
+          <t>1734.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1399.08</t>
+          <t>1409.4</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>484</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>40.78876440717845</t>
+          <t>71.73331272021419</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>256.2012539090763</t>
+          <t>241.9283284419107</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>2737</v>
+        <v>2250</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-25.80</t>
+          <t>-25.21</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-34.17</t>
+          <t>-34.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>63.32000000000001</t>
+          <t>63.22000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>64.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-70.76</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.17</t>
+          <t>-104.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4902.0</t>
+          <t>2737.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1719.6</t>
+          <t>2150.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1444.3</t>
+          <t>1645.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1359.62</t>
+          <t>1399.08</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>505</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1.622857225015206</t>
+          <t>40.78876440717845</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>215.2625312225603</t>
+          <t>256.2012539090763</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>4902</v>
+        <v>2737</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-25.56</t>
+          <t>-25.80</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>-34.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3660,22 +3660,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>63.32000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>65.68</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-81.32</t>
+          <t>-70.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.43</t>
+          <t>-104.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>4902.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1236.2</t>
+          <t>1719.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1032.5</t>
+          <t>1444.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1312.6</t>
+          <t>1359.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>275</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-37.22071986544753</t>
+          <t>1.622857225015206</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-82.87359158755407</t>
+          <t>215.2625312225603</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>757</v>
+        <v>4902</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>63.84</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.43</t>
+          <t>64.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>65.68</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-90.63</t>
+          <t>-81.32</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-103.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1163.8</t>
+          <t>1236.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1022.0</t>
+          <t>1032.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1382.28</t>
+          <t>1312.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>203</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-28.92019773415543</t>
+          <t>-37.22071986544753</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-61.71542447387628</t>
+          <t>-82.87359158755407</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>446</v>
+        <v>757</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>63.3</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>64.18</t>
+          <t>63.84</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>65.82</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-81.89</t>
+          <t>-90.63</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.11</t>
+          <t>-102.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1912.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1249.6</t>
+          <t>1163.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1085.2</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1402.54</t>
+          <t>1382.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>141</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-22.95742923602436</t>
+          <t>-28.92019773415543</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>4.036079419730413</t>
+          <t>-61.71542447387628</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1912</v>
+        <v>446</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>63.3</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>63.3</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>63.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>62.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-33.85</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.18</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.18</t>
+          <t>64.16</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>64.47</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>66.12</t>
+          <t>65.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-81.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.68</t>
+          <t>-102.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>581.0</t>
+          <t>1912.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1140.6</t>
+          <t>1249.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1110.9</t>
+          <t>1085.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1385.86</t>
+          <t>1402.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>164</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-27.86533990070705</t>
+          <t>-22.95742923602436</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-59.24877499725039</t>
+          <t>4.036079419730413</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>581</v>
+        <v>1912</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-25.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>-33.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.15</t>
+          <t>34.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.78</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.25</t>
+          <t>64.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.56</t>
+          <t>64.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>66.27</t>
+          <t>66.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.30</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.59</t>
+          <t>-101.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7929.008608321377</t>
+          <t>7917.797277936963</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2485.0</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1169.0</t>
+          <t>1140.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1347.3</t>
+          <t>1110.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1410.76</t>
+          <t>1385.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-178</t>
+          <t>29</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-22.15926079224463</t>
+          <t>-27.86533990070705</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-4.932539343035387</t>
+          <t>-59.24877499725039</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2485</v>
+        <v>581</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,157 +5810,157 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>91.9</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>99.37</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>355200475.5730659</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>76417304.6</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>319430807.84</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>48395514</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>92.31</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>99.99</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>355605937.846485</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>95573934.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>336619552.5</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>68436405</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>100.61</t>
+          <t>99.99</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>111293530.2</t>
+          <t>95573934.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>366752945.54</t>
+          <t>336619552.5</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>102624938</v>
+        <v>68436405</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>101.18</t>
+          <t>100.61</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>124126000.4</t>
+          <t>111293530.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>399636300.16</t>
+          <t>366752945.54</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>62765638</v>
+        <v>102624938</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>101.62</t>
+          <t>101.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>138609938.8</t>
+          <t>124126000.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>443270959.36</t>
+          <t>399636300.16</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>99864028</v>
+        <v>62765638</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>101.62</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>146673374.0</t>
+          <t>138609938.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>454484548.46</t>
+          <t>443270959.36</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>144178661</v>
+        <v>99864028</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>95.16</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>146439342.4</t>
+          <t>146673374.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>461884050.18</t>
+          <t>454484548.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>147034386</v>
+        <v>144178661</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>102.52</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>135964184.0</t>
+          <t>146439342.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>481289771.06</t>
+          <t>461884050.18</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-29607378.16346818</t>
+          <t>-28080257.81287342</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>166787289</v>
+        <v>147034386</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.99</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.32</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.52</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>126336486.8</t>
+          <t>135964184.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>501408648.9</t>
+          <t>481289771.06</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-32847954.76562259</t>
+          <t>-29607378.16346818</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>135185330</v>
+        <v>166787289</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1479.927</t>
+          <t>1433.749</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-127.83</t>
+          <t>-128.18</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>140181204.0</t>
+          <t>135185330.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>137059889.8</t>
+          <t>126336486.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>221562336.5</t>
+          <t>216135889.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>538168556.64</t>
+          <t>501408648.9</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-84502446</t>
+          <t>-89799402</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28065906.14552652</t>
+          <t>-28801605.93323361</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-32918284.49135661</t>
+          <t>-32847954.76562259</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>140181204</v>
+        <v>135185330</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1504.164</t>
+          <t>1479.927</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.91</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-126.99</t>
+          <t>-127.83</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>143008503.0</t>
+          <t>140181204.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>152789337.4</t>
+          <t>137059889.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>233463581.9</t>
+          <t>221562336.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>553861277.88</t>
+          <t>538168556.64</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-80674244</t>
+          <t>-84502446</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-27183655.53719378</t>
+          <t>-28065906.14552652</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-32378374.72485676</t>
+          <t>-32918284.49135661</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>143008503</v>
+        <v>140181204</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1012.26</t>
+          <t>1504.164</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-34.56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>94.24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>103.01</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-22.08</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-125.99</t>
+          <t>-126.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>94658594.0</t>
+          <t>143008503.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>222851108.2</t>
+          <t>152789337.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>272945780.2</t>
+          <t>233463581.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>561353465.26</t>
+          <t>553861277.88</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-50094672</t>
+          <t>-80674244</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-26239161.13943687</t>
+          <t>-27183655.53719378</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-30753629.42539778</t>
+          <t>-32378374.72485676</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>94658594</v>
+        <v>143008503</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>190.975</t>
+          <t>148.395</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-17.30</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10585,17 +10585,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10606,12 +10606,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10621,62 +10621,62 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.17</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-66.82</t>
+          <t>-63.35</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-108.67</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10696,46 +10696,46 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>2688443.0</t>
+          <t>2077109.0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>1524941.6</t>
+          <t>1759442.8</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>1839009.9</t>
+          <t>1890917.2</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>4178193.24</t>
+          <t>4159009.66</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-314068</t>
+          <t>-131474</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-275743.0887770982</t>
+          <t>-255459.7471046391</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-180495.3613280805</t>
+          <t>-143901.3679061139</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>2688443</v>
+        <v>2077109</v>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>111.87</t>
+          <t>190.975</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10936,17 +10936,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-33.43</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-17.30</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -11021,17 +11021,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -11042,12 +11042,12 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -11062,57 +11062,57 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-70.44</t>
+          <t>-66.82</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-108.67</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -11132,46 +11132,46 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1603545.0</t>
+          <t>2688443.0</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>1278371.2</t>
+          <t>1524941.6</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>1920357.8</t>
+          <t>1839009.9</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>4166690.22</t>
+          <t>4178193.24</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-641986</t>
+          <t>-314068</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-293060.8574041924</t>
+          <t>-275743.0887770982</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-291826.3033120302</t>
+          <t>-180495.3613280805</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1603545</v>
+        <v>2688443</v>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11300,22 +11300,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.771</t>
+          <t>111.87</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11372,17 +11372,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-37.46</t>
+          <t>-33.43</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11457,17 +11457,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11478,77 +11478,77 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-66.66</t>
+          <t>-70.44</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-105.95</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11568,46 +11568,46 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>819720.0</t>
+          <t>1603545.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>1201241.0</t>
+          <t>1278371.2</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>1920681.7</t>
+          <t>1920357.8</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>4177484.36</t>
+          <t>4166690.22</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-719440</t>
+          <t>-641986</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-293285.3217845855</t>
+          <t>-293060.8574041924</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-324209.0667422423</t>
+          <t>-291826.3033120302</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>819720</v>
+        <v>1603545</v>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11711,12 +11711,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11736,22 +11736,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>110.996</t>
+          <t>55.771</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11798,7 +11798,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11808,17 +11808,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>-37.46</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-14.66</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11893,17 +11893,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11914,77 +11914,77 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>15.17</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-73.36</t>
+          <t>-66.66</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-104.96</t>
+          <t>-105.95</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -12004,46 +12004,46 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>1608397.0</t>
+          <t>819720.0</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2163327.6</t>
+          <t>1201241.0</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2017693.3</t>
+          <t>1920681.7</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>4186216.38</t>
+          <t>4177484.36</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>-719440</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-287662.8227013752</t>
+          <t>-293285.3217845855</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-274910.0121160368</t>
+          <t>-324209.0667422423</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>1608397</v>
+        <v>819720</v>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
@@ -12112,17 +12112,17 @@
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12177,17 +12177,17 @@
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>61.609</t>
+          <t>110.996</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12244,17 +12244,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-12.95</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12329,17 +12329,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12350,77 +12350,77 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-73.36</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.96</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12440,46 +12440,46 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>904603.0</t>
+          <t>1608397.0</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>2022391.6</t>
+          <t>2163327.6</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>2323211.4</t>
+          <t>2017693.3</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>4187498.26</t>
+          <t>4186216.38</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-300819</t>
+          <t>145634</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-289981.5155350731</t>
+          <t>-287662.8227013752</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-279165.6836458847</t>
+          <t>-274910.0121160368</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>904603</v>
+        <v>1608397</v>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
@@ -12543,22 +12543,22 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12613,17 +12613,17 @@
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>96.998</t>
+          <t>61.609</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12680,17 +12680,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-12.95</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12765,17 +12765,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12786,77 +12786,77 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-39.38</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-103.57</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12876,46 +12876,46 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>1455591.0</t>
+          <t>904603.0</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>2153078.2</t>
+          <t>2022391.6</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>2633849.5</t>
+          <t>2323211.4</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>4198766.18</t>
+          <t>4187498.26</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-480771</t>
+          <t>-300819</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-291948.0304240164</t>
+          <t>-289981.5155350731</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-199868.5114154578</t>
+          <t>-279165.6836458847</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>1455591</v>
+        <v>904603</v>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
@@ -12979,22 +12979,22 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -13044,22 +13044,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79.439</t>
+          <t>96.998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -13116,17 +13116,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13201,17 +13201,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13222,52 +13222,52 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -13277,24 +13277,24 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-39.38</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-103.21</t>
+          <t>-103.57</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13312,46 +13312,46 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>1217894.0</t>
+          <t>1455591.0</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>2562344.4</t>
+          <t>2153078.2</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2660547.0</t>
+          <t>2633849.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>4192640.7</t>
+          <t>4198766.18</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-98202</t>
+          <t>-480771</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-308689.7611528453</t>
+          <t>-291948.0304240164</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-138483.1042500096</t>
+          <t>-199868.5114154578</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>1217894</v>
+        <v>1455591</v>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13480,22 +13480,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>364.024</t>
+          <t>79.439</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13552,17 +13552,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.07</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13637,17 +13637,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13658,52 +13658,52 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-49.87</t>
+          <t>-20.58</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-103.05</t>
+          <t>-103.21</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13748,46 +13748,46 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>5630153.0</t>
+          <t>1217894.0</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>2640122.4</t>
+          <t>2562344.4</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>2652719.7</t>
+          <t>2660547.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>4214329.42</t>
+          <t>4192640.7</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-12597</t>
+          <t>-98202</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-339636.42604427</t>
+          <t>-308689.7611528453</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-20376.3045761548</t>
+          <t>-138483.1042500096</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>5630153</v>
+        <v>1217894</v>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
@@ -13851,22 +13851,22 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13916,22 +13916,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>60.824</t>
+          <t>364.024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13988,17 +13988,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-11.51</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -14073,17 +14073,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -14094,57 +14094,57 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>15.31</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-142.09</t>
+          <t>-49.87</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-102.67</t>
+          <t>-103.05</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14184,46 +14184,46 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>903717.0</t>
+          <t>5630153.0</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>1872059.0</t>
+          <t>2640122.4</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>2265582.9</t>
+          <t>2652719.7</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>4151982.3</t>
+          <t>4214329.42</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-393523</t>
+          <t>-12597</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-397683.7208566546</t>
+          <t>-339636.42604427</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-323666.6155929281</t>
+          <t>-20376.3045761548</t>
         </is>
       </c>
       <c r="BD32" t="n">
-        <v>903717</v>
+        <v>5630153</v>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
@@ -14287,22 +14287,22 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14352,22 +14352,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
+          <t>14.95</t>
+        </is>
+      </c>
+      <c r="CE32" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="CF32" t="inlineStr">
+        <is>
           <t>14.8</t>
         </is>
       </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>105.654</t>
+          <t>60.824</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14424,17 +14424,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14530,32 +14530,32 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -14565,42 +14565,42 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>15.31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-238.86</t>
+          <t>-142.09</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-101.72</t>
+          <t>-102.67</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14620,46 +14620,46 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>1558036.0</t>
+          <t>903717.0</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>2624031.2</t>
+          <t>1872059.0</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>2434384.3</t>
+          <t>2265582.9</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>4178511.28</t>
+          <t>4151982.3</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>189646</t>
+          <t>-393523</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-411141.3763591503</t>
+          <t>-397683.7208566546</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-238975.1093457136</t>
+          <t>-323666.6155929281</t>
         </is>
       </c>
       <c r="BD33" t="n">
-        <v>1558036</v>
+        <v>903717</v>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14733,12 +14733,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14793,17 +14793,17 @@
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14835,12 +14835,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>234.752</t>
+          <t>105.654</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14860,17 +14860,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14945,17 +14945,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14966,12 +14966,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14981,62 +14981,62 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-458.21</t>
+          <t>-238.86</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-100.69</t>
+          <t>-101.72</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -15056,46 +15056,46 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>26730326.92467719</t>
+          <t>26696495.02865329</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>3501922.0</t>
+          <t>1558036.0</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>3114620.8</t>
+          <t>2624031.2</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>2578828.8</t>
+          <t>2434384.3</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>4176793.06</t>
+          <t>4178511.28</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>535792</t>
+          <t>189646</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-442444.3339979569</t>
+          <t>-411141.3763591503</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-179558.0250873468</t>
+          <t>-238975.1093457136</t>
         </is>
       </c>
       <c r="BD34" t="n">
-        <v>3501922</v>
+        <v>1558036</v>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -15224,22 +15224,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CG34" t="inlineStr">
+        <is>
           <t>14.75</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>14.8</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>65.28</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>64.45</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>64.45999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>890.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1040.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1040.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1629.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1306.26</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1306.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-83.95071200320331</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>890</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>890.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>64.58</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>64.34</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>64.45999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1312.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1312.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1731.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1324.24</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1324.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-47.41929502427229</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>69</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>64.02000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>64.23</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>64.47</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>64.47</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2341.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1845.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1845.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1782.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1386.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1386.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>94.42627548221026</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2341</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2341.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>63.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>64.11</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>64.43</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>64.43000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1135.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2358.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2358</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1797.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1366.6</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1366.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>50.26186636710622</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1135</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1135.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>63.5</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>64.11</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>64.43</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>64.11</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>64.43000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>766.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2282.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2282.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1723.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1383.56</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1383.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>114.589072403847</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>766</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>766.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>63.25999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>64.06</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>64.41</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>64.06</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>64.41</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2250.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1734.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1409.4</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1409.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>241.9283284419107</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2250</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2250.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>63.22000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>64.07</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>64.41</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>64.41</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2737.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2150.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>2150.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1645.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1399.08</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1399.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>256.2012539090763</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2737</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2737.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>63.32000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4902.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1719.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1719.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1444.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1359.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1359.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>215.2625312225603</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4902</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4902.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>63.34</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>64.12</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>757.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1236.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1236.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1032.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1312.6</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1312.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-82.87359158755407</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>757</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>757.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>63.84</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>64.16</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>64.43</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>64.43000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1163.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1163.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1022.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1382.28</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1382.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-61.71542447387628</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>446</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>64.18</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>64.16</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>64.47</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>64.47</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1912.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1249.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1249.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1085.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1402.54</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1402.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>4.036079419730413</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1912</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1912.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5667,11 +5601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>2476</t>
@@ -5853,41 +5783,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5908,20 +5834,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5860,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6029,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6213,11 @@
           <t>14.19</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15.15</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6264,16 @@
           <t>1207614.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1679286.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1679286.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1921306.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>4104519.9</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>4104519.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6290,10 @@
           <t>-179900.1633130845</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1207614</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1207614.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6459,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6643,11 @@
           <t>14.23</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>14.93</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15.17</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6694,16 @@
           <t>2077109.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1759442.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1759442.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1890917.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>4159009.66</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>4159009.66</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6720,10 @@
           <t>-143901.3679061139</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2077109</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2077109.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6889,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7073,11 @@
           <t>14.42</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15.2</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7124,16 @@
           <t>2688443.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1524941.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1524941.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1839009.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>4178193.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>4178193.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7150,10 @@
           <t>-180495.3613280805</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2688443</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2688443.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7319,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7503,11 @@
           <t>14.58</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7554,16 @@
           <t>1603545.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1278371.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1278371.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1920357.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>4166690.22</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>4166690.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7580,10 @@
           <t>-291826.3033120302</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1603545</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1603545.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7933,11 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>15.24</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7984,16 @@
           <t>819720.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1201241.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1201241</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1920681.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>4177484.36</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>4177484.36</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8010,10 @@
           <t>-324209.0667422423</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>819720</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>819720.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8179,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8363,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>15.26</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15.26</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8414,16 @@
           <t>1608397.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2163327.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2163327.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2017693.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>4186216.38</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>4186216.38</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8440,10 @@
           <t>-274910.0121160368</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1608397</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1608397.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8793,11 @@
           <t>15.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8844,16 @@
           <t>904603.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2022391.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2022391.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2323211.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>4187498.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>4187498.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8870,10 @@
           <t>-279165.6836458847</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>904603</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>904603.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9039,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9223,11 @@
           <t>15.08</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.3</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9274,16 @@
           <t>1455591.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2153078.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2153078.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2633849.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>4198766.18</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>4198766.18</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9300,10 @@
           <t>-199868.5114154578</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1455591</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1455591.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9469,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9653,11 @@
           <t>15.06</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>15.34</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.3</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9704,16 @@
           <t>1217894.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2562344.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2562344.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2660547.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>4192640.7</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>4192640.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9730,10 @@
           <t>-138483.1042500096</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1217894</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1217894.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10083,11 @@
           <t>15.04</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>15.36</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.3</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10134,16 @@
           <t>5630153.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2640122.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2640122.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2652719.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>4214329.42</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>4214329.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10160,10 @@
           <t>-20376.3045761548</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>5630153</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>5630153.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10329,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10513,11 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>15.31</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>15.31</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10564,16 @@
           <t>903717.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1872059.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1872059</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2265582.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>4151982.3</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>4151982.3</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>-323666.6155929281</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>903717</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>903717.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.02</t>
+          <t>-35.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-30.21</t>
+          <t>-30.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,22 +993,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>65.78</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>64.55</v>
+        <v>64.63</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.45999999999999</v>
+        <v>64.47</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3051.68</t>
+          <t>354.67</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.71</t>
+          <t>-97.42</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1001.2</v>
+        <v>1117</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1641.8</t>
+          <t>1737.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1275</v>
+        <v>1299.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-640</t>
+          <t>-620</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>10.38022233754688</t>
+          <t>-2.83503795219656</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-131.3489360883748</t>
+          <t>-75.51896954578547</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>66.9</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-36.16</t>
+          <t>-39.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.78</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>64.45</v>
+        <v>64.55</v>
       </c>
       <c r="AN3" t="n">
         <v>64.45999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>65.09</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>391.30</t>
+          <t>3051.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.94</t>
+          <t>-99.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1040.2</v>
+        <v>1001.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1629.3</t>
+          <t>1641.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1306.26</v>
+        <v>1275</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-589</t>
+          <t>-640</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>36.149160233169</t>
+          <t>10.38022233754688</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-83.95071200320331</t>
+          <t>-131.3489360883748</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-36.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-31.46</t>
+          <t>-30.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>64.58</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>64.34</v>
+        <v>64.45</v>
       </c>
       <c r="AN4" t="n">
         <v>64.45999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>65.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>126.32</t>
+          <t>391.30</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1312.2</v>
+        <v>1040.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1731.5</t>
+          <t>1629.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1324.24</v>
+        <v>1306.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-419</t>
+          <t>-589</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>57.98550063978215</t>
+          <t>36.149160233169</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-47.41929502427229</t>
+          <t>-83.95071200320331</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-24.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>64.02000000000001</t>
+          <t>64.58</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>64.23</v>
+        <v>64.34</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.47</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>65.04</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>126.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.05</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2341.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1845.8</v>
+        <v>1312.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1782.7</t>
+          <t>1731.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1386.18</v>
+        <v>1324.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-419</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>77.15000894233751</t>
+          <t>57.98550063978215</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>94.42627548221026</t>
+          <t>-47.41929502427229</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2341.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>-31.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.02000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>64.11</v>
+        <v>64.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.43000000000001</v>
+        <v>64.47</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>65.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>55.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.75</t>
+          <t>-105.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1135.0</t>
+          <t>2341.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2358</v>
+        <v>1845.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1797.1</t>
+          <t>1782.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1366.6</v>
+        <v>1386.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>63</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>74.00886957145156</t>
+          <t>77.15000894233751</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>50.26186636710622</t>
+          <t>94.42627548221026</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1135.0</t>
+          <t>2341.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-32.81</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,27 +3169,27 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>65.16</t>
+          <t>65.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.61</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>766.0</t>
+          <t>1135.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2282.4</v>
+        <v>2358</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1723.1</t>
+          <t>1797.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1383.56</v>
+        <v>1366.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>560</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>78.32650651769616</t>
+          <t>74.00886957145156</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>114.589072403847</t>
+          <t>50.26186636710622</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>766.0</t>
+          <t>1135.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-33.85</t>
+          <t>-32.81</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,63 +3599,63 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>63.25999999999999</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>64.06</v>
+        <v>64.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.41</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>65.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-42.30</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.54</t>
+          <t>-105.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2250.0</t>
+          <t>766.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2218.4</v>
+        <v>2282.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1734.0</t>
+          <t>1723.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1409.4</v>
+        <v>1383.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>559</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>71.73331272021419</t>
+          <t>78.32650651769616</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>241.9283284419107</t>
+          <t>114.589072403847</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2250.0</t>
+          <t>766.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>63.5</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-34.38</t>
+          <t>-33.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>63.22000000000001</t>
+          <t>63.25999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>64.06999999999999</v>
+        <v>64.06</v>
       </c>
       <c r="AN9" t="n">
         <v>64.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-42.30</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.95</t>
+          <t>-105.54</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2737.0</t>
+          <t>2250.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2150.8</v>
+        <v>2218.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1645.7</t>
+          <t>1734.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1399.08</v>
+        <v>1409.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>484</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>40.78876440717845</t>
+          <t>71.73331272021419</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>256.2012539090763</t>
+          <t>241.9283284419107</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2737.0</t>
+          <t>2250.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-34.17</t>
+          <t>-34.38</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.26</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>63.32000000000001</t>
+          <t>63.22000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>64.09999999999999</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.42</v>
+        <v>64.41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-70.76</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.17</t>
+          <t>-104.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4902.0</t>
+          <t>2737.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1719.6</v>
+        <v>2150.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1444.3</t>
+          <t>1645.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1359.62</v>
+        <v>1399.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>505</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1.622857225015206</t>
+          <t>40.78876440717845</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>215.2625312225603</t>
+          <t>256.2012539090763</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4902.0</t>
+          <t>2737.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>-34.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>14.26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -4914,43 +4914,43 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>63.34</t>
+          <t>63.32000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>64.12</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AN11" t="n">
         <v>64.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>65.68</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-81.32</t>
+          <t>-70.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.43</t>
+          <t>-104.17</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>4902.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1236.2</v>
+        <v>1719.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1032.5</t>
+          <t>1444.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1312.6</v>
+        <v>1359.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>275</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-37.22071986544753</t>
+          <t>1.622857225015206</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-82.87359158755407</t>
+          <t>215.2625312225603</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>757.0</t>
+          <t>4902.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>63.84</t>
+          <t>63.34</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>64.16</v>
+        <v>64.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.43000000000001</v>
+        <v>64.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>65.82</t>
+          <t>65.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-90.63</t>
+          <t>-81.32</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-103.43</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7898.305714285714</t>
+          <t>7890.706134094151</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1163.8</v>
+        <v>1236.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1022.0</t>
+          <t>1032.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1382.28</v>
+        <v>1312.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>203</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-28.92019773415543</t>
+          <t>-37.22071986544753</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-61.71542447387628</t>
+          <t>-82.87359158755407</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>757.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>21.41</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>73.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>63.1</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>63.3</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN13" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,17 +6001,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN14" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,151 +7034,151 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>354018572.6854494</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>354437913.0685714</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>95573934</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>336619552.5</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>93.03</v>
+        <v>92.31</v>
       </c>
       <c r="AN17" t="n">
-        <v>100.61</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>111293530.2</v>
+        <v>95573934</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>366752945.54</v>
+        <v>336619552.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.75</v>
+        <v>93.03</v>
       </c>
       <c r="AN18" t="n">
-        <v>101.18</v>
+        <v>100.61</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>124126000.4</v>
+        <v>111293530.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>399636300.16</v>
+        <v>366752945.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>94.36</v>
+        <v>93.75</v>
       </c>
       <c r="AN19" t="n">
-        <v>101.62</v>
+        <v>101.18</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>138609938.8</v>
+        <v>124126000.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>443270959.36</v>
+        <v>399636300.16</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>95.16</v>
+        <v>94.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>101.96</v>
+        <v>101.62</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>146673374</v>
+        <v>138609938.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>454484548.46</v>
+        <v>443270959.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>95.84</v>
+        <v>95.16</v>
       </c>
       <c r="AN21" t="n">
-        <v>102.28</v>
+        <v>101.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>146439342.4</v>
+        <v>146673374</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>461884050.18</v>
+        <v>454484548.46</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>96.31999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="AN22" t="n">
-        <v>102.52</v>
+        <v>102.28</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>135964184</v>
+        <v>146439342.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>481289771.06</v>
+        <v>461884050.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-29607378.16346818</t>
+          <t>-28080257.81287342</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>96.8</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="AN23" t="n">
-        <v>102.75</v>
+        <v>102.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>126336486.8</v>
+        <v>135964184</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>501408648.9</v>
+        <v>481289771.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-32847954.76562259</t>
+          <t>-29607378.16346818</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28.288</t>
+          <t>107.92</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10474,73 +10474,73 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>14.83</v>
+        <v>14.78</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-32.90</t>
+          <t>-22.29</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-112.73</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10560,43 +10560,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>404781.0</t>
+          <t>1544643.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>1596298.4</v>
+        <v>1584518</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>1398769.7</t>
+          <t>1431444.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>4064230.28</v>
+        <v>4044797.48</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>197528</t>
+          <t>153073</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-246447.3642540991</t>
+          <t>-243216.1040813446</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-260814.2910151368</t>
+          <t>-225444.1731311949</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>404781.0</t>
+          <t>1544643.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>84.992</t>
+          <t>28.288</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10798,17 +10798,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10904,37 +10904,37 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -10944,33 +10944,33 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>14.87</v>
+        <v>14.83</v>
       </c>
       <c r="AN25" t="n">
-        <v>15.15</v>
+        <v>15.14</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-32.90</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-111.68</t>
+          <t>-112.73</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10990,43 +10990,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1207614.0</t>
+          <t>404781.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>1679286.2</v>
+        <v>1596298.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>1921306.9</t>
+          <t>1398769.7</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>4104519.9</v>
+        <v>4064230.28</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-242020</t>
+          <t>197528</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-243835.1957520922</t>
+          <t>-246447.3642540991</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-179900.1633130845</t>
+          <t>-260814.2910151368</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>1207614.0</t>
+          <t>404781.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -11156,22 +11156,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
           <t>14.3</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="CG25" t="inlineStr">
-        <is>
-          <t>14.2</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>148.395</t>
+          <t>84.992</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11228,17 +11228,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-18.48</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11313,17 +11313,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11334,73 +11334,73 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-4.70</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>14.93</v>
+        <v>14.87</v>
       </c>
       <c r="AN26" t="n">
-        <v>15.17</v>
+        <v>15.15</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-63.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-111.68</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11420,43 +11420,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>2077109.0</t>
+          <t>1207614.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>1759442.8</v>
+        <v>1679286.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>1890917.2</t>
+          <t>1921306.9</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>4159009.66</v>
+        <v>4104519.9</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-131474</t>
+          <t>-242020</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-255459.7471046391</t>
+          <t>-243835.1957520922</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-143901.3679061139</t>
+          <t>-179900.1633130845</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>2077109.0</t>
+          <t>1207614.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11521,17 +11521,17 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11586,22 +11586,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="CE26" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="CF26" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="CG26" t="inlineStr">
+        <is>
           <t>14.2</t>
-        </is>
-      </c>
-      <c r="CE26" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="CF26" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="CG26" t="inlineStr">
-        <is>
-          <t>13.9</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>190.975</t>
+          <t>148.395</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11658,17 +11658,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-17.30</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11743,17 +11743,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11764,12 +11764,12 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -11779,58 +11779,58 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>15.02</v>
+        <v>14.93</v>
       </c>
       <c r="AN27" t="n">
-        <v>15.2</v>
+        <v>15.17</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-66.82</t>
+          <t>-63.35</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-108.67</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11850,43 +11850,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>2688443.0</t>
+          <t>2077109.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>1524941.6</v>
+        <v>1759442.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1839009.9</t>
+          <t>1890917.2</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>4178193.24</v>
+        <v>4159009.66</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-314068</t>
+          <t>-131474</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-275743.0887770982</t>
+          <t>-255459.7471046391</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-180495.3613280805</t>
+          <t>-143901.3679061139</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>2688443.0</t>
+          <t>2077109.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -12016,12 +12016,12 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>111.87</t>
+          <t>190.975</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12088,17 +12088,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-33.43</t>
+          <t>-17.08</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-17.30</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12194,12 +12194,12 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -12214,53 +12214,53 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>15.1</v>
+        <v>15.02</v>
       </c>
       <c r="AN28" t="n">
-        <v>15.22</v>
+        <v>15.2</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>15.34</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-70.44</t>
+          <t>-66.82</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-108.67</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12280,43 +12280,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>1603545.0</t>
+          <t>2688443.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>1278371.2</v>
+        <v>1524941.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>1920357.8</t>
+          <t>1839009.9</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>4166690.22</v>
+        <v>4178193.24</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-641986</t>
+          <t>-314068</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-293060.8574041924</t>
+          <t>-275743.0887770982</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-291826.3033120302</t>
+          <t>-180495.3613280805</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>1603545.0</t>
+          <t>2688443.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12446,22 +12446,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.771</t>
+          <t>111.87</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12518,17 +12518,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-37.46</t>
+          <t>-33.43</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12603,17 +12603,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12624,73 +12624,73 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>8.99</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>15.17</v>
+        <v>15.1</v>
       </c>
       <c r="AN29" t="n">
-        <v>15.24</v>
+        <v>15.22</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-66.66</t>
+          <t>-70.44</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-105.95</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12710,43 +12710,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>819720.0</t>
+          <t>1603545.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>1201241</v>
+        <v>1278371.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>1920681.7</t>
+          <t>1920357.8</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>4177484.36</v>
+        <v>4166690.22</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-719440</t>
+          <t>-641986</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-293285.3217845855</t>
+          <t>-293060.8574041924</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-324209.0667422423</t>
+          <t>-291826.3033120302</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>819720.0</t>
+          <t>1603545.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12816,12 +12816,12 @@
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12876,22 +12876,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>110.996</t>
+          <t>55.771</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12948,17 +12948,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>-37.46</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-14.66</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13033,17 +13033,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13054,73 +13054,73 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.99</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>15.22</v>
+        <v>15.17</v>
       </c>
       <c r="AN30" t="n">
-        <v>15.26</v>
+        <v>15.24</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-73.36</t>
+          <t>-66.66</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-104.96</t>
+          <t>-105.95</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13140,43 +13140,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>1608397.0</t>
+          <t>819720.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>2163327.6</v>
+        <v>1201241</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2017693.3</t>
+          <t>1920681.7</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>4186216.38</v>
+        <v>4177484.36</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>-719440</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-287662.8227013752</t>
+          <t>-293285.3217845855</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-274910.0121160368</t>
+          <t>-324209.0667422423</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>1608397.0</t>
+          <t>819720.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13311,17 +13311,17 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>61.609</t>
+          <t>110.996</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13378,17 +13378,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-12.95</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13463,17 +13463,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13484,73 +13484,73 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>15.27</v>
+        <v>15.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-47.71</t>
+          <t>-73.36</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.96</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13570,43 +13570,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>904603.0</t>
+          <t>1608397.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>2022391.6</v>
+        <v>2163327.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>2323211.4</t>
+          <t>2017693.3</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>4187498.26</v>
+        <v>4186216.38</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-300819</t>
+          <t>145634</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-289981.5155350731</t>
+          <t>-287662.8227013752</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-279165.6836458847</t>
+          <t>-274910.0121160368</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>904603.0</t>
+          <t>1608397.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13671,17 +13671,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13741,17 +13741,17 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13773,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>96.998</t>
+          <t>61.609</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13808,17 +13808,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-12.95</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13914,73 +13914,73 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>15.3</v>
+        <v>15.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-39.38</t>
+          <t>-47.71</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-103.57</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14000,43 +14000,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>1455591.0</t>
+          <t>904603.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>2153078.2</v>
+        <v>2022391.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>2633849.5</t>
+          <t>2323211.4</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>4198766.18</v>
+        <v>4187498.26</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-480771</t>
+          <t>-300819</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-291948.0304240164</t>
+          <t>-289981.5155350731</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-199868.5114154578</t>
+          <t>-279165.6836458847</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>1455591.0</t>
+          <t>904603.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -14101,17 +14101,17 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -14166,22 +14166,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>79.439</t>
+          <t>96.998</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14238,17 +14238,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-18.25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14323,17 +14323,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14344,75 +14344,75 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>15.34</v>
+        <v>15.3</v>
       </c>
       <c r="AN33" t="n">
         <v>15.3</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-39.38</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
           <t>-0.07</t>
         </is>
       </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-103.21</t>
+          <t>-103.57</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14430,43 +14430,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>1217894.0</t>
+          <t>1455591.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>2562344.4</v>
+        <v>2153078.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>2660547.0</t>
+          <t>2633849.5</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>4192640.7</v>
+        <v>4198766.18</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-98202</t>
+          <t>-480771</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-308689.7611528453</t>
+          <t>-291948.0304240164</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-138483.1042500096</t>
+          <t>-199868.5114154578</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>1217894.0</t>
+          <t>1455591.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14596,22 +14596,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>364.024</t>
+          <t>79.439</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14753,17 +14753,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,51 +14774,51 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>15.36</v>
+        <v>15.34</v>
       </c>
       <c r="AN34" t="n">
         <v>15.3</v>
@@ -14830,12 +14830,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-49.87</t>
+          <t>-20.58</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-103.05</t>
+          <t>-103.21</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14860,43 +14860,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>26623674.46071429</t>
+          <t>26589000.12410842</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>5630153.0</t>
+          <t>1217894.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>2640122.4</v>
+        <v>2562344.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>2652719.7</t>
+          <t>2660547.0</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>4214329.42</v>
+        <v>4192640.7</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-12597</t>
+          <t>-98202</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-339636.42604427</t>
+          <t>-308689.7611528453</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-20376.3045761548</t>
+          <t>-138483.1042500096</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>5630153.0</t>
+          <t>1217894.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14961,7 +14961,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.05999999999999</t>
+          <t>66.14000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>65.04000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.62</v>
+        <v>64.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-90.28</t>
+          <t>-89.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1866.0</t>
+          <t>686.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1227</v>
+        <v>1095.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>998.9</t>
+          <t>1060.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1315.84</v>
+        <v>1315.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>35</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-51.23808981312222</t>
+          <t>-53.21749112573387</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25.84926422214335</t>
+          <t>-64.10419834509798</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1866.0</t>
+          <t>686.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>22.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>66.05999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>64.84</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.56</v>
+        <v>64.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-90.88</t>
+          <t>-90.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1042.0</t>
+          <t>1866.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>975.8</v>
+        <v>1227</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1046.4</t>
+          <t>998.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1294.06</v>
+        <v>1315.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-70</t>
+          <t>228</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-55.85423992057292</t>
+          <t>-51.23808981312222</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-96.70474175284585</t>
+          <t>-25.84926422214335</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1042.0</t>
+          <t>1866.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>53.57</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.15</v>
+        <v>-1.24</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>64.87</v>
+        <v>64.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.55</v>
+        <v>64.56</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-91.13</t>
+          <t>-90.88</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>1042.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1110.2</v>
+        <v>975.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1055.7</t>
+          <t>1046.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1289.1</v>
+        <v>1294.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-70</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-48.42687595106875</t>
+          <t>-55.85423992057292</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-106.1873974483904</t>
+          <t>-96.70474175284585</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>1042.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.68</t>
+          <t>53.57</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.71</v>
+        <v>-1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.64000000000001</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>64.84</v>
+        <v>64.87</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.53</v>
+        <v>64.55</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>65.03</t>
+          <t>64.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-91.91</t>
+          <t>-91.13</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1214.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1090.2</v>
+        <v>1110.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1065.2</t>
+          <t>1055.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1287.32</v>
+        <v>1289.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>54</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-37.92496295155574</t>
+          <t>-48.42687595106875</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-76.19164139029726</t>
+          <t>-106.1873974483904</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1214.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>65.8</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,61 +2707,61 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>97.36</t>
+          <t>84.68</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.21</v>
+        <v>-1.71</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.37</v>
+        <v>2.78</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.94000000000001</t>
+          <t>66.64000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>64.76000000000001</v>
+        <v>64.84</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.51000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>65.09</t>
+          <t>65.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>117.42</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-91.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1342.0</t>
+          <t>1214.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1025.4</v>
+        <v>1090.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1168.8</t>
+          <t>1065.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1294.18</v>
+        <v>1287.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-143</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-30.96738505360274</t>
+          <t>-37.92496295155574</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-88.79800268622512</t>
+          <t>-76.19164139029726</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1342.0</t>
+          <t>1214.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>65.5</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>66.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-41.08</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,22 +3103,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -3129,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>99.17</t>
+          <t>97.36</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.39</v>
+        <v>-0.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.13</v>
+        <v>3.37</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.74000000000001</t>
+          <t>66.94000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>64.72</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.48</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>65.13</t>
+          <t>65.09</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>185.56</t>
+          <t>117.42</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-95.19</t>
+          <t>-93.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1342.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>770.8</v>
+        <v>1025.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1308.3</t>
+          <t>1168.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1296.54</v>
+        <v>1294.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-537</t>
+          <t>-143</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-20.45272730221685</t>
+          <t>-30.96738505360274</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-117.3500187273285</t>
+          <t>-88.79800268622512</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>1342.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.71</t>
+          <t>-41.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3565,31 +3565,31 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.89</v>
+        <v>3.13</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.74000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>64.63</v>
+        <v>64.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.47</v>
+        <v>64.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,14 +3598,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>354.67</t>
+          <t>185.56</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.42</t>
+          <t>-95.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1714.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1117</v>
+        <v>770.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1737.5</t>
+          <t>1308.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1299.02</v>
+        <v>1296.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-620</t>
+          <t>-537</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2.83503795219656</t>
+          <t>-20.45272730221685</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-75.51896954578547</t>
+          <t>-117.3500187273285</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1714.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.02</t>
+          <t>-35.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,22 +3947,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -3973,28 +3973,28 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.17</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>0.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4004,30 +4004,30 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.78</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>64.55</v>
+        <v>64.63</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.45999999999999</v>
+        <v>64.47</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.13</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3051.68</t>
+          <t>354.67</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.71</t>
+          <t>-97.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1001.2</v>
+        <v>1117</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1641.8</t>
+          <t>1737.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1275</v>
+        <v>1299.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-640</t>
+          <t>-620</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>10.38022233754688</t>
+          <t>-2.83503795219656</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-131.3489360883748</t>
+          <t>-75.51896954578547</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>571.0</t>
+          <t>1714.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>66.9</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-36.16</t>
+          <t>-39.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4409,47 +4409,47 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.78</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>64.45</v>
+        <v>64.55</v>
       </c>
       <c r="AN10" t="n">
         <v>64.45999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>65.09</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>391.30</t>
+          <t>3051.68</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.94</t>
+          <t>-99.71</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1040.2</v>
+        <v>1001.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1629.3</t>
+          <t>1641.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1306.26</v>
+        <v>1275</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-589</t>
+          <t>-640</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.149160233169</t>
+          <t>10.38022233754688</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-83.95071200320331</t>
+          <t>-131.3489360883748</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>571.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.22</t>
+          <t>-36.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.89</v>
+        <v>2.63</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.38</v>
+        <v>1.3</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>64.58</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>64.34</v>
+        <v>64.45</v>
       </c>
       <c r="AN11" t="n">
         <v>64.45999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>65.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>126.32</t>
+          <t>391.30</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.17</v>
+        <v>-0.09</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.84</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1312.2</v>
+        <v>1040.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1731.5</t>
+          <t>1629.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1324.24</v>
+        <v>1306.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-419</t>
+          <t>-589</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>57.98550063978215</t>
+          <t>36.149160233169</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-47.41929502427229</t>
+          <t>-83.95071200320331</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-24.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5253,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>2.78</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.02000000000001</t>
+          <t>64.58</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>64.23</v>
+        <v>64.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.47</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>65.04</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>126.32</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.23</v>
+        <v>-0.17</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.05</t>
+          <t>-103.84</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7838.05162659123</t>
+          <t>7828.434322033899</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2341.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1845.8</v>
+        <v>1312.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1782.7</t>
+          <t>1731.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1386.18</v>
+        <v>1324.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-419</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>77.15000894233751</t>
+          <t>57.98550063978215</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>94.42627548221026</t>
+          <t>-47.41929502427229</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2341.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>702.221</t>
+          <t>2774.481</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.41</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>0.28</v>
+        <v>2.42</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>88.44</v>
+        <v>88.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>95.36</v>
+        <v>95</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>97.79</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>-2.38</v>
+        <v>-2.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2.75</v>
+        <v>-2.61</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.26</t>
+          <t>-136.27</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>60837416.0</t>
+          <t>247564662.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>60572677.2</v>
+        <v>97122828.59999999</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>59826908.2</t>
+          <t>79743823.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>204019569.06</v>
+        <v>203801095.58</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>745769</t>
+          <t>17379005</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-23466461.21743436</t>
+          <t>-20010208.62825078</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-16683257.10160669</t>
+          <t>-1000819.387741104</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>60837416.0</t>
+          <t>247564662.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5835,22 +5835,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>550.336</t>
+          <t>702.221</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-18.41</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,66 +6078,66 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.6</v>
+        <v>0.28</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.94</v>
+        <v>-1.57</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>88.73999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>95.79000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-2.53</v>
+        <v>-2.38</v>
       </c>
       <c r="AR14" t="n">
-        <v>-2.85</v>
+        <v>-2.75</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-139.56</t>
+          <t>-138.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>47715894.0</t>
+          <t>60837416.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>66195563.4</v>
+        <v>60572677.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>60586807.1</t>
+          <t>59826908.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>211721596.5</v>
+        <v>204019569.06</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5608756</t>
+          <t>745769</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-24699771.05667575</t>
+          <t>-23466461.21743436</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-18484418.2963573</t>
+          <t>-16683257.10160669</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>47715894.0</t>
+          <t>60837416.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>86.1</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>87.3</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>86.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>801.854</t>
+          <t>550.336</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,66 +6500,66 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-0.44</v>
+        <v>-0.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>-2.04</v>
+        <v>-1.94</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>87.28</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>89.09999999999999</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>96.26000000000001</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.76</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-2.62</v>
+        <v>-2.53</v>
       </c>
       <c r="AR15" t="n">
-        <v>-2.92</v>
+        <v>-2.85</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-140.65</t>
+          <t>-139.56</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69980794.0</t>
+          <t>47715894.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>64716425.2</v>
+        <v>66195563.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>66077711.5</t>
+          <t>60586807.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>222934351.1</v>
+        <v>211721596.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1361286</t>
+          <t>5608756</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-25829835.19491547</t>
+          <t>-24699771.05667575</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-18991470.56398827</t>
+          <t>-18484418.2963573</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>69980794.0</t>
+          <t>47715894.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6744,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
-      </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>678.728</t>
+          <t>801.854</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.21</v>
+        <v>-0.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>-2.41</v>
+        <v>-2.04</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>87.32000000000001</t>
+          <t>87.28</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>89.48</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AN16" t="n">
-        <v>96.72</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>97.76</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>10.51</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>-2.72</v>
+        <v>-2.62</v>
       </c>
       <c r="AR16" t="n">
-        <v>-3</v>
+        <v>-2.92</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-141.71</t>
+          <t>-140.65</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>59515377.0</t>
+          <t>69980794.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>61769492.8</v>
+        <v>64716425.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>65356195.9</t>
+          <t>66077711.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>234235775.26</v>
+        <v>222934351.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3586703</t>
+          <t>-1361286</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-27073174.21872042</t>
+          <t>-25829835.19491547</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-21423089.14046149</t>
+          <t>-18991470.56398827</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>59515377.0</t>
+          <t>69980794.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,42 +7213,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>678.728</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>739.811</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>87.1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,66 +7344,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>67.28</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.34</v>
+        <v>0.21</v>
       </c>
       <c r="AI17" t="n">
-        <v>-2.75</v>
+        <v>-2.41</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.32000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>89.87</v>
+        <v>89.48</v>
       </c>
       <c r="AN17" t="n">
-        <v>97.14</v>
+        <v>96.72</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>97.72</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>-2.88</v>
+        <v>-2.72</v>
       </c>
       <c r="AR17" t="n">
-        <v>-3.07</v>
+        <v>-3</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-142.67</t>
+          <t>-141.71</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>62364817.4</v>
+        <v>61769492.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>69391061.0</t>
+          <t>65356195.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>243715090.02</v>
+        <v>234235775.26</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-7026243</t>
+          <t>-3586703</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28100462.4147675</t>
+          <t>-27073174.21872042</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-23010424.95897819</t>
+          <t>-21423089.14046149</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1014.23</t>
+          <t>739.811</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,12 +7766,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7781,51 +7781,51 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="AI18" t="n">
-        <v>-3.37</v>
+        <v>-2.75</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>87.29999999999998</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>90.34</v>
+        <v>89.87</v>
       </c>
       <c r="AN18" t="n">
-        <v>97.52</v>
+        <v>97.14</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-3</v>
+        <v>-2.88</v>
       </c>
       <c r="AR18" t="n">
-        <v>-3.12</v>
+        <v>-3.07</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-143.32</t>
+          <t>-142.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>59081139.2</v>
+        <v>62364817.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>77327536.6</t>
+          <t>69391061.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>250820460.68</v>
+        <v>243715090.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-18246397</t>
+          <t>-7026243</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-29025923.77036555</t>
+          <t>-28100462.4147675</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-25023946.09403855</t>
+          <t>-23010424.95897819</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>461.141</t>
+          <t>1014.23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,266 +8188,266 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.8</v>
+        <v>-0.23</v>
       </c>
       <c r="AI19" t="n">
-        <v>-4.12</v>
+        <v>-3.37</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>87.29999999999998</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>97.62</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-143.32</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>351873007.4788135</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>59081139.2</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>77327536.6</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>250820460.68</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-18246397</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-29025923.77036555</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-25023946.09403855</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>23.06</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>35.83</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>18917</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>87.1</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>90.84</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>97.54</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AQ19" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-143.71</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>351845462.9448373</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>54978050.8</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>83135790.5</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>260959475.16</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-28157739</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-29753556.07515229</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-29592900.56933765</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-7.291353668658945</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>11.64963320584363</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>10.65346457950322</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>29.60%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>15.93%</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>35.33</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>18411</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>鉅祥-電子零組件業-上市</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>87.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8469,7 +8469,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="AI20" t="n">
-        <v>-5.08</v>
+        <v>-4.12</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN20" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-3.28</v>
+        <v>-3.11</v>
       </c>
       <c r="AR20" t="n">
-        <v>-3.15</v>
+        <v>-3.14</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
       <c r="AI21" t="n">
-        <v>-5.14</v>
+        <v>-5.08</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN21" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-3.37</v>
+        <v>-3.28</v>
       </c>
       <c r="AR21" t="n">
-        <v>-3.12</v>
+        <v>-3.15</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,66 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>-5.79</v>
+        <v>-5.14</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN22" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-3.52</v>
+        <v>-3.37</v>
       </c>
       <c r="AR22" t="n">
-        <v>-3.06</v>
+        <v>-3.12</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>351845462.9448373</t>
+          <t>351873007.4788135</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,143 +9876,143 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-5.79</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>351873007.4788135</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH23" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ23" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>351845462.9448373</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>95573934</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>336619552.5</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI23" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>65.769</t>
+          <t>33.154</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10303,54 +10303,54 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-1.38</v>
+        <v>-0.9</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.48</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>14.57</v>
+        <v>14.55</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.17</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AQ24" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-111.69</t>
+          <t>-111.45</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>940479.0</t>
+          <t>472050.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>1413394.6</v>
+        <v>1389357.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>1389041.8</t>
+          <t>1228535.9</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>4067497.64</v>
+        <v>4025193.42</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>160821</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-180857.6472476565</t>
+          <t>-176382.4624295088</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-83496.8637044155</t>
+          <t>-151768.9459296963</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>940479.0</t>
+          <t>472050.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10542,17 +10542,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>205.684</t>
+          <t>65.769</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-16.42</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10725,61 +10725,61 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>54.58</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-2.26</v>
+        <v>-1.38</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="AN25" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>13.20</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AQ25" t="n">
         <v>-0.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-111.69</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>2946717.0</t>
+          <t>940479.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>1543158.4</v>
+        <v>1413394.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>1563838.2</t>
+          <t>1389041.8</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>4086954.16</v>
+        <v>4067497.64</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-20679</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-198559.6078918822</t>
+          <t>-180857.6472476565</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-33172.1082502855</t>
+          <t>-83496.8637044155</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>2946717.0</t>
+          <t>940479.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>123.728</t>
+          <t>205.684</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-16.42</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11147,58 +11147,58 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.75</v>
+        <v>-2.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.36</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>14.64</v>
+        <v>14.6</v>
       </c>
       <c r="AN26" t="n">
         <v>15.12</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>13.20</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="AR26" t="n">
         <v>-0.23</v>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-112.38</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1840658.0</t>
+          <t>2946717.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>1262743.6</v>
+        <v>1543158.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>1429521.0</t>
+          <t>1563838.2</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>4055672.82</v>
+        <v>4086954.16</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-166777</t>
+          <t>-20679</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-228630.0623721725</t>
+          <t>-198559.6078918822</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-175048.9537354463</t>
+          <t>-33172.1082502855</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>1840658.0</t>
+          <t>2946717.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.009</t>
+          <t>123.728</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11569,12 +11569,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -11583,47 +11583,47 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>-1.11</v>
+        <v>-0.36</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>14.67</v>
+        <v>14.64</v>
       </c>
       <c r="AN27" t="n">
         <v>15.12</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-113.02</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>746884.0</t>
+          <t>1840658.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>975568.2</v>
+        <v>1262743.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1327427.2</t>
+          <t>1429521.0</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>4038105.5</v>
+        <v>4055672.82</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-351859</t>
+          <t>-166777</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-238372.0821243045</t>
+          <t>-228630.0623721725</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-252972.0917951243</t>
+          <t>-175048.9537354463</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>746884.0</t>
+          <t>1840658.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40.151</t>
+          <t>51.009</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-24.47</t>
+          <t>-26.51</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -11991,61 +11991,61 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
           <t>93.75</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>78.62</t>
-        </is>
-      </c>
       <c r="AH28" t="n">
-        <v>1.52</v>
+        <v>0.62</v>
       </c>
       <c r="AI28" t="n">
-        <v>-1.95</v>
+        <v>-1.11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>14.72</v>
+        <v>14.67</v>
       </c>
       <c r="AN28" t="n">
-        <v>15.13</v>
+        <v>15.12</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-113.43</t>
+          <t>-113.02</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>592235.0</t>
+          <t>746884.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>1067714.2</v>
+        <v>975568.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>1413578.5</t>
+          <t>1327427.2</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>4041840.44</v>
+        <v>4038105.5</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-345864</t>
+          <t>-351859</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-235717.5349114282</t>
+          <t>-238372.0821243045</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-238066.0714591246</t>
+          <t>-252972.0917951243</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>592235.0</t>
+          <t>746884.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12230,12 +12230,12 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>108.25</t>
+          <t>40.151</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-24.47</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12413,58 +12413,58 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>78.62</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>2.94</v>
+        <v>1.52</v>
       </c>
       <c r="AI29" t="n">
-        <v>-3.22</v>
+        <v>-1.95</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>14.76</v>
+        <v>14.72</v>
       </c>
       <c r="AN29" t="n">
         <v>15.13</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="AR29" t="n">
         <v>-0.26</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-113.64</t>
+          <t>-113.43</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>1589298.0</t>
+          <t>592235.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>1364689</v>
+        <v>1067714.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>1444815.3</t>
+          <t>1413578.5</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>4050706.62</v>
+        <v>4041840.44</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-80126</t>
+          <t>-345864</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-235290.5282663925</t>
+          <t>-235717.5349114282</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-191699.8612841559</t>
+          <t>-238066.0714591246</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>1589298.0</t>
+          <t>592235.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>107.92</t>
+          <t>108.25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12835,58 +12835,58 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>0.99</v>
+        <v>2.94</v>
       </c>
       <c r="AI30" t="n">
-        <v>-4.23</v>
+        <v>-3.22</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="AN30" t="n">
         <v>15.13</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-22.29</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AR30" t="n">
         <v>-0.26</v>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-113.64</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>1544643.0</t>
+          <t>1589298.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>1584518</v>
+        <v>1364689</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>1431444.6</t>
+          <t>1444815.3</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>4044797.48</v>
+        <v>4050706.62</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>153073</t>
+          <t>-80126</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-243216.1040813446</t>
+          <t>-235290.5282663925</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-225444.1731311949</t>
+          <t>-191699.8612841559</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>1544643.0</t>
+          <t>1589298.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>28.288</t>
+          <t>107.92</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13257,61 +13257,61 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>34.51</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.64</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>14.83</v>
+        <v>14.78</v>
       </c>
       <c r="AN31" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-32.90</t>
+          <t>-22.29</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-112.73</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>404781.0</t>
+          <t>1544643.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>1596298.4</v>
+        <v>1584518</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>1398769.7</t>
+          <t>1431444.6</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>4064230.28</v>
+        <v>4044797.48</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>197528</t>
+          <t>153073</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-246447.3642540991</t>
+          <t>-243216.1040813446</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-260814.2910151368</t>
+          <t>-225444.1731311949</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>404781.0</t>
+          <t>1544643.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>84.992</t>
+          <t>28.288</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13679,28 +13679,28 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="AI32" t="n">
-        <v>-4.59</v>
+        <v>-4.64</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -13710,30 +13710,30 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>14.87</v>
+        <v>14.83</v>
       </c>
       <c r="AN32" t="n">
-        <v>15.15</v>
+        <v>15.14</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-32.90</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-111.68</t>
+          <t>-112.73</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>1207614.0</t>
+          <t>404781.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>1679286.2</v>
+        <v>1596298.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1921306.9</t>
+          <t>1398769.7</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>4104519.9</v>
+        <v>4064230.28</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-242020</t>
+          <t>197528</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-243835.1957520922</t>
+          <t>-246447.3642540991</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-179900.1633130845</t>
+          <t>-260814.2910151368</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>1207614.0</t>
+          <t>404781.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="CF32" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="CG32" t="inlineStr">
+        <is>
           <t>14.3</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>14.2</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>148.395</t>
+          <t>84.992</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-18.48</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14101,61 +14101,61 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>-2.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI33" t="n">
-        <v>-4.7</v>
+        <v>-4.59</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>14.93</v>
+        <v>14.87</v>
       </c>
       <c r="AN33" t="n">
-        <v>15.17</v>
+        <v>15.15</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-63.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-110.30</t>
+          <t>-111.68</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>2077109.0</t>
+          <t>1207614.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>1759442.8</v>
+        <v>1679286.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>1890917.2</t>
+          <t>1921306.9</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>4159009.66</v>
+        <v>4104519.9</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-131474</t>
+          <t>-242020</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-255459.7471046391</t>
+          <t>-243835.1957520922</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-143901.3679061139</t>
+          <t>-179900.1633130845</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>2077109.0</t>
+          <t>1207614.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="CE33" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="CF33" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="CG33" t="inlineStr">
+        <is>
           <t>14.2</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>13.9</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>190.975</t>
+          <t>148.395</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-17.08</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-17.30</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14533,51 +14533,51 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>-2.22</v>
+        <v>-2.32</v>
       </c>
       <c r="AI34" t="n">
-        <v>-4.01</v>
+        <v>-4.7</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>15.02</v>
+        <v>14.93</v>
       </c>
       <c r="AN34" t="n">
-        <v>15.2</v>
+        <v>15.17</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>15.32</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-66.82</t>
+          <t>-63.35</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.27</v>
+        <v>-0.32</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-108.67</t>
+          <t>-110.30</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>26381716.39816125</t>
+          <t>26345454.19279661</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>2688443.0</t>
+          <t>2077109.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>1524941.6</v>
+        <v>1759442.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>1839009.9</t>
+          <t>1890917.2</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>4178193.24</v>
+        <v>4159009.66</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-314068</t>
+          <t>-131474</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-275743.0887770982</t>
+          <t>-255459.7471046391</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-180495.3613280805</t>
+          <t>-143901.3679061139</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>2688443.0</t>
+          <t>2077109.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -14762,12 +14762,12 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -943,42 +943,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>81.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>79.9</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1153,47 +1153,47 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>6.28</v>
+        <v>5.54</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.22</v>
+        <v>12.25</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>75.17999999999999</t>
+          <t>77.60000000000001</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>68.20999999999999</v>
+        <v>69.13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>65.81999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>94.20</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-56.26</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,48 +1212,48 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>7396.0</t>
+          <t>8040.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>8371.200000000001</v>
+        <v>9418.200000000001</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>4733.5</t>
+          <t>5416.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>2057.92</v>
+        <v>2200.4</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>589.7064861097956</t>
+          <t>720.98642989612</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1506.663253556186</t>
+          <t>1443.026120720904</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>7396.0</t>
+          <t>8040.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1635,47 +1635,47 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>9.99</v>
+        <v>6.28</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.83</v>
+        <v>10.22</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>72.64</t>
+          <t>75.17999999999999</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>67.36</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>65.5</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>65.17</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>105.33</t>
+          <t>94.20</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-73.52</t>
+          <t>-65.36</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>12334.0</t>
+          <t>7396.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>7029.2</v>
+        <v>8371.200000000001</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>4128.1</t>
+          <t>4733.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>1917.62</v>
+        <v>2057.92</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>422.9870738468156</t>
+          <t>589.7064861097956</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>1612.764041408154</t>
+          <t>1506.663253556186</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>12334.0</t>
+          <t>7396.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.99</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2117,47 +2117,47 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>6.28</v>
+        <v>9.99</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.37</v>
+        <v>7.83</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>66.53</v>
+        <v>67.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>65.18000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.17</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>105.33</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-80.49</t>
+          <t>-73.52</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,48 +2176,48 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>13543.0</t>
+          <t>12334.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>4935.6</v>
+        <v>7029.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>2955.7</t>
+          <t>4128.1</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>1689.06</v>
+        <v>1917.62</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>206.6639888356631</t>
+          <t>422.9870738468156</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1177.666451146388</t>
+          <t>1612.764041408154</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>13543.0</t>
+          <t>12334.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>66.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2599,47 +2599,47 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>5.22</v>
+        <v>6.28</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.44</v>
+        <v>5.37</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>65.97</v>
+        <v>66.53</v>
       </c>
       <c r="AZ5" t="n">
-        <v>64.95999999999999</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>64.91</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>76.81</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1.21</v>
+        <v>1.68</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-84.90</t>
+          <t>-80.49</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,48 +2658,48 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>5778.0</t>
+          <t>13543.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>2435.4</v>
+        <v>4935.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>1772.8</t>
+          <t>2955.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>1452.84</v>
+        <v>1689.06</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>30.11808659734954</t>
+          <t>206.6639888356631</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>384.5032346600663</t>
+          <t>1177.666451146388</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>5778.0</t>
+          <t>13543.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12.64</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>37.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3081,114 +3081,114 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>4.18</v>
+        <v>5.22</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.22</v>
+        <v>3.44</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>68.24</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>65.97</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>64.91</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>76.81</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-84.90</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>7867.47268907563</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>5778.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2435.4</v>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>1772.8</t>
+        </is>
+      </c>
+      <c r="BL6" t="n">
+        <v>1452.84</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>30.11808659734954</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>384.5032346600663</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>5778.0</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="AY6" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>64.86</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>56.28</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-87.80</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>7861.592566619916</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>2805.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1414</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>1252.1</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>1363.08</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-34.31557668678077</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>69.64495272746126</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>2805.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
           <t>2025/11/27</t>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>67.9</t>
-        </is>
-      </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,74 +3368,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14.77</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>12.93</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>67.2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>15.89</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4.69</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>67.2</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>90.0</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,51 +3559,51 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.6</v>
+        <v>4.18</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>66.14000000000001</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>65.22</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>64.69</v>
+        <v>64.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>56.28</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-89.51</t>
+          <t>-87.80</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,48 +3622,48 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>686.0</t>
+          <t>2805.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>1095.8</v>
+        <v>1414</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>1060.6</t>
+          <t>1252.1</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>1315.38</v>
+        <v>1363.08</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-53.21749112573387</t>
+          <t>-34.31557668678077</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-64.10419834509798</t>
+          <t>69.64495272746126</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>686.0</t>
+          <t>2805.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,51 +4041,51 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>66.05999999999999</t>
+          <t>66.14000000000001</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>65.04000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="AZ8" t="n">
-        <v>64.62</v>
+        <v>64.69</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-90.28</t>
+          <t>-89.51</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,48 +4104,48 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1866.0</t>
+          <t>686.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>1227</v>
+        <v>1095.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>998.9</t>
+          <t>1060.6</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>1315.84</v>
+        <v>1315.38</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>35</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-51.23808981312222</t>
+          <t>-53.21749112573387</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-25.84926422214335</t>
+          <t>-64.10419834509798</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1866.0</t>
+          <t>686.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>22.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,61 +4513,61 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>66.05999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>64.84</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>64.56</v>
+        <v>64.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-90.88</t>
+          <t>-90.28</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,48 +4586,48 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1042.0</t>
+          <t>1866.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>975.8</v>
+        <v>1227</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>1046.4</t>
+          <t>998.9</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>1294.06</v>
+        <v>1315.84</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-70</t>
+          <t>228</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-55.85423992057292</t>
+          <t>-51.23808981312222</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-96.70474175284585</t>
+          <t>-25.84926422214335</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1042.0</t>
+          <t>1866.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,61 +4995,61 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>53.57</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-1.15</v>
+        <v>-1.24</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>64.87</v>
+        <v>64.84</v>
       </c>
       <c r="AZ10" t="n">
-        <v>64.55</v>
+        <v>64.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-91.13</t>
+          <t>-90.88</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>1042.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>1110.2</v>
+        <v>975.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>1055.7</t>
+          <t>1046.4</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>1289.1</v>
+        <v>1294.06</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-70</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-48.42687595106875</t>
+          <t>-55.85423992057292</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-106.1873974483904</t>
+          <t>-96.70474175284585</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>1042.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,61 +5477,61 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>84.68</t>
+          <t>53.57</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-1.71</v>
+        <v>-1.15</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>66.64000000000001</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>64.84</v>
+        <v>64.87</v>
       </c>
       <c r="AZ11" t="n">
-        <v>64.53</v>
+        <v>64.55</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>65.03</t>
+          <t>64.96</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-91.91</t>
+          <t>-91.13</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1214.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>1090.2</v>
+        <v>1110.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>1065.2</t>
+          <t>1055.7</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>1287.32</v>
+        <v>1289.1</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>54</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-37.92496295155574</t>
+          <t>-48.42687595106875</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-76.19164139029726</t>
+          <t>-106.1873974483904</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1214.0</t>
+          <t>671.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
           <t>65.8</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>59.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.36</t>
+          <t>84.68</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.21</v>
+        <v>-1.71</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.37</v>
+        <v>2.78</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>66.94000000000001</t>
+          <t>66.64000000000001</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>64.76000000000001</v>
+        <v>64.84</v>
       </c>
       <c r="AZ12" t="n">
-        <v>64.51000000000001</v>
+        <v>64.53</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>65.09</t>
+          <t>65.03</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>117.42</t>
+          <t>63.12</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-93.18</t>
+          <t>-91.91</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7861.592566619916</t>
+          <t>7867.47268907563</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1342.0</t>
+          <t>1214.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>1025.4</v>
+        <v>1090.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>1168.8</t>
+          <t>1065.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>1294.18</v>
+        <v>1287.32</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-143</t>
+          <t>25</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-30.96738505360274</t>
+          <t>-37.92496295155574</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-88.79800268622512</t>
+          <t>-76.19164139029726</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1342.0</t>
+          <t>1214.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.17</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>77.49</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
           <t>65.5</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>66.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1543.527</t>
+          <t>729.797</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6415,17 +6415,17 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -6436,12 +6436,12 @@
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -6451,51 +6451,51 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>-0.52</v>
+        <v>-0.29</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.85999999999999</t>
         </is>
       </c>
       <c r="AY13" t="n">
-        <v>87.66</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>93.54000000000001</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>97.76</t>
+          <t>97.74</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BD13" t="n">
-        <v>-1.76</v>
+        <v>-1.62</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>-124.45</t>
+          <t>-122.49</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -6514,43 +6514,43 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>137673707.0</t>
+          <t>64840840.0</t>
         </is>
       </c>
       <c r="BJ13" t="n">
-        <v>125689193.8</v>
+        <v>98073388.40000001</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>111406011.2</t>
+          <t>111938557.5</t>
         </is>
       </c>
       <c r="BL13" t="n">
-        <v>178269824.62</v>
+        <v>176644905.64</v>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>14283182</t>
+          <t>-13865169</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-7134784.641639013</t>
+          <t>-6446458.61580967</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>1086109.263055518</t>
+          <t>-2660665.473748282</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>137673707.0</t>
+          <t>64840840.0</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="CK13" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>643.866</t>
+          <t>1543.527</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-17.20</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6918,50 +6918,50 @@
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="AY14" t="n">
-        <v>87.59999999999999</v>
+        <v>87.66</v>
       </c>
       <c r="AZ14" t="n">
-        <v>93.84999999999999</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6970,14 +6970,14 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-1.24</v>
+        <v>-1.14</v>
       </c>
       <c r="BD14" t="n">
-        <v>-1.91</v>
+        <v>-1.76</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>-126.59</t>
+          <t>-124.45</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -6996,43 +6996,43 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>56804590.0</t>
+          <t>137673707.0</t>
         </is>
       </c>
       <c r="BJ14" t="n">
-        <v>147667384.8</v>
+        <v>125689193.8</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>104120031.0</t>
+          <t>111406011.2</t>
         </is>
       </c>
       <c r="BL14" t="n">
-        <v>179667813.68</v>
+        <v>178269824.62</v>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>43547353</t>
+          <t>14283182</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-8629492.624310747</t>
+          <t>-7134784.641639013</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-1403666.47947675</t>
+          <t>1086109.263055518</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>56804590.0</t>
+          <t>137673707.0</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="CK14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL14" t="inlineStr">
@@ -7162,22 +7162,22 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1085.855</t>
+          <t>643.866</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7379,17 +7379,17 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -7400,66 +7400,66 @@
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>71.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>86.46</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>-0.18</v>
+        <v>-0.43</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.51</v>
+        <v>1.92</v>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>88.96000000000001</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AY15" t="n">
-        <v>87.64</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>94.15000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>97.77</t>
+          <t>97.76</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-1.38</v>
+        <v>-1.24</v>
       </c>
       <c r="BD15" t="n">
-        <v>-2.08</v>
+        <v>-1.91</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>-128.92</t>
+          <t>-126.59</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -7478,43 +7478,43 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>97061166.0</t>
+          <t>56804590.0</t>
         </is>
       </c>
       <c r="BJ15" t="n">
-        <v>148473950</v>
+        <v>147667384.8</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>107334756.7</t>
+          <t>104120031.0</t>
         </is>
       </c>
       <c r="BL15" t="n">
-        <v>182304910.58</v>
+        <v>179667813.68</v>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>41139193</t>
+          <t>43547353</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-9943279.196098745</t>
+          <t>-8629492.624310747</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>3754190.226887047</t>
+          <t>-1403666.47947675</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>97061166.0</t>
+          <t>56804590.0</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="CK15" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL15" t="inlineStr">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1480.896</t>
+          <t>1085.855</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7861,17 +7861,17 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -7882,66 +7882,66 @@
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>71.87</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>86.46</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1.02</v>
+        <v>-0.18</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.86</v>
+        <v>1.51</v>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.96000000000001</t>
         </is>
       </c>
       <c r="AY16" t="n">
-        <v>87.73999999999999</v>
+        <v>87.64</v>
       </c>
       <c r="AZ16" t="n">
-        <v>94.48</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>97.83</t>
+          <t>97.77</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-1.53</v>
+        <v>-1.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>-2.25</v>
+        <v>-2.08</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>-131.35</t>
+          <t>-128.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -7960,43 +7960,43 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>133986639.0</t>
+          <t>97061166.0</t>
         </is>
       </c>
       <c r="BJ16" t="n">
-        <v>138604895.6</v>
+        <v>148473950</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>101660660.4</t>
+          <t>107334756.7</t>
         </is>
       </c>
       <c r="BL16" t="n">
-        <v>186479697.22</v>
+        <v>182304910.58</v>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>36944235</t>
+          <t>41139193</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-12433728.18209616</t>
+          <t>-9943279.196098745</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>6675274.156446502</t>
+          <t>3754190.226887047</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>133986639.0</t>
+          <t>97061166.0</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -8061,17 +8061,17 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="CK16" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL16" t="inlineStr">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
@@ -8163,7 +8163,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2247.663</t>
+          <t>1480.896</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8343,17 +8343,17 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -8364,66 +8364,66 @@
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>96.87</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>84.67</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1.82</v>
+        <v>1.02</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0.01</v>
+        <v>0.86</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AY17" t="n">
-        <v>88.01000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>94.73</v>
+        <v>94.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>97.83</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>32.31</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-1.75</v>
+        <v>-1.53</v>
       </c>
       <c r="BD17" t="n">
-        <v>-2.44</v>
+        <v>-2.25</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>-133.88</t>
+          <t>-131.35</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -8442,43 +8442,43 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>202919867.0</t>
+          <t>133986639.0</t>
         </is>
       </c>
       <c r="BJ17" t="n">
-        <v>125803726.6</v>
+        <v>138604895.6</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>93786609.7</t>
+          <t>101660660.4</t>
         </is>
       </c>
       <c r="BL17" t="n">
-        <v>193744090.72</v>
+        <v>186479697.22</v>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>32017116</t>
+          <t>36944235</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-15908092.24364937</t>
+          <t>-12433728.18209616</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>6653547.87165834</t>
+          <t>6675274.156446502</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>202919867.0</t>
+          <t>133986639.0</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="CK17" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL17" t="inlineStr">
@@ -8608,22 +8608,22 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2774.481</t>
+          <t>2247.663</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>34.14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8825,17 +8825,17 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -8846,66 +8846,66 @@
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.87</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>84.67</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.71</v>
+        <v>-0.01</v>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AY18" t="n">
-        <v>88.2</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>95</v>
+        <v>94.73</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>97.79</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-2.03</v>
+        <v>-1.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>-2.61</v>
+        <v>-2.44</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>-136.27</t>
+          <t>-133.88</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -8924,43 +8924,43 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>247564662.0</t>
+          <t>202919867.0</t>
         </is>
       </c>
       <c r="BJ18" t="n">
-        <v>97122828.59999999</v>
+        <v>125803726.6</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>79743823.0</t>
+          <t>93786609.7</t>
         </is>
       </c>
       <c r="BL18" t="n">
-        <v>203801095.58</v>
+        <v>193744090.72</v>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>17379005</t>
+          <t>32017116</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-20010208.62825078</t>
+          <t>-15908092.24364937</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-1000819.387741104</t>
+          <t>6653547.87165834</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>247564662.0</t>
+          <t>202919867.0</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="CK18" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL18" t="inlineStr">
@@ -9090,22 +9090,22 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>702.221</t>
+          <t>2774.481</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.41</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9307,17 +9307,17 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -9328,66 +9328,66 @@
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>0.28</v>
+        <v>2.42</v>
       </c>
       <c r="AU19" t="n">
-        <v>-1.57</v>
+        <v>-0.71</v>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="AY19" t="n">
-        <v>88.44</v>
+        <v>88.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>95.36</v>
+        <v>95</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>97.79</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>21.98</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-2.38</v>
+        <v>-2.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>-2.75</v>
+        <v>-2.61</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>-138.26</t>
+          <t>-136.27</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -9406,43 +9406,43 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>60837416.0</t>
+          <t>247564662.0</t>
         </is>
       </c>
       <c r="BJ19" t="n">
-        <v>60572677.2</v>
+        <v>97122828.59999999</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>59826908.2</t>
+          <t>79743823.0</t>
         </is>
       </c>
       <c r="BL19" t="n">
-        <v>204019569.06</v>
+        <v>203801095.58</v>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>745769</t>
+          <t>17379005</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-23466461.21743436</t>
+          <t>-20010208.62825078</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-16683257.10160669</t>
+          <t>-1000819.387741104</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>60837416.0</t>
+          <t>247564662.0</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -9507,17 +9507,17 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="CK19" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL19" t="inlineStr">
@@ -9572,22 +9572,22 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>550.336</t>
+          <t>702.221</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-18.41</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9789,17 +9789,17 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -9810,66 +9810,66 @@
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>-0.6</v>
+        <v>0.28</v>
       </c>
       <c r="AU20" t="n">
-        <v>-1.94</v>
+        <v>-1.57</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AY20" t="n">
-        <v>88.73999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="AZ20" t="n">
-        <v>95.79000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>13.63</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-2.53</v>
+        <v>-2.38</v>
       </c>
       <c r="BD20" t="n">
-        <v>-2.85</v>
+        <v>-2.75</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>-139.56</t>
+          <t>-138.26</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
@@ -9888,43 +9888,43 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>47715894.0</t>
+          <t>60837416.0</t>
         </is>
       </c>
       <c r="BJ20" t="n">
-        <v>66195563.4</v>
+        <v>60572677.2</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>60586807.1</t>
+          <t>59826908.2</t>
         </is>
       </c>
       <c r="BL20" t="n">
-        <v>211721596.5</v>
+        <v>204019569.06</v>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>5608756</t>
+          <t>745769</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-24699771.05667575</t>
+          <t>-23466461.21743436</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-18484418.2963573</t>
+          <t>-16683257.10160669</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>47715894.0</t>
+          <t>60837416.0</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="CK20" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL20" t="inlineStr">
@@ -10054,22 +10054,22 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>86.1</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>87.3</t>
-        </is>
-      </c>
-      <c r="CQ20" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>86.1</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>86.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>801.854</t>
+          <t>550.336</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10271,17 +10271,17 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -10292,66 +10292,66 @@
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>-0.44</v>
+        <v>-0.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>-2.04</v>
+        <v>-1.94</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>87.28</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="AY21" t="n">
-        <v>89.09999999999999</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>96.26000000000001</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>97.76</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-2.62</v>
+        <v>-2.53</v>
       </c>
       <c r="BD21" t="n">
-        <v>-2.92</v>
+        <v>-2.85</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>-140.65</t>
+          <t>-139.56</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
@@ -10370,43 +10370,43 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>69980794.0</t>
+          <t>47715894.0</t>
         </is>
       </c>
       <c r="BJ21" t="n">
-        <v>64716425.2</v>
+        <v>66195563.4</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>66077711.5</t>
+          <t>60586807.1</t>
         </is>
       </c>
       <c r="BL21" t="n">
-        <v>222934351.1</v>
+        <v>211721596.5</v>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-1361286</t>
+          <t>5608756</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-25829835.19491547</t>
+          <t>-24699771.05667575</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-18991470.56398827</t>
+          <t>-18484418.2963573</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>69980794.0</t>
+          <t>47715894.0</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="CK21" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL21" t="inlineStr">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CQ21" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
-      </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>678.728</t>
+          <t>801.854</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10753,17 +10753,17 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -10774,66 +10774,66 @@
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>0.21</v>
+        <v>-0.44</v>
       </c>
       <c r="AU22" t="n">
-        <v>-2.41</v>
+        <v>-2.04</v>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>87.32000000000001</t>
+          <t>87.28</t>
         </is>
       </c>
       <c r="AY22" t="n">
-        <v>89.48</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>96.72</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>97.76</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>10.51</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-2.72</v>
+        <v>-2.62</v>
       </c>
       <c r="BD22" t="n">
-        <v>-3</v>
+        <v>-2.92</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>-141.71</t>
+          <t>-140.65</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
@@ -10852,43 +10852,43 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>59515377.0</t>
+          <t>69980794.0</t>
         </is>
       </c>
       <c r="BJ22" t="n">
-        <v>61769492.8</v>
+        <v>64716425.2</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>65356195.9</t>
+          <t>66077711.5</t>
         </is>
       </c>
       <c r="BL22" t="n">
-        <v>234235775.26</v>
+        <v>222934351.1</v>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-3586703</t>
+          <t>-1361286</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-27073174.21872042</t>
+          <t>-25829835.19491547</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-21423089.14046149</t>
+          <t>-18991470.56398827</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>59515377.0</t>
+          <t>69980794.0</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="CK22" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
@@ -11065,42 +11065,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>678.728</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>739.811</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>87.1</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11235,17 +11235,17 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -11256,66 +11256,66 @@
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>730</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>67.28</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>-0.34</v>
+        <v>0.21</v>
       </c>
       <c r="AU23" t="n">
-        <v>-2.75</v>
+        <v>-2.41</v>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.32000000000001</t>
         </is>
       </c>
       <c r="AY23" t="n">
-        <v>89.87</v>
+        <v>89.48</v>
       </c>
       <c r="AZ23" t="n">
-        <v>97.14</v>
+        <v>96.72</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>97.72</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-2.88</v>
+        <v>-2.72</v>
       </c>
       <c r="BD23" t="n">
-        <v>-3.07</v>
+        <v>-3</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>-142.67</t>
+          <t>-141.71</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
@@ -11334,43 +11334,43 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>350727571.1760168</t>
+          <t>350372576.342437</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="BJ23" t="n">
-        <v>62364817.4</v>
+        <v>61769492.8</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>69391061.0</t>
+          <t>65356195.9</t>
         </is>
       </c>
       <c r="BL23" t="n">
-        <v>243715090.02</v>
+        <v>234235775.26</v>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-7026243</t>
+          <t>-3586703</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-28100462.4147675</t>
+          <t>-27073174.21872042</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-23010424.95897819</t>
+          <t>-21423089.14046149</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
@@ -11505,17 +11505,17 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
@@ -11537,7 +11537,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>203.098</t>
+          <t>282.533</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11577,12 +11577,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-15.84</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11717,17 +11717,17 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -11738,66 +11738,66 @@
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>0.42</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AU24" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>14.34</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="AY24" t="n">
         <v>14.36</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.96</v>
+        <v>14.94</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BC24" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BD24" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-109.61</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
@@ -11816,43 +11816,43 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>2896825.0</t>
+          <t>4037973.0</t>
         </is>
       </c>
       <c r="BJ24" t="n">
-        <v>1719622</v>
+        <v>2266211.6</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>1554489.8</t>
+          <t>1883598.7</t>
         </is>
       </c>
       <c r="BL24" t="n">
-        <v>2196821.64</v>
+        <v>2235162.98</v>
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>165132</t>
+          <t>382612</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-105469.4323524598</t>
+          <t>-53710.37107420978</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>63690.98668445204</t>
+          <t>230964.4659561655</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>2896825.0</t>
+          <t>4037973.0</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -11957,12 +11957,12 @@
       </c>
       <c r="CK24" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
@@ -12029,42 +12029,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>203.098</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>-0.35</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>101.266</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-15.84</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12199,17 +12199,17 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -12220,66 +12220,66 @@
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="AU25" t="n">
-        <v>-0.42</v>
+        <v>-0.12</v>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>14.34</t>
         </is>
       </c>
       <c r="AY25" t="n">
-        <v>14.38</v>
+        <v>14.36</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.98</v>
+        <v>14.96</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>16.47</t>
         </is>
       </c>
       <c r="BC25" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="BD25" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>-110.44</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
@@ -12298,43 +12298,43 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1440266.0</t>
+          <t>2896825.0</t>
         </is>
       </c>
       <c r="BJ25" t="n">
-        <v>1234667</v>
+        <v>1719622</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>1324030.8</t>
+          <t>1554489.8</t>
         </is>
       </c>
       <c r="BL25" t="n">
-        <v>2200028.02</v>
+        <v>2196821.64</v>
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>-89363</t>
+          <t>165132</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-136225.8721773529</t>
+          <t>-105469.4323524598</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-55279.9475138688</t>
+          <t>63690.98668445204</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>1440266.0</t>
+          <t>2896825.0</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="CK25" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -12464,22 +12464,22 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
+          <t>14.55</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
           <t>14.4</t>
-        </is>
-      </c>
-      <c r="CR25" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>14.35</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>141.061</t>
+          <t>101.266</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12541,12 +12541,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-15.84</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12681,17 +12681,17 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -12702,63 +12702,63 @@
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="AU26" t="n">
-        <v>-0.68</v>
+        <v>-0.42</v>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AY26" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14.98</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="BC26" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="BD26" t="n">
         <v>-0.2</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>-110.78</t>
+          <t>-110.44</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
@@ -12780,43 +12780,43 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>2043336.0</t>
+          <t>1440266.0</t>
         </is>
       </c>
       <c r="BJ26" t="n">
-        <v>1134709.6</v>
+        <v>1234667</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
-          <t>1338934.0</t>
+          <t>1324030.8</t>
         </is>
       </c>
       <c r="BL26" t="n">
-        <v>2277439.74</v>
+        <v>2200028.02</v>
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>-204224</t>
+          <t>-89363</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-150943.3130252591</t>
+          <t>-136225.8721773529</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-67204.24824311747</t>
+          <t>-55279.9475138688</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>2043336.0</t>
+          <t>1440266.0</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="CC26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD26" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="CK26" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
@@ -12946,22 +12946,22 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
           <t>14.35</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>14.4</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>63.94</t>
+          <t>141.061</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13018,17 +13018,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13163,17 +13163,17 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -13184,67 +13184,67 @@
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>0.14</v>
+        <v>0.63</v>
       </c>
       <c r="AU27" t="n">
-        <v>-1.19</v>
+        <v>-0.68</v>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AY27" t="n">
-        <v>14.45</v>
+        <v>14.41</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.03</v>
+        <v>15</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="BC27" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="BD27" t="n">
         <v>-0.2</v>
       </c>
-      <c r="BD27" t="n">
-        <v>-0.21</v>
-      </c>
       <c r="BE27" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>-111.08</t>
+          <t>-110.78</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
@@ -13262,43 +13262,43 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>912658.0</t>
+          <t>2043336.0</t>
         </is>
       </c>
       <c r="BJ27" t="n">
-        <v>1315385.8</v>
+        <v>1134709.6</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
-          <t>1289064.7</t>
+          <t>1338934.0</t>
         </is>
       </c>
       <c r="BL27" t="n">
-        <v>2507792.08</v>
+        <v>2277439.74</v>
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>-204224</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-166168.597531103</t>
+          <t>-150943.3130252591</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-146453.4547047897</t>
+          <t>-67204.24824311747</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>912658.0</t>
+          <t>2043336.0</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
@@ -13373,12 +13373,12 @@
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -13403,12 +13403,12 @@
       </c>
       <c r="CK27" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
@@ -13428,22 +13428,22 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
           <t>14.35</t>
         </is>
       </c>
-      <c r="CR27" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
@@ -13475,12 +13475,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>63.94</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13500,17 +13500,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21.22</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-16.42</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13645,17 +13645,17 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -13666,59 +13666,59 @@
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>-0.77</v>
+        <v>0.14</v>
       </c>
       <c r="AU28" t="n">
-        <v>-1.05</v>
+        <v>-1.19</v>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AY28" t="n">
-        <v>14.51</v>
+        <v>14.45</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15.06</v>
+        <v>15.03</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BC28" t="n">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>-111.28</t>
+          <t>-111.08</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
@@ -13744,43 +13744,43 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1305025.0</t>
+          <t>912658.0</t>
         </is>
       </c>
       <c r="BJ28" t="n">
-        <v>1500985.8</v>
+        <v>1315385.8</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>1238277.0</t>
+          <t>1289064.7</t>
         </is>
       </c>
       <c r="BL28" t="n">
-        <v>3036367.9</v>
+        <v>2507792.08</v>
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>262708</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-169753.1689540691</t>
+          <t>-166168.597531103</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-133292.0548391505</t>
+          <t>-146453.4547047897</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>1305025.0</t>
+          <t>912658.0</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="CK28" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
@@ -13910,22 +13910,22 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
@@ -13957,12 +13957,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33.154</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -13982,17 +13982,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-16.42</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -14127,17 +14127,17 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
@@ -14148,66 +14148,66 @@
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>10.37</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>-0.9</v>
+        <v>-0.77</v>
       </c>
       <c r="AU29" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.05</v>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="AY29" t="n">
-        <v>14.55</v>
+        <v>14.51</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.1</v>
+        <v>15.06</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="BC29" t="n">
         <v>-0.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>-111.45</t>
+          <t>-111.28</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
@@ -14226,43 +14226,43 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>472050.0</t>
+          <t>1305025.0</t>
         </is>
       </c>
       <c r="BJ29" t="n">
-        <v>1389357.6</v>
+        <v>1500985.8</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>1228535.9</t>
+          <t>1238277.0</t>
         </is>
       </c>
       <c r="BL29" t="n">
-        <v>4025193.42</v>
+        <v>3036367.9</v>
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>160821</t>
+          <t>262708</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>-176382.4624295088</t>
+          <t>-169753.1689540691</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-151768.9459296963</t>
+          <t>-133292.0548391505</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>472050.0</t>
+          <t>1305025.0</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="CC29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD29" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="CK29" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
@@ -14392,22 +14392,22 @@
       </c>
       <c r="CP29" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>65.769</t>
+          <t>33.154</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14464,17 +14464,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -14630,59 +14630,59 @@
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>-1.38</v>
+        <v>-0.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>-0.48</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="AY30" t="n">
-        <v>14.57</v>
+        <v>14.55</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>15.17</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BC30" t="n">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>-111.69</t>
+          <t>-111.45</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
@@ -14708,43 +14708,43 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>940479.0</t>
+          <t>472050.0</t>
         </is>
       </c>
       <c r="BJ30" t="n">
-        <v>1413394.6</v>
+        <v>1389357.6</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>1389041.8</t>
+          <t>1228535.9</t>
         </is>
       </c>
       <c r="BL30" t="n">
-        <v>4067497.64</v>
+        <v>4025193.42</v>
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>160821</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>-180857.6472476565</t>
+          <t>-176382.4624295088</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-83496.8637044155</t>
+          <t>-151768.9459296963</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>940479.0</t>
+          <t>472050.0</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="CC30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD30" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
@@ -14849,12 +14849,12 @@
       </c>
       <c r="CK30" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
@@ -14874,17 +14874,17 @@
       </c>
       <c r="CP30" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
@@ -14921,12 +14921,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>205.684</t>
+          <t>65.769</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -14946,17 +14946,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15021,7 +15021,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-16.42</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15091,17 +15091,17 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -15112,66 +15112,66 @@
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>54.58</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>-2.26</v>
+        <v>-1.38</v>
       </c>
       <c r="AU31" t="n">
-        <v>-0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AY31" t="n">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>13.20</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BC31" t="n">
         <v>-0.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>-111.98</t>
+          <t>-111.69</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
@@ -15190,43 +15190,43 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>2946717.0</t>
+          <t>940479.0</t>
         </is>
       </c>
       <c r="BJ31" t="n">
-        <v>1543158.4</v>
+        <v>1413394.6</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>1563838.2</t>
+          <t>1389041.8</t>
         </is>
       </c>
       <c r="BL31" t="n">
-        <v>4086954.16</v>
+        <v>4067497.64</v>
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>-20679</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>-198559.6078918822</t>
+          <t>-180857.6472476565</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-33172.1082502855</t>
+          <t>-83496.8637044155</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>2946717.0</t>
+          <t>940479.0</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="CK31" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
@@ -15356,22 +15356,22 @@
       </c>
       <c r="CP31" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
@@ -15403,12 +15403,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>123.728</t>
+          <t>205.684</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -15428,17 +15428,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-11.67</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-16.42</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -15594,63 +15594,63 @@
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>0.75</v>
+        <v>-2.26</v>
       </c>
       <c r="AU32" t="n">
-        <v>-0.36</v>
+        <v>-0.1</v>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="AY32" t="n">
-        <v>14.64</v>
+        <v>14.6</v>
       </c>
       <c r="AZ32" t="n">
         <v>15.12</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>13.20</t>
         </is>
       </c>
       <c r="BC32" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="BD32" t="n">
         <v>-0.23</v>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>-112.38</t>
+          <t>-111.98</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
@@ -15672,43 +15672,43 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>1840658.0</t>
+          <t>2946717.0</t>
         </is>
       </c>
       <c r="BJ32" t="n">
-        <v>1262743.6</v>
+        <v>1543158.4</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>1429521.0</t>
+          <t>1563838.2</t>
         </is>
       </c>
       <c r="BL32" t="n">
-        <v>4055672.82</v>
+        <v>4086954.16</v>
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>-166777</t>
+          <t>-20679</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>-228630.0623721725</t>
+          <t>-198559.6078918822</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>-175048.9537354463</t>
+          <t>-33172.1082502855</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>1840658.0</t>
+          <t>2946717.0</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
@@ -15813,12 +15813,12 @@
       </c>
       <c r="CK32" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL32" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM32" t="inlineStr">
@@ -15838,22 +15838,22 @@
       </c>
       <c r="CP32" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="CQ32" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR32" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CT32" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>51.009</t>
+          <t>123.728</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -15910,17 +15910,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-11.67</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -16055,17 +16055,17 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -16076,17 +16076,17 @@
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -16095,47 +16095,47 @@
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="AU33" t="n">
-        <v>-1.11</v>
+        <v>-0.36</v>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>14.51</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AY33" t="n">
-        <v>14.67</v>
+        <v>14.64</v>
       </c>
       <c r="AZ33" t="n">
         <v>15.12</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BC33" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="BD33" t="n">
-        <v>-0.25</v>
+        <v>-0.23</v>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>-113.02</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
@@ -16154,43 +16154,43 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>746884.0</t>
+          <t>1840658.0</t>
         </is>
       </c>
       <c r="BJ33" t="n">
-        <v>975568.2</v>
+        <v>1262743.6</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>1327427.2</t>
+          <t>1429521.0</t>
         </is>
       </c>
       <c r="BL33" t="n">
-        <v>4038105.5</v>
+        <v>4055672.82</v>
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>-351859</t>
+          <t>-166777</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>-238372.0821243045</t>
+          <t>-228630.0623721725</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>-252972.0917951243</t>
+          <t>-175048.9537354463</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>746884.0</t>
+          <t>1840658.0</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="CC33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD33" t="inlineStr">
@@ -16265,12 +16265,12 @@
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="CK33" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL33" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM33" t="inlineStr">
@@ -16320,22 +16320,22 @@
       </c>
       <c r="CP33" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CQ33" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CR33" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CT33" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>40.151</t>
+          <t>51.009</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -16397,12 +16397,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-24.47</t>
+          <t>-26.51</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -16537,12 +16537,12 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -16558,66 +16558,66 @@
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>283</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
           <t>93.75</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>78.62</t>
-        </is>
-      </c>
       <c r="AT34" t="n">
-        <v>1.52</v>
+        <v>0.62</v>
       </c>
       <c r="AU34" t="n">
-        <v>-1.95</v>
+        <v>-1.11</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="AY34" t="n">
-        <v>14.72</v>
+        <v>14.67</v>
       </c>
       <c r="AZ34" t="n">
-        <v>15.13</v>
+        <v>15.12</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.23</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="BC34" t="n">
-        <v>-0.24</v>
+        <v>-0.22</v>
       </c>
       <c r="BD34" t="n">
-        <v>-0.26</v>
+        <v>-0.25</v>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>-113.43</t>
+          <t>-113.02</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
@@ -16636,43 +16636,43 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>26178792.05259467</t>
+          <t>26150610.21428571</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>592235.0</t>
+          <t>746884.0</t>
         </is>
       </c>
       <c r="BJ34" t="n">
-        <v>1067714.2</v>
+        <v>975568.2</v>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>1413578.5</t>
+          <t>1327427.2</t>
         </is>
       </c>
       <c r="BL34" t="n">
-        <v>4041840.44</v>
+        <v>4038105.5</v>
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>-345864</t>
+          <t>-351859</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>-235717.5349114282</t>
+          <t>-238372.0821243045</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>-238066.0714591246</t>
+          <t>-252972.0917951243</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>592235.0</t>
+          <t>746884.0</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="CC34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD34" t="inlineStr">
@@ -16747,12 +16747,12 @@
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
@@ -16777,12 +16777,12 @@
       </c>
       <c r="CK34" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL34" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="CM34" t="inlineStr">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="CP34" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CQ34" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CR34" t="inlineStr">
@@ -16817,7 +16817,7 @@
       </c>
       <c r="CS34" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CT34" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW34"/>
+  <dimension ref="A1:CW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,70 +1149,70 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>96.88</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>98.96</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.72</v>
+        <v>-1.17</v>
       </c>
       <c r="AV2" t="n">
-        <v>16.73</v>
+        <v>15.32</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>85.82000000000001</t>
+          <t>87.02000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>73.52</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>67.86</v>
+        <v>68.78</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>67.21</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5.72</v>
+        <v>5.81</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.9</v>
+        <v>4.59</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-14.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>9107.6</v>
+        <v>6927.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8739.4</t>
+          <t>8832.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>2848.26</v>
+        <v>2979.9</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-1904</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1093.963525651517</t>
+          <t>940.893182930256</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1017.737408501809</t>
+          <t>362.3489566076769</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>86.0</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>87.3</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,70 +1636,70 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.48</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.45</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.42</v>
+        <v>16.49</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>84.34</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>72.45</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>67.41</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>66.42</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>57.94</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5.43</v>
+        <v>5.84</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.44</v>
+        <v>4.29</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-24.12</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>6956.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>9711.6</v>
+        <v>8766</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8370.4</t>
+          <t>9092.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>2798.4</v>
+        <v>2936.24</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>1107.822819678736</t>
+          <t>1046.083042261634</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>1526.671108033216</t>
+          <t>782.7403836172798</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>6956.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,70 +2123,70 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.88</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.96</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>5.36</v>
+        <v>1.72</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>16.73</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>82.76000000000002</t>
+          <t>85.82000000000001</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>71.34</v>
+        <v>73.52</v>
       </c>
       <c r="BA4" t="n">
-        <v>66.97</v>
+        <v>67.86</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>66.14</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>67.73</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>4.93</v>
+        <v>5.72</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.94</v>
+        <v>3.9</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-35.11</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>13794.0</t>
+          <t>4376.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>10787.2</v>
+        <v>9107.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7861.4</t>
+          <t>8739.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>2692.06</v>
+        <v>2848.26</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>368</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1031.668585432467</t>
+          <t>1093.963525651517</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1922.766710648325</t>
+          <t>1017.737408501809</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>13794.0</t>
+          <t>4376.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,109 +2424,109 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16.02</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-30.00</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>84.9</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4.58</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>63.02</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-30.00</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/05/21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>False</t>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2624,56 +2624,56 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>5.83</v>
+        <v>4.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.35</v>
+        <v>16.42</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>80.22</t>
+          <t>84.34</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>70.15000000000001</v>
+        <v>72.45</v>
       </c>
       <c r="BA5" t="n">
-        <v>66.56</v>
+        <v>67.41</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.42</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>75.43</t>
+          <t>57.94</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>4.29</v>
+        <v>5.43</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.44</v>
+        <v>3.44</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-46.10</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>12372.0</t>
+          <t>6956.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>10737</v>
+        <v>9711.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6586.2</t>
+          <t>8370.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>2438.22</v>
+        <v>2798.4</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>869.6507444841296</t>
+          <t>1107.822819678736</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1687.304474718183</t>
+          <t>1526.671108033216</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>12372.0</t>
+          <t>6956.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,56 +3111,56 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.25</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>77.60000000000001</t>
+          <t>82.76000000000002</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>69.13</v>
+        <v>71.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>66.16</v>
+        <v>66.97</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>66.14</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>83.20</t>
+          <t>67.73</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3.63</v>
+        <v>4.93</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-56.26</t>
+          <t>-35.91</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>8040.0</t>
+          <t>13794.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>9418.200000000001</v>
+        <v>10787.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>5416.1</t>
+          <t>7861.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>2200.4</v>
+        <v>2692.06</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>720.98642989612</t>
+          <t>1031.668585432467</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1443.026120720904</t>
+          <t>1922.766710648325</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>8040.0</t>
+          <t>13794.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,56 +3598,56 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>6.28</v>
+        <v>5.83</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.22</v>
+        <v>14.35</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>75.17999999999999</t>
+          <t>80.22</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>68.20999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>65.81999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>94.20</t>
+          <t>75.43</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>3.05</v>
+        <v>4.29</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>2.44</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-46.76</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>7396.0</t>
+          <t>12372.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>8371.200000000001</v>
+        <v>10737</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>4733.5</t>
+          <t>6586.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2057.92</v>
+        <v>2438.22</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>589.7064861097956</t>
+          <t>869.6507444841296</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1506.663253556186</t>
+          <t>1687.304474718183</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>7396.0</t>
+          <t>12372.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,56 +4085,56 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>9.99</v>
+        <v>5.54</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.83</v>
+        <v>12.25</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>72.64</t>
+          <t>77.60000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>67.36</v>
+        <v>69.13</v>
       </c>
       <c r="BA8" t="n">
-        <v>65.5</v>
+        <v>66.16</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>65.17</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>105.33</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>2.47</v>
+        <v>3.63</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-73.52</t>
+          <t>-56.80</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>12334.0</t>
+          <t>8040.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>7029.2</v>
+        <v>9418.200000000001</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>4128.1</t>
+          <t>5416.1</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1917.62</v>
+        <v>2200.4</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>422.9870738468156</t>
+          <t>720.98642989612</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1612.764041408154</t>
+          <t>1443.026120720904</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>12334.0</t>
+          <t>8040.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>66.99</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4575,53 +4575,53 @@
         <v>6.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.37</v>
+        <v>10.22</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>75.17999999999999</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>66.53</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>65.18000000000001</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>94.20</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.88</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-80.49</t>
+          <t>-65.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>13543.0</t>
+          <t>7396.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>4935.6</v>
+        <v>8371.200000000001</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>2955.7</t>
+          <t>4733.5</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>1689.06</v>
+        <v>2057.92</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>206.6639888356631</t>
+          <t>589.7064861097956</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1177.666451146388</t>
+          <t>1506.663253556186</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>13543.0</t>
+          <t>7396.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5059,56 +5059,56 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>5.22</v>
+        <v>9.99</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.44</v>
+        <v>7.83</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>65.97</v>
+        <v>67.36</v>
       </c>
       <c r="BA10" t="n">
-        <v>64.95999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>64.91</t>
+          <t>65.17</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>76.81</t>
+          <t>105.33</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1.21</v>
+        <v>2.47</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.68</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-84.90</t>
+          <t>-73.84</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,48 +5118,48 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>7899.85</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5778.0</t>
+          <t>12334.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2435.4</v>
+        <v>7029.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1772.8</t>
+          <t>4128.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1452.84</v>
+        <v>1917.62</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>30.11808659734954</t>
+          <t>422.9870738468156</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>384.5032346600663</t>
+          <t>1612.764041408154</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5778.0</t>
+          <t>12334.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>66.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,114 +5546,114 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>4.18</v>
+        <v>6.28</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.22</v>
+        <v>5.37</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
+          <t>70.1</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>90.33</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-80.73</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>7899.85</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>13543.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>4935.6</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>2955.7</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
+        <v>1689.06</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>206.6639888356631</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>1177.666451146388</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>13543.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="AZ11" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>64.86</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>56.28</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-87.80</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>7901.981197771588</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>2805.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="n">
-        <v>1414</v>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1252.1</t>
-        </is>
-      </c>
-      <c r="BM11" t="n">
-        <v>1363.08</v>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-34.31557668678077</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>69.64495272746126</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>2805.0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="BT11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.87</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,132 +5808,132 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>951.833</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-07-23 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-24 00:00:00</t>
+          <t>2025-09-16 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-12-09 00:00:00</t>
+          <t>2025-03-06 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-01-10 00:00:00</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-15.09</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/05/21</t>
+          <t>2025/06/05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5943,67 +5943,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
+          <t>2025/10/28</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/07/07</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>69.9</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>2025/06/17</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>73.4</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/02/18</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>63.7</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,151 +6014,151 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.6</v>
+        <v>-1.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.41</v>
+        <v>0.31</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>66.14000000000001</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>65.22</v>
+        <v>88.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>64.69</v>
+        <v>91.52</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.61</v>
+        <v>-0.79</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.48</v>
+        <v>-1</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-89.51</t>
+          <t>-113.85</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>7901.981197771588</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>686.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1095.8</v>
+        <v>111275328.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1060.6</t>
+          <t>100026664.5</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>1315.38</v>
+        <v>147996956.16</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>11248664</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-53.21749112573387</t>
+          <t>-2738274.442947037</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-64.10419834509798</t>
+          <t>-1122935.745458856</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>686.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -6168,32 +6168,32 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>0.287940031871747</t>
+          <t>-7.291353668658945</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>5.366330372797562</t>
+          <t>11.64963320584363</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>100.0247812334774</t>
+          <t>10.65346457950322</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,92 +6203,92 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>21.24%</t>
+          <t>29.60%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>6.87%</t>
+          <t>15.93%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>車用電子產品85.06%、網通消費性7.34%、導線架5.11%、其他2.17%、營建0.33% (2024年)</t>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>佳穎-電子零組件業-上櫃</t>
+          <t>鉅祥-電子零組件業-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 半導體 - 導線架** 電腦及週邊設備 - 金屬、塑膠模具** 連接器 - 金屬材料** 建材營造 - 建設業** 汽車 - 其他** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 醫療器材 - 金屬零件</t>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1249.386</t>
+          <t>1363.614</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.29</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.41</v>
+        <v>-1.38</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>88.22</v>
+        <v>88.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>91.98</v>
+        <v>91.77</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>97.54</t>
+          <t>97.41</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="BE13" t="n">
-        <v>-1.12</v>
+        <v>-1.05</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-114.56</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>101146388.8</v>
+        <v>112207558.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>113417791.3</t>
+          <t>105140473.3</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>159052256.76</v>
+        <v>151128209.54</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-12271402</t>
+          <t>7067084</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-3786620.742334045</t>
+          <t>-3031972.387944888</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>284599.6578018218</t>
+          <t>1118593.561195478</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>90.1</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1393.898</t>
+          <t>1249.386</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.24</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-17.29</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>88.88000000000001</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>88.13</v>
+        <v>88.22</v>
       </c>
       <c r="BA14" t="n">
-        <v>92.23999999999999</v>
+        <v>91.98</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="BE14" t="n">
-        <v>-1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>125159487.0</t>
+          <t>111360593.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>106409011.6</v>
+        <v>101146388.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>127038198.2</t>
+          <t>113417791.3</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>162865460.56</v>
+        <v>159052256.76</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-20629186</t>
+          <t>-12271402</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4526842.633267839</t>
+          <t>-3786620.742334045</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>24382.73660366237</t>
+          <t>284599.6578018218</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>125159487.0</t>
+          <t>111360593.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1303.889</t>
+          <t>1393.898</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-16.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.26</v>
+        <v>0.59</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>88.88000000000001</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>87.95999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="BA15" t="n">
-        <v>92.54000000000001</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>97.63</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.83</v>
+        <v>-0.71</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.37</v>
+        <v>-1.24</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-118.99</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>116861326.0</t>
+          <t>125159487.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>92738032.2</v>
+        <v>106409011.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>120605991.1</t>
+          <t>127038198.2</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>163596980.62</v>
+        <v>162865460.56</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-27867958</t>
+          <t>-20629186</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-5354338.155062658</t>
+          <t>-4526842.633267839</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-1826679.462843835</t>
+          <t>24382.73660366237</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>116861326.0</t>
+          <t>125159487.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>993.996</t>
+          <t>1303.889</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-21.91</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.75</v>
+        <v>1.26</v>
       </c>
       <c r="AV16" t="n">
         <v>0.93</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>87.73999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>92.84</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>97.71</t>
+          <t>97.69</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>38.98</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.03</v>
+        <v>-0.83</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1.5</v>
+        <v>-1.37</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-118.99</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>87509698.0</t>
+          <t>116861326.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>88778000.2</v>
+        <v>92738032.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>113691447.9</t>
+          <t>120605991.1</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>169005650.08</v>
+        <v>163596980.62</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-24913447</t>
+          <t>-27867958</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-5995730.644556989</t>
+          <t>-5354338.155062658</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-3516726.802667245</t>
+          <t>-1826679.462843835</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>87509698.0</t>
+          <t>116861326.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,42 +8253,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>993.996</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>729.797</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-21.91</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.20</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.29</v>
+        <v>-0.75</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.25</v>
+        <v>0.93</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>88.85999999999999</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>87.76000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>93.23999999999999</v>
+        <v>92.84</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>97.74</t>
+          <t>97.71</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.05</v>
+        <v>-1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.62</v>
+        <v>-1.5</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-122.49</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>64840840.0</t>
+          <t>87509698.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>98073388.40000001</v>
+        <v>88778000.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>111938557.5</t>
+          <t>113691447.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>176644905.64</v>
+        <v>169005650.08</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-13865169</t>
+          <t>-24913447</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-6446458.61580967</t>
+          <t>-5995730.644556989</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-2660665.473748282</t>
+          <t>-3516726.802667245</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>64840840.0</t>
+          <t>87509698.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1543.527</t>
+          <t>729.797</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,51 +8951,51 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.52</v>
+        <v>-0.29</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.85999999999999</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>87.66</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="BA18" t="n">
-        <v>93.54000000000001</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>97.76</t>
+          <t>97.74</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.76</v>
+        <v>-1.62</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-124.45</t>
+          <t>-122.49</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>137673707.0</t>
+          <t>64840840.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>125689193.8</v>
+        <v>98073388.40000001</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>111406011.2</t>
+          <t>111938557.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>178269824.62</v>
+        <v>176644905.64</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>14283182</t>
+          <t>-13865169</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-7134784.641639013</t>
+          <t>-6446458.61580967</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1086109.263055518</t>
+          <t>-2660665.473748282</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>137673707.0</t>
+          <t>64840840.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>643.866</t>
+          <t>1543.527</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-17.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,50 +9423,50 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>87.59999999999999</v>
+        <v>87.66</v>
       </c>
       <c r="BA19" t="n">
-        <v>93.84999999999999</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
@@ -9475,14 +9475,14 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.24</v>
+        <v>-1.14</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.91</v>
+        <v>-1.76</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-126.59</t>
+          <t>-124.45</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>56804590.0</t>
+          <t>137673707.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>147667384.8</v>
+        <v>125689193.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>104120031.0</t>
+          <t>111406011.2</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>179667813.68</v>
+        <v>178269824.62</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>43547353</t>
+          <t>14283182</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-8629492.624310747</t>
+          <t>-7134784.641639013</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-1403666.47947675</t>
+          <t>1086109.263055518</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>56804590.0</t>
+          <t>137673707.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,22 +9602,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1085.855</t>
+          <t>643.866</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>71.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>86.46</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.18</v>
+        <v>-0.43</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.51</v>
+        <v>1.92</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>88.96000000000001</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>87.64</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>94.15000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>97.77</t>
+          <t>97.76</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-1.38</v>
+        <v>-1.24</v>
       </c>
       <c r="BE20" t="n">
-        <v>-2.08</v>
+        <v>-1.91</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-128.92</t>
+          <t>-126.59</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>97061166.0</t>
+          <t>56804590.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>148473950</v>
+        <v>147667384.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>107334756.7</t>
+          <t>104120031.0</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>182304910.58</v>
+        <v>179667813.68</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>41139193</t>
+          <t>43547353</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-9943279.196098745</t>
+          <t>-8629492.624310747</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>3754190.226887047</t>
+          <t>-1403666.47947675</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>97061166.0</t>
+          <t>56804590.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1480.896</t>
+          <t>1085.855</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-17.01</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>952</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>71.87</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>86.46</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>1.02</v>
+        <v>-0.18</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.86</v>
+        <v>1.51</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.96000000000001</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>87.73999999999999</v>
+        <v>87.64</v>
       </c>
       <c r="BA21" t="n">
-        <v>94.48</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>97.83</t>
+          <t>97.77</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-1.53</v>
+        <v>-1.38</v>
       </c>
       <c r="BE21" t="n">
-        <v>-2.25</v>
+        <v>-2.08</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-131.35</t>
+          <t>-128.92</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>348794234.7520833</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>133986639.0</t>
+          <t>97061166.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>138604895.6</v>
+        <v>148473950</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>101660660.4</t>
+          <t>107334756.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>186479697.22</v>
+        <v>182304910.58</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>36944235</t>
+          <t>41139193</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-12433728.18209616</t>
+          <t>-9943279.196098745</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>6675274.156446502</t>
+          <t>3754190.226887047</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>133986639.0</t>
+          <t>97061166.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>36.43</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10683,17 +10683,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2247.663</t>
+          <t>431.346</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,37 +10733,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-07-23 00:00:00</t>
+          <t>2025-05-16 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-09-16 00:00:00</t>
+          <t>2025-05-22 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10788,22 +10788,22 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>-15.09</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025/06/05</t>
+          <t>2025/06/17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -10813,67 +10813,67 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/10/29</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2025/06/17</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,121 +10884,121 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>96.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>84.67</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>88.01000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>94.73</v>
+        <v>14.8</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-1.75</v>
+        <v>-0.09</v>
       </c>
       <c r="BE22" t="n">
-        <v>-2.44</v>
+        <v>-0.14</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-133.88</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>202919867.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>125803726.6</v>
+        <v>2521617.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>93786609.7</t>
+          <t>2376458.4</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>193744090.72</v>
+        <v>1900953.72</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>32017116</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-15908092.24364937</t>
+          <t>48697.84917443918</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>6653547.87165834</t>
+          <t>348831.8917657966</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>202919867.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11008,32 +11008,32 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -11043,27 +11043,27 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>-7.291353668658945</t>
+          <t>-6.02377851815522</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>11.64963320584363</t>
+          <t>-4.975973459650803</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>10.65346457950322</t>
+          <t>-2.72815082383395</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,87 +11073,87 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>29.60%</t>
+          <t>6.98%</t>
         </is>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
-          <t>15.93%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+          <t>電線99.84%、其他0.16% (2024年)</t>
         </is>
       </c>
       <c r="CO22" t="inlineStr">
         <is>
-          <t>鉅祥-電子零組件業-上市</t>
+          <t>榮星-電器電纜-上市</t>
         </is>
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="CV22" t="inlineStr">
         <is>
-          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+          <t>** 通信網路 - 線材** 連接器 - 金屬材料** 電機機械 - 金屬加工處理** 其他 - 其他</t>
         </is>
       </c>
       <c r="CW22" t="inlineStr">
@@ -11170,17 +11170,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2774.481</t>
+          <t>113.748</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>-23.64</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,37 +11220,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-23 00:00:00</t>
+          <t>2025-05-16 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-09-16 00:00:00</t>
+          <t>2025-05-22 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>2025-03-27 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-03-07 00:00:00</t>
+          <t>2025-04-07 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11275,22 +11275,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>-15.09</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/06/05</t>
+          <t>2025/06/17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11300,67 +11300,67 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/10/29</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/06/17</t>
+          <t>2025/10/23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-03-28 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,121 +11371,121 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.71</v>
+        <v>-0.57</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>88.2</v>
+        <v>14.38</v>
       </c>
       <c r="BA23" t="n">
-        <v>95</v>
+        <v>14.81</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>97.79</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-2.03</v>
+        <v>-0.12</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.61</v>
+        <v>-0.15</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-136.27</t>
+          <t>-107.88</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2025/11/28</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>349341721.6775766</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>247564662.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>97122828.59999999</v>
+        <v>1399497</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>79743823.0</t>
+          <t>1832854.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>203801095.58</v>
+        <v>1802723.72</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>17379005</t>
+          <t>-433357</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-20010208.62825078</t>
+          <t>-5871.97675126217</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-1000819.387741104</t>
+          <t>-234.5173715241253</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>247564662.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11495,32 +11495,32 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>15.55</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電器電纜</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -11530,27 +11530,27 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>-7.291353668658945</t>
+          <t>-6.02377851815522</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>11.64963320584363</t>
+          <t>-4.975973459650803</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>10.65346457950322</t>
+          <t>-2.72815082383395</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,87 +11560,87 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>29.60%</t>
+          <t>6.98%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>15.93%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+          <t>電線99.84%、其他0.16% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>鉅祥-電子零組件業-上市</t>
+          <t>榮星-電器電纜-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+          <t>** 通信網路 - 線材** 連接器 - 金屬材料** 電機機械 - 金屬加工處理** 其他 - 其他</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -15267,12 +15267,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>26016140.38579387</t>
+          <t>25960493.0125</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15540,1467 +15540,6 @@
         </is>
       </c>
       <c r="CW31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>【d2】</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>63.94</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-05-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2025-03-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-16.13</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="AU32" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>-3.87</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
-      </c>
-      <c r="AZ32" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>15.03</v>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>15.14</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="BD32" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>-111.08</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>26016140.38579387</t>
-        </is>
-      </c>
-      <c r="BJ32" t="inlineStr">
-        <is>
-          <t>912658.0</t>
-        </is>
-      </c>
-      <c r="BK32" t="n">
-        <v>1315385.8</v>
-      </c>
-      <c r="BL32" t="inlineStr">
-        <is>
-          <t>1289064.7</t>
-        </is>
-      </c>
-      <c r="BM32" t="n">
-        <v>2507792.08</v>
-      </c>
-      <c r="BN32" t="inlineStr">
-        <is>
-          <t>26321</t>
-        </is>
-      </c>
-      <c r="BO32" t="inlineStr">
-        <is>
-          <t>-166168.597531103</t>
-        </is>
-      </c>
-      <c r="BP32" t="inlineStr">
-        <is>
-          <t>-146453.4547047897</t>
-        </is>
-      </c>
-      <c r="BQ32" t="inlineStr">
-        <is>
-          <t>912658.0</t>
-        </is>
-      </c>
-      <c r="BR32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BU32" t="inlineStr">
-        <is>
-          <t>-8.04</t>
-        </is>
-      </c>
-      <c r="BV32" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="BW32" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="BX32" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BY32" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ32" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="CA32" t="inlineStr">
-        <is>
-          <t>-6.02377851815522</t>
-        </is>
-      </c>
-      <c r="CB32" t="inlineStr">
-        <is>
-          <t>-4.975973459650803</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>-2.72815082383395</t>
-        </is>
-      </c>
-      <c r="CD32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="CI32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ32" t="inlineStr">
-        <is>
-          <t>6.98%</t>
-        </is>
-      </c>
-      <c r="CK32" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="CL32" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
-      <c r="CM32" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="CN32" t="inlineStr">
-        <is>
-          <t>電線99.84%、其他0.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO32" t="inlineStr">
-        <is>
-          <t>榮星-電器電纜-上市</t>
-        </is>
-      </c>
-      <c r="CP32" t="inlineStr">
-        <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="CQ32" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="CR32" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="CS32" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="CT32" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="CU32" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
-      </c>
-      <c r="CV32" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 線材** 連接器 - 金屬材料** 電機機械 - 金屬加工處理** 其他 - 其他</t>
-        </is>
-      </c>
-      <c r="CW32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>【d2】</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>92.09</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2025-05-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025-03-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-16.42</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>10.37</t>
-        </is>
-      </c>
-      <c r="AU33" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>-3.66</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>14.36</t>
-        </is>
-      </c>
-      <c r="AZ33" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
-      </c>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>6.20</t>
-        </is>
-      </c>
-      <c r="BD33" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>-111.28</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="BI33" t="inlineStr">
-        <is>
-          <t>26016140.38579387</t>
-        </is>
-      </c>
-      <c r="BJ33" t="inlineStr">
-        <is>
-          <t>1305025.0</t>
-        </is>
-      </c>
-      <c r="BK33" t="n">
-        <v>1500985.8</v>
-      </c>
-      <c r="BL33" t="inlineStr">
-        <is>
-          <t>1238277.0</t>
-        </is>
-      </c>
-      <c r="BM33" t="n">
-        <v>3036367.9</v>
-      </c>
-      <c r="BN33" t="inlineStr">
-        <is>
-          <t>262708</t>
-        </is>
-      </c>
-      <c r="BO33" t="inlineStr">
-        <is>
-          <t>-169753.1689540691</t>
-        </is>
-      </c>
-      <c r="BP33" t="inlineStr">
-        <is>
-          <t>-133292.0548391505</t>
-        </is>
-      </c>
-      <c r="BQ33" t="inlineStr">
-        <is>
-          <t>1305025.0</t>
-        </is>
-      </c>
-      <c r="BR33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BU33" t="inlineStr">
-        <is>
-          <t>-8.36</t>
-        </is>
-      </c>
-      <c r="BV33" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="BW33" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="BX33" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BY33" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ33" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="CA33" t="inlineStr">
-        <is>
-          <t>-6.02377851815522</t>
-        </is>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>-4.975973459650803</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>-2.72815082383395</t>
-        </is>
-      </c>
-      <c r="CD33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ33" t="inlineStr">
-        <is>
-          <t>6.98%</t>
-        </is>
-      </c>
-      <c r="CK33" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="CL33" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
-      <c r="CM33" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="CN33" t="inlineStr">
-        <is>
-          <t>電線99.84%、其他0.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO33" t="inlineStr">
-        <is>
-          <t>榮星-電器電纜-上市</t>
-        </is>
-      </c>
-      <c r="CP33" t="inlineStr">
-        <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="CQ33" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="CR33" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="CS33" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="CT33" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="CU33" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
-      </c>
-      <c r="CV33" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 線材** 連接器 - 金屬材料** 電機機械 - 金屬加工處理** 其他 - 其他</t>
-        </is>
-      </c>
-      <c r="CW33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【d2】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>33.154</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-05-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-03-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>-16.13</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
-      </c>
-      <c r="AU34" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>-3.68</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AZ34" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>8.27</t>
-        </is>
-      </c>
-      <c r="BD34" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>-111.45</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2025/12/02</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>26016140.38579387</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>472050.0</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>1389357.6</v>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>1228535.9</t>
-        </is>
-      </c>
-      <c r="BM34" t="n">
-        <v>4025193.42</v>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>160821</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>-176382.4624295088</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>-151768.9459296963</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>472050.0</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>-8.04</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>榮星</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>-6.02377851815522</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>-4.975973459650803</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>-2.72815082383395</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ34" t="inlineStr">
-        <is>
-          <t>6.98%</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="CL34" t="inlineStr">
-        <is>
-          <t>24.26</t>
-        </is>
-      </c>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="CN34" t="inlineStr">
-        <is>
-          <t>電線99.84%、其他0.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO34" t="inlineStr">
-        <is>
-          <t>榮星-電器電纜-上市</t>
-        </is>
-      </c>
-      <c r="CP34" t="inlineStr">
-        <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="CQ34" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="CR34" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="CT34" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>12.23</t>
-        </is>
-      </c>
-      <c r="CV34" t="inlineStr">
-        <is>
-          <t>** 通信網路 - 線材** 連接器 - 金屬材料** 電機機械 - 金屬加工處理** 其他 - 其他</t>
-        </is>
-      </c>
-      <c r="CW34" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.56</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,70 +1144,70 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>81.88</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.32</v>
+        <v>13.55</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>87.02000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>75.45999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="BA2" t="n">
-        <v>68.78</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>67.49</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5.81</v>
+        <v>5.71</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.59</v>
+        <v>4.81</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>6927.8</v>
+        <v>5249.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8832.4</t>
+          <t>8018.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>2979.9</v>
+        <v>3057.46</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1904</t>
+          <t>-2769</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>940.893182930256</t>
+          <t>830.8351907541801</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>362.3489566076769</t>
+          <t>225.5162337857628</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,75 +1631,75 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>92.48</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>96.45</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.49</v>
+        <v>15.32</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.02000000000001</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>74.51000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>68.31999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>67.21</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>8766</v>
+        <v>6927.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>9092.1</t>
+          <t>8832.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>2936.24</v>
+        <v>2979.9</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-1904</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>1046.083042261634</t>
+          <t>940.893182930256</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>782.7403836172798</t>
+          <t>362.3489566076769</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,75 +2118,75 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>96.88</t>
+          <t>92.48</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>98.96</t>
+          <t>96.45</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.73</v>
+        <v>16.49</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>85.82000000000001</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>73.52</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>67.86</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>9107.6</v>
+        <v>8766</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8739.4</t>
+          <t>9092.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>2848.26</v>
+        <v>2936.24</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1093.963525651517</t>
+          <t>1046.083042261634</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1017.737408501809</t>
+          <t>782.7403836172798</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,75 +2605,75 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.88</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.96</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>4.1</v>
+        <v>1.72</v>
       </c>
       <c r="AV5" t="n">
-        <v>16.42</v>
+        <v>16.73</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>84.34</t>
+          <t>85.82000000000001</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>72.45</v>
+        <v>73.52</v>
       </c>
       <c r="BA5" t="n">
-        <v>67.41</v>
+        <v>67.86</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>66.42</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>57.94</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5.43</v>
+        <v>5.72</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>6956.0</t>
+          <t>4376.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>9711.6</v>
+        <v>9107.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8370.4</t>
+          <t>8739.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>2798.4</v>
+        <v>2848.26</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>368</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1107.822819678736</t>
+          <t>1093.963525651517</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1526.671108033216</t>
+          <t>1017.737408501809</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6956.0</t>
+          <t>4376.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>16.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,56 +3111,56 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>5.36</v>
+        <v>4.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>16.42</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>82.76000000000002</t>
+          <t>84.34</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>71.34</v>
+        <v>72.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>66.97</v>
+        <v>67.41</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>66.14</t>
+          <t>66.42</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>67.73</t>
+          <t>57.94</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>4.93</v>
+        <v>5.43</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.94</v>
+        <v>3.44</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-35.91</t>
+          <t>-28.53</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>13794.0</t>
+          <t>6956.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>10787.2</v>
+        <v>9711.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>7861.4</t>
+          <t>8370.4</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>2692.06</v>
+        <v>2798.4</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1031.668585432467</t>
+          <t>1107.822819678736</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1922.766710648325</t>
+          <t>1526.671108033216</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>13794.0</t>
+          <t>6956.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,109 +3398,109 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>37.22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>29.76</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-30.00</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>84.9</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>63.02</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>26.34</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-30.00</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/05/21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>False</t>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,56 +3598,56 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>5.83</v>
+        <v>5.36</v>
       </c>
       <c r="AV7" t="n">
-        <v>14.35</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>80.22</t>
+          <t>82.76000000000002</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>70.15000000000001</v>
+        <v>71.34</v>
       </c>
       <c r="BA7" t="n">
-        <v>66.56</v>
+        <v>66.97</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>65.84</t>
+          <t>66.14</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>75.43</t>
+          <t>67.73</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>4.29</v>
+        <v>4.93</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-46.76</t>
+          <t>-38.88</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>12372.0</t>
+          <t>13794.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>10737</v>
+        <v>10787.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6586.2</t>
+          <t>7861.4</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2438.22</v>
+        <v>2692.06</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>869.6507444841296</t>
+          <t>1031.668585432467</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1687.304474718183</t>
+          <t>1922.766710648325</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>12372.0</t>
+          <t>13794.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,56 +4085,56 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>5.54</v>
+        <v>5.83</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.25</v>
+        <v>14.35</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>77.60000000000001</t>
+          <t>80.22</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>69.13</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>66.16</v>
+        <v>66.56</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.84</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>83.20</t>
+          <t>75.43</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>3.63</v>
+        <v>4.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-56.80</t>
+          <t>-49.23</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>8040.0</t>
+          <t>12372.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>9418.200000000001</v>
+        <v>10737</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>5416.1</t>
+          <t>6586.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2200.4</v>
+        <v>2438.22</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>720.98642989612</t>
+          <t>869.6507444841296</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1443.026120720904</t>
+          <t>1687.304474718183</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>8040.0</t>
+          <t>12372.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>18.90</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,56 +4572,56 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>6.28</v>
+        <v>5.54</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.22</v>
+        <v>12.25</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>75.17999999999999</t>
+          <t>77.60000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>68.20999999999999</v>
+        <v>69.13</v>
       </c>
       <c r="BA9" t="n">
-        <v>65.81999999999999</v>
+        <v>66.16</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>94.20</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-65.79</t>
+          <t>-58.81</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>7396.0</t>
+          <t>8040.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>8371.200000000001</v>
+        <v>9418.200000000001</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>4733.5</t>
+          <t>5416.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2057.92</v>
+        <v>2200.4</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>589.7064861097956</t>
+          <t>720.98642989612</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1506.663253556186</t>
+          <t>1443.026120720904</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>7396.0</t>
+          <t>8040.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5059,56 +5059,56 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>9.99</v>
+        <v>6.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.83</v>
+        <v>10.22</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>72.64</t>
+          <t>75.17999999999999</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>67.36</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="BA10" t="n">
-        <v>65.5</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>65.17</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>105.33</t>
+          <t>94.20</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-73.84</t>
+          <t>-67.37</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,48 +5118,48 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>12334.0</t>
+          <t>7396.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>7029.2</v>
+        <v>8371.200000000001</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>4128.1</t>
+          <t>4733.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1917.62</v>
+        <v>2057.92</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>422.9870738468156</t>
+          <t>589.7064861097956</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1612.764041408154</t>
+          <t>1506.663253556186</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>12334.0</t>
+          <t>7396.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>66.99</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>18.90</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,56 +5546,56 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>6.28</v>
+        <v>9.99</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.37</v>
+        <v>7.83</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>72.64</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>66.53</v>
+        <v>67.36</v>
       </c>
       <c r="BA11" t="n">
-        <v>65.18000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.17</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>105.33</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-80.73</t>
+          <t>-75.06</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>7899.85</t>
+          <t>7900.129680998613</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>13543.0</t>
+          <t>12334.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>4935.6</v>
+        <v>7029.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2955.7</t>
+          <t>4128.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>1689.06</v>
+        <v>1917.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>206.6639888356631</t>
+          <t>422.9870738468156</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1177.666451146388</t>
+          <t>1612.764041408154</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>13543.0</t>
+          <t>12334.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.44</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>951.833</t>
+          <t>441.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.45</v>
+        <v>-0.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>88.2</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>91.52</v>
+        <v>91.27</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.79</v>
+        <v>-0.77</v>
       </c>
       <c r="BE12" t="n">
-        <v>-1</v>
+        <v>-0.95</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-113.85</t>
+          <t>-113.21</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>111275328.8</v>
+        <v>95636449.59999999</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>100026664.5</t>
+          <t>94187240.9</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>147996956.16</v>
+        <v>145660623.92</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>11248664</t>
+          <t>1449208</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2738274.442947037</t>
+          <t>-3236625.211952172</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-1122935.745458856</t>
+          <t>-5977554.441480413</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1363.614</t>
+          <t>951.833</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.38</v>
+        <v>-1.45</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AZ13" t="n">
         <v>88.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>91.77</v>
+        <v>91.52</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>97.41</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.74</v>
+        <v>-0.79</v>
       </c>
       <c r="BE13" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-114.56</t>
+          <t>-113.85</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>112207558.2</v>
+        <v>111275328.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>105140473.3</t>
+          <t>100026664.5</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>151128209.54</v>
+        <v>147996956.16</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>7067084</t>
+          <t>11248664</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-3031972.387944888</t>
+          <t>-2738274.442947037</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>1118593.561195478</t>
+          <t>-1122935.745458856</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="CT13" t="inlineStr">
+        <is>
           <t>87.2</t>
-        </is>
-      </c>
-      <c r="CT13" t="inlineStr">
-        <is>
-          <t>87.4</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1249.386</t>
+          <t>1363.614</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.29</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.41</v>
+        <v>-1.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>88.22</v>
+        <v>88.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>91.98</v>
+        <v>91.77</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>97.54</t>
+          <t>97.41</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="BE14" t="n">
-        <v>-1.12</v>
+        <v>-1.05</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-114.56</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>101146388.8</v>
+        <v>112207558.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>113417791.3</t>
+          <t>105140473.3</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>159052256.76</v>
+        <v>151128209.54</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-12271402</t>
+          <t>7067084</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-3786620.742334045</t>
+          <t>-3031972.387944888</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>284599.6578018218</t>
+          <t>1118593.561195478</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
           <t>90.1</t>
         </is>
       </c>
-      <c r="CR14" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1393.898</t>
+          <t>1249.386</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-16.24</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-17.29</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>88.88000000000001</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>88.13</v>
+        <v>88.22</v>
       </c>
       <c r="BA15" t="n">
-        <v>92.23999999999999</v>
+        <v>91.98</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>125159487.0</t>
+          <t>111360593.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>106409011.6</v>
+        <v>101146388.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>127038198.2</t>
+          <t>113417791.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>162865460.56</v>
+        <v>159052256.76</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-20629186</t>
+          <t>-12271402</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-4526842.633267839</t>
+          <t>-3786620.742334045</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>24382.73660366237</t>
+          <t>284599.6578018218</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>125159487.0</t>
+          <t>111360593.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7659,17 +7659,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1303.889</t>
+          <t>1393.898</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-23.11</t>
+          <t>-16.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.26</v>
+        <v>0.59</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>88.88000000000001</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>87.95999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="BA16" t="n">
-        <v>92.54000000000001</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>97.69</t>
+          <t>97.63</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>42.27</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.83</v>
+        <v>-0.71</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1.37</v>
+        <v>-1.24</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-118.99</t>
+          <t>-117.18</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>116861326.0</t>
+          <t>125159487.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>92738032.2</v>
+        <v>106409011.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>120605991.1</t>
+          <t>127038198.2</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>163596980.62</v>
+        <v>162865460.56</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-27867958</t>
+          <t>-20629186</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-5354338.155062658</t>
+          <t>-4526842.633267839</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-1826679.462843835</t>
+          <t>24382.73660366237</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>116861326.0</t>
+          <t>125159487.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>993.996</t>
+          <t>1303.889</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-21.91</t>
+          <t>-23.11</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.75</v>
+        <v>1.26</v>
       </c>
       <c r="AV17" t="n">
         <v>0.93</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>87.73999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>92.84</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>97.71</t>
+          <t>97.69</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>38.98</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.03</v>
+        <v>-0.83</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.5</v>
+        <v>-1.37</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-118.99</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>87509698.0</t>
+          <t>116861326.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>88778000.2</v>
+        <v>92738032.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>113691447.9</t>
+          <t>120605991.1</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>169005650.08</v>
+        <v>163596980.62</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-24913447</t>
+          <t>-27867958</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-5995730.644556989</t>
+          <t>-5354338.155062658</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-3516726.802667245</t>
+          <t>-1826679.462843835</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>87509698.0</t>
+          <t>116861326.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,34 +8740,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>993.996</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>729.797</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>-21.91</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.20</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.29</v>
+        <v>-0.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.25</v>
+        <v>0.93</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>88.85999999999999</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>87.76000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>93.23999999999999</v>
+        <v>92.84</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>97.74</t>
+          <t>97.71</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>34.91</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.05</v>
+        <v>-1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.62</v>
+        <v>-1.5</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-122.49</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>64840840.0</t>
+          <t>87509698.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>98073388.40000001</v>
+        <v>88778000.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>111938557.5</t>
+          <t>113691447.9</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>176644905.64</v>
+        <v>169005650.08</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-13865169</t>
+          <t>-24913447</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-6446458.61580967</t>
+          <t>-5995730.644556989</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-2660665.473748282</t>
+          <t>-3516726.802667245</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>64840840.0</t>
+          <t>87509698.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1543.527</t>
+          <t>729.797</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>-12.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,51 +9438,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>70.83</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.52</v>
+        <v>-0.29</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.85999999999999</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>87.66</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="BA19" t="n">
-        <v>93.54000000000001</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>97.76</t>
+          <t>97.74</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>34.91</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.76</v>
+        <v>-1.62</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-124.45</t>
+          <t>-122.49</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>137673707.0</t>
+          <t>64840840.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>125689193.8</v>
+        <v>98073388.40000001</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>111406011.2</t>
+          <t>111938557.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>178269824.62</v>
+        <v>176644905.64</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>14283182</t>
+          <t>-13865169</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-7134784.641639013</t>
+          <t>-6446458.61580967</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>1086109.263055518</t>
+          <t>-2660665.473748282</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>137673707.0</t>
+          <t>64840840.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,17 +9667,17 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>643.866</t>
+          <t>1543.527</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-17.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,50 +9910,50 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>70.83</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>87.59999999999999</v>
+        <v>87.66</v>
       </c>
       <c r="BA20" t="n">
-        <v>93.84999999999999</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
@@ -9962,14 +9962,14 @@
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-1.24</v>
+        <v>-1.14</v>
       </c>
       <c r="BE20" t="n">
-        <v>-1.91</v>
+        <v>-1.76</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-126.59</t>
+          <t>-124.45</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>56804590.0</t>
+          <t>137673707.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>147667384.8</v>
+        <v>125689193.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>104120031.0</t>
+          <t>111406011.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>179667813.68</v>
+        <v>178269824.62</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>43547353</t>
+          <t>14283182</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-8629492.624310747</t>
+          <t>-7134784.641639013</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-1403666.47947675</t>
+          <t>1086109.263055518</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>56804590.0</t>
+          <t>137673707.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1085.855</t>
+          <t>643.866</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>71.87</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>86.46</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.18</v>
+        <v>-0.43</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.51</v>
+        <v>1.92</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>88.96000000000001</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>87.64</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>94.15000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>97.77</t>
+          <t>97.76</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-1.38</v>
+        <v>-1.24</v>
       </c>
       <c r="BE21" t="n">
-        <v>-2.08</v>
+        <v>-1.91</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-128.92</t>
+          <t>-126.59</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>348794234.7520833</t>
+          <t>348390914.5859917</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>97061166.0</t>
+          <t>56804590.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>148473950</v>
+        <v>147667384.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>107334756.7</t>
+          <t>104120031.0</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>182304910.58</v>
+        <v>179667813.68</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>41139193</t>
+          <t>43547353</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-9943279.196098745</t>
+          <t>-8629492.624310747</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>3754190.226887047</t>
+          <t>-1403666.47947675</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>97061166.0</t>
+          <t>56804590.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>36.43</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>431.346</t>
+          <t>227.292</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,35 +10899,35 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.21</v>
+        <v>0.35</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.4</v>
+        <v>14.42</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.8</v>
+        <v>14.78</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
@@ -10936,14 +10936,14 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-106.41</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2521617.4</v>
+        <v>2822775</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2376458.4</t>
+          <t>2509841.5</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>1900953.72</v>
+        <v>1920541.68</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>145159</t>
+          <t>312933</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>48697.84917443918</t>
+          <t>96835.51558879873</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>348831.8917657966</t>
+          <t>361592.6808677763</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,42 +11175,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>431.346</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>113.748</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11376,12 +11376,12 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
@@ -11390,47 +11390,47 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.57</v>
+        <v>-0.21</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.38</v>
+        <v>14.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-107.88</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>1399497</v>
+        <v>2521617.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1832854.3</t>
+          <t>2376458.4</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>1802723.72</v>
+        <v>1900953.72</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-433357</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-5871.97675126217</t>
+          <t>48697.84917443918</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-234.5173715241253</t>
+          <t>348831.8917657966</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,192 +11662,192 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>113.748</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-23.64</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-05-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-05-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-03-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-04-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-16.13</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>15.45</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
           <t>-0.69</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>116.163</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>4.49</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-05-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2025-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-03-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>-16.13</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>-0.34</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11873,51 +11873,51 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ24" t="n">
         <v>14.38</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.83</v>
+        <v>14.81</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-107.88</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>1661534.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>1881341.8</v>
+        <v>1399497</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>1800481.9</t>
+          <t>1832854.3</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>1834681.52</v>
+        <v>1802723.72</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>-433357</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-6896.969365759996</t>
+          <t>-5871.97675126217</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>6816.488052714849</t>
+          <t>-234.5173715241253</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>1661534.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>76.688</t>
+          <t>116.163</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12350,54 +12350,54 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.49</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.19</v>
+        <v>-0.47</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>14.36</v>
+        <v>14.38</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.86</v>
+        <v>14.83</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BD25" t="n">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-108.59</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1097726.0</t>
+          <t>1661534.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>2128400</v>
+        <v>1881341.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>1681533.5</t>
+          <t>1800481.9</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>1860414.56</v>
+        <v>1834681.52</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>446866</t>
+          <t>80859</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-9390.32526002815</t>
+          <t>-6896.969365759996</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>13133.22837117384</t>
+          <t>6816.488052714849</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1097726.0</t>
+          <t>1661534.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>132.03</t>
+          <t>76.688</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-16.72</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12837,62 +12837,62 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.84</v>
+        <v>0.49</v>
       </c>
       <c r="AV26" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>-3.35</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>14.33</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+      <c r="BD26" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BE26" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>14.32</t>
-        </is>
-      </c>
-      <c r="AZ26" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="BD26" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>-0.17</v>
-      </c>
       <c r="BF26" t="inlineStr">
         <is>
           <t>1.9</t>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-108.96</t>
+          <t>-108.59</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1871379.0</t>
+          <t>1097726.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2196908</v>
+        <v>2128400</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>1665808.8</t>
+          <t>1681533.5</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2006977.52</v>
+        <v>1860414.56</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>531099</t>
+          <t>446866</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-13485.5168293376</t>
+          <t>-9390.32526002815</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>82096.09924143064</t>
+          <t>13133.22837117384</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1871379.0</t>
+          <t>1097726.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.724</t>
+          <t>132.03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-16.72</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13324,61 +13324,61 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>44.44</t>
-        </is>
-      </c>
       <c r="AU27" t="n">
-        <v>-0.42</v>
+        <v>-0.84</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AZ27" t="n">
         <v>14.34</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.92</v>
+        <v>14.89</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="BD27" t="n">
         <v>-0.15</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-109.23</t>
+          <t>-108.96</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>738097.0</t>
+          <t>1871379.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2231299.4</v>
+        <v>2196908</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>1773342.6</t>
+          <t>1665808.8</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>2107346.04</v>
+        <v>2006977.52</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>457956</t>
+          <t>531099</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-30863.99247856819</t>
+          <t>-13485.5168293376</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>94791.08979746047</t>
+          <t>82096.09924143064</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>738097.0</t>
+          <t>1871379.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
           <t>14.2</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>14.3</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>282.533</t>
+          <t>51.724</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-15.84</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13811,33 +13811,33 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -13846,19 +13846,19 @@
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>14.36</v>
+        <v>14.34</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.94</v>
+        <v>14.92</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>16.31</t>
         </is>
       </c>
       <c r="BD28" t="n">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-109.61</t>
+          <t>-109.23</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>4037973.0</t>
+          <t>738097.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2266211.6</v>
+        <v>2231299.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>1883598.7</t>
+          <t>1773342.6</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>2235162.98</v>
+        <v>2107346.04</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>382612</t>
+          <t>457956</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-53710.37107420978</t>
+          <t>-30863.99247856819</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>230964.4659561655</t>
+          <t>94791.08979746047</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>4037973.0</t>
+          <t>738097.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>203.098</t>
+          <t>282.533</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>20.31</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-15.84</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14298,61 +14298,61 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>0.42</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AV29" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>14.34</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="AZ29" t="n">
         <v>14.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>14.96</v>
+        <v>14.94</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BE29" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-109.61</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>2896825.0</t>
+          <t>4037973.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>1719622</v>
+        <v>2266211.6</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>1554489.8</t>
+          <t>1883598.7</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>2196821.64</v>
+        <v>2235162.98</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>165132</t>
+          <t>382612</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>-105469.4323524598</t>
+          <t>-53710.37107420978</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>63690.98668445204</t>
+          <t>230964.4659561655</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>2896825.0</t>
+          <t>4037973.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,22 +14472,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>101.266</t>
+          <t>203.098</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-15.84</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14785,61 +14785,61 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
       <c r="AV30" t="n">
-        <v>-0.42</v>
+        <v>-0.12</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>14.34</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>14.38</v>
+        <v>14.36</v>
       </c>
       <c r="BA30" t="n">
-        <v>14.98</v>
+        <v>14.96</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>16.47</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="BE30" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-110.44</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>1440266.0</t>
+          <t>2896825.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>1234667</v>
+        <v>1719622</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>1324030.8</t>
+          <t>1554489.8</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>2200028.02</v>
+        <v>2196821.64</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>-89363</t>
+          <t>165132</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>-136225.8721773529</t>
+          <t>-105469.4323524598</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-55279.9475138688</t>
+          <t>63690.98668445204</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>1440266.0</t>
+          <t>2896825.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
+          <t>14.55</t>
+        </is>
+      </c>
+      <c r="CS30" t="inlineStr">
+        <is>
+          <t>14.05</t>
+        </is>
+      </c>
+      <c r="CT30" t="inlineStr">
+        <is>
           <t>14.4</t>
-        </is>
-      </c>
-      <c r="CS30" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>14.35</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>141.061</t>
+          <t>101.266</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-15.84</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15272,58 +15272,58 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="AV31" t="n">
-        <v>-0.68</v>
+        <v>-0.42</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
       <c r="BA31" t="n">
-        <v>15</v>
+        <v>14.98</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="BE31" t="n">
         <v>-0.2</v>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-110.78</t>
+          <t>-110.44</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>25960493.0125</t>
+          <t>25931512.78710125</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>2043336.0</t>
+          <t>1440266.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>1134709.6</v>
+        <v>1234667</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>1338934.0</t>
+          <t>1324030.8</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>2277439.74</v>
+        <v>2200028.02</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>-204224</t>
+          <t>-89363</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>-150943.3130252591</t>
+          <t>-136225.8721773529</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>-67204.24824311747</t>
+          <t>-55279.9475138688</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>2043336.0</t>
+          <t>1440266.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>24.98</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.15</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="CT31" t="inlineStr">
+        <is>
           <t>14.35</t>
-        </is>
-      </c>
-      <c r="CT31" t="inlineStr">
-        <is>
-          <t>14.4</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -978,17 +978,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.79</v>
+        <v>-1.47</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.04</v>
+        <v>5.43</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>86.03999999999999</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>80.38</v>
+        <v>81.34</v>
       </c>
       <c r="BA2" t="n">
-        <v>71.01000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.88</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4.95</v>
+        <v>4.61</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7980</v>
+        <v>7801</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>7453.9</t>
+          <t>6525.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>3650.3</v>
+        <v>3698.72</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>708.4855518157484</t>
+          <t>591.4911124595092</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>159.757199259232</t>
+          <t>-51.97830399980649</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.05</v>
+        <v>-1.79</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.69</v>
+        <v>7.04</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>86.34</t>
+          <t>86.03999999999999</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>79.44</v>
+        <v>80.38</v>
       </c>
       <c r="BA3" t="n">
-        <v>70.59</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5.31</v>
+        <v>4.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>8035.4</v>
+        <v>7980</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>8400.7</t>
+          <t>7453.9</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>3611.88</v>
+        <v>3650.3</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-365</t>
+          <t>526</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>808.2543431896604</t>
+          <t>708.4855518157484</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>628.1737325128852</t>
+          <t>159.757199259232</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,61 +2123,61 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>55.98</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.42</v>
+        <v>-0.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.26</v>
+        <v>8.69</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>86.34</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>78.40000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="BA4" t="n">
-        <v>70.14</v>
+        <v>70.59</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>68.36</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5.51</v>
+        <v>5.31</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.08</v>
+        <v>5.13</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>8004.6</v>
+        <v>8035.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8556.1</t>
+          <t>8400.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>3524.06</v>
+        <v>3611.88</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-551</t>
+          <t>-365</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>840.9962724036195</t>
+          <t>808.2543431896604</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>891.1197181426451</t>
+          <t>628.1737325128852</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.34</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,61 +2610,61 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>78.17</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.82</v>
+        <v>10.26</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>77.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>69.67</v>
+        <v>70.14</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5.63</v>
+        <v>5.51</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.98</v>
+        <v>5.08</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>6841</v>
+        <v>8004.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8276.3</t>
+          <t>8556.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>3337.94</v>
+        <v>3524.06</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1435</t>
+          <t>-551</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>831.8829186328876</t>
+          <t>840.9962724036195</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>837.645421965779</t>
+          <t>891.1197181426451</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-17.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>81.36</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>78.17</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.99</v>
+        <v>0.18</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.55</v>
+        <v>11.82</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>86.75999999999999</t>
+          <t>86.54</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>76.41</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>69.20999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>5.71</v>
+        <v>5.63</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.81</v>
+        <v>4.98</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>5249.2</v>
+        <v>6841</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8018.2</t>
+          <t>8276.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>3057.46</v>
+        <v>3337.94</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2769</t>
+          <t>-1435</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>830.8351907541801</t>
+          <t>831.8829186328876</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>225.5162337857628</t>
+          <t>837.645421965779</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.56</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>81.88</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.32</v>
+        <v>13.55</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>87.02000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>75.45999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="BA7" t="n">
-        <v>68.78</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>67.49</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>5.81</v>
+        <v>5.71</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.59</v>
+        <v>4.81</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>6927.8</v>
+        <v>5249.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8832.4</t>
+          <t>8018.2</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2979.9</v>
+        <v>3057.46</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1904</t>
+          <t>-2769</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>940.893182930256</t>
+          <t>830.8351907541801</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>362.3489566076769</t>
+          <t>225.5162337857628</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>92.48</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>96.45</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="AV8" t="n">
-        <v>16.49</v>
+        <v>15.32</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.02000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>74.51000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>68.31999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>67.21</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-16.41</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8766</v>
+        <v>6927.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>9092.1</t>
+          <t>8832.4</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2936.24</v>
+        <v>2979.9</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-1904</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1046.083042261634</t>
+          <t>940.893182930256</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>782.7403836172798</t>
+          <t>362.3489566076769</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,61 +4558,61 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>96.88</t>
+          <t>92.48</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>98.96</t>
+          <t>96.45</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.73</v>
+        <v>16.49</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>85.82000000000001</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>73.52</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>67.86</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-16.41</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>9107.6</v>
+        <v>8766</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8739.4</t>
+          <t>9092.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2848.26</v>
+        <v>2936.24</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1093.963525651517</t>
+          <t>1046.083042261634</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1017.737408501809</t>
+          <t>782.7403836172798</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.88</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.96</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>4.1</v>
+        <v>1.72</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.42</v>
+        <v>16.73</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>84.34</t>
+          <t>85.82000000000001</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>72.45</v>
+        <v>73.52</v>
       </c>
       <c r="BA10" t="n">
-        <v>67.41</v>
+        <v>67.86</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>66.42</t>
+          <t>66.69</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>57.94</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>5.43</v>
+        <v>5.72</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-32.91</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>7927.92</t>
+          <t>7926.309917355373</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6956.0</t>
+          <t>4376.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9711.6</v>
+        <v>9107.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8370.4</t>
+          <t>8739.4</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2798.4</v>
+        <v>2848.26</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>368</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1107.822819678736</t>
+          <t>1093.963525651517</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1526.671108033216</t>
+          <t>1017.737408501809</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6956.0</t>
+          <t>4376.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>30.30</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>80.37</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2267.169</t>
+          <t>1438.883</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>74.24</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>88.47</v>
+        <v>88.61</v>
       </c>
       <c r="BA11" t="n">
-        <v>90.28</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>96.22</t>
+          <t>95.91</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.44</v>
+        <v>-0.34</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.76</v>
+        <v>-0.68</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-109.39</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>203737902.0</t>
+          <t>128131031.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>128239336.4</v>
+        <v>146132156.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>119757332.6</t>
+          <t>120884303.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>140693214.84</v>
+        <v>140636943.88</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>8482003</t>
+          <t>25247853</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-410149.9745844807</t>
+          <t>1278326.497674501</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>12840690.60496596</t>
+          <t>10564947.0950989</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>203737902.0</t>
+          <t>128131031.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3130.894</t>
+          <t>2267.169</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>61.36</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.49</v>
+        <v>-0.15</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>88.34999999999999</v>
+        <v>88.47</v>
       </c>
       <c r="BA12" t="n">
-        <v>90.5</v>
+        <v>90.28</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.22</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.55</v>
+        <v>-0.44</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.84</v>
+        <v>-0.76</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>282535630.0</t>
+          <t>203737902.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>104061466.2</v>
+        <v>128239336.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>108134512.2</t>
+          <t>119757332.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>140300951.66</v>
+        <v>140693214.84</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-4073046</t>
+          <t>8482003</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2819393.716320924</t>
+          <t>-410149.9745844807</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>7532420.490313008</t>
+          <t>12840690.60496596</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>282535630.0</t>
+          <t>203737902.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,17 +6193,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>700.544</t>
+          <t>3130.894</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1.11</v>
+        <v>-0.49</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>88.18000000000001</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>90.73</v>
+        <v>90.5</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>96.64</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.87</v>
+        <v>-0.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>60695655.0</t>
+          <t>282535630.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>71583677.59999999</v>
+        <v>104061466.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>86365033.2</t>
+          <t>108134512.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>142652545.32</v>
+        <v>140300951.66</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-14781355</t>
+          <t>-4073046</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-4701541.75389073</t>
+          <t>-2819393.716320924</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-8762451.262416676</t>
+          <t>7532420.490313008</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>60695655.0</t>
+          <t>282535630.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>640.814</t>
+          <t>700.544</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7007,47 +7007,47 @@
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.78</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.7</v>
+        <v>-1.11</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>87.58000000000001</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>88.2</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="BA14" t="n">
-        <v>91.02</v>
+        <v>90.73</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>96.64</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-112.84</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>55560565.0</t>
+          <t>60695655.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>81716665.2</v>
+        <v>71583677.59999999</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>94062838.4</t>
+          <t>86365033.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>144519824.5</v>
+        <v>142652545.32</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-12346173</t>
+          <t>-14781355</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-3963194.570522375</t>
+          <t>-4701541.75389073</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-7959326.042658493</t>
+          <t>-8762451.262416676</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>55560565.0</t>
+          <t>60695655.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,42 +7279,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>640.814</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>86.9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>441.13</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,17 +7475,17 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
@@ -7494,47 +7494,47 @@
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.2</v>
+        <v>-0.78</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.15</v>
+        <v>-0.7</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.58000000000001</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>88.20999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>91.27</v>
+        <v>91.02</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>96.85</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.77</v>
+        <v>-0.82</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-113.21</t>
+          <t>-112.84</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>38666930.0</t>
+          <t>55560565.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>95636449.59999999</v>
+        <v>81716665.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>94187240.9</t>
+          <t>94062838.4</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>145660623.92</v>
+        <v>144519824.5</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>1449208</t>
+          <t>-12346173</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-3236625.211952172</t>
+          <t>-3963194.570522375</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-5977554.441480413</t>
+          <t>-7959326.042658493</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>38666930.0</t>
+          <t>55560565.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>951.833</t>
+          <t>441.13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.45</v>
+        <v>-0.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>88.2</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>91.52</v>
+        <v>91.27</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.79</v>
+        <v>-0.77</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1</v>
+        <v>-0.95</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-113.85</t>
+          <t>-113.21</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>111275328.8</v>
+        <v>95636449.59999999</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>100026664.5</t>
+          <t>94187240.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>147996956.16</v>
+        <v>145660623.92</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>11248664</t>
+          <t>1449208</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2738274.442947037</t>
+          <t>-3236625.211952172</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-1122935.745458856</t>
+          <t>-5977554.441480413</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1363.614</t>
+          <t>951.833</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,12 +8449,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8464,51 +8464,51 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.38</v>
+        <v>-1.45</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AZ17" t="n">
         <v>88.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>91.77</v>
+        <v>91.52</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>97.41</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.74</v>
+        <v>-0.79</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-114.56</t>
+          <t>-113.85</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>112207558.2</v>
+        <v>111275328.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>105140473.3</t>
+          <t>100026664.5</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>151128209.54</v>
+        <v>147996956.16</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>7067084</t>
+          <t>11248664</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-3031972.387944888</t>
+          <t>-2738274.442947037</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>1118593.561195478</t>
+          <t>-1122935.745458856</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
           <t>87.2</t>
-        </is>
-      </c>
-      <c r="CT17" t="inlineStr">
-        <is>
-          <t>87.4</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1249.386</t>
+          <t>1363.614</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.29</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.41</v>
+        <v>-1.38</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>88.22</v>
+        <v>88.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>91.98</v>
+        <v>91.77</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>97.54</t>
+          <t>97.41</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.12</v>
+        <v>-1.05</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-114.56</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>101146388.8</v>
+        <v>112207558.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>113417791.3</t>
+          <t>105140473.3</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>159052256.76</v>
+        <v>151128209.54</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-12271402</t>
+          <t>7067084</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-3786620.742334045</t>
+          <t>-3031972.387944888</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>284599.6578018218</t>
+          <t>1118593.561195478</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
           <t>90.1</t>
         </is>
       </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1393.898</t>
+          <t>1249.386</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-16.24</t>
+          <t>-10.82</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-17.29</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>88.88000000000001</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>88.13</v>
+        <v>88.22</v>
       </c>
       <c r="BA19" t="n">
-        <v>92.23999999999999</v>
+        <v>91.98</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>97.63</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>42.27</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-117.18</t>
+          <t>-115.64</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>347715371.0958621</t>
+          <t>347501157.838843</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>125159487.0</t>
+          <t>111360593.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>106409011.6</v>
+        <v>101146388.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>127038198.2</t>
+          <t>113417791.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>162865460.56</v>
+        <v>159052256.76</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-20629186</t>
+          <t>-12271402</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-4526842.633267839</t>
+          <t>-3786620.742334045</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>24382.73660366237</t>
+          <t>284599.6578018218</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>125159487.0</t>
+          <t>111360593.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.61</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>141.743</t>
+          <t>219.266</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-12.94</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>71.67</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.29</v>
+        <v>-1.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>14.42</v>
+        <v>14.44</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.71</v>
+        <v>14.69</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>112.33</t>
+          <t>94.48</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-102.61</t>
+          <t>-102.11</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2051916.0</t>
+          <t>3160120.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2219282</v>
+        <v>2175872.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>2370449.7</t>
+          <t>2499323.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>1963397.92</v>
+        <v>2012189.46</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-151167</t>
+          <t>-323451</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>115704.4448370511</t>
+          <t>114810.8753269176</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>47429.30185316503</t>
+          <t>109896.2430211832</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2051916.0</t>
+          <t>3160120.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>97.727</t>
+          <t>141.743</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>71.67</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.14</v>
+        <v>-1.29</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>14.44</v>
+        <v>14.42</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.73</v>
+        <v>14.71</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>118.20</t>
+          <t>112.33</t>
         </is>
       </c>
       <c r="BD21" t="n">
         <v>0.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-103.34</t>
+          <t>-102.61</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>1443719.0</t>
+          <t>2051916.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>3078638.6</v>
+        <v>2219282</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2239067.8</t>
+          <t>2370449.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>1944320.84</v>
+        <v>1963397.92</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>839570</t>
+          <t>-151167</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>128118.1071977577</t>
+          <t>115704.4448370511</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>75233.05368981184</t>
+          <t>47429.30185316503</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>1443719.0</t>
+          <t>2051916.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>98.471</t>
+          <t>97.727</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
+          <t>83.33</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>97.22</t>
-        </is>
-      </c>
       <c r="AU22" t="n">
-        <v>0.75</v>
+        <v>-0.14</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.43</v>
+        <v>14.44</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.74</v>
+        <v>14.73</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>97.50</t>
+          <t>118.20</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-104.33</t>
+          <t>-103.34</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>1456124.0</t>
+          <t>1443719.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3115644.6</v>
+        <v>3078638.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2498493.2</t>
+          <t>2239067.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>1944927.72</v>
+        <v>1944320.84</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>617151</t>
+          <t>839570</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>137733.5714719296</t>
+          <t>128118.1071977577</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>177429.7686818144</t>
+          <t>75233.05368981184</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>1456124.0</t>
+          <t>1443719.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>189.182</t>
+          <t>98.471</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.72</v>
+        <v>0.75</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.42</v>
+        <v>14.43</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.76</v>
+        <v>14.74</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>76.06</t>
+          <t>97.50</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-104.33</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>2767484.0</t>
+          <t>1456124.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3156726.6</v>
+        <v>3115644.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2642563.3</t>
+          <t>2498493.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>1946447.4</v>
+        <v>1944927.72</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>514163</t>
+          <t>617151</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>130516.0810701324</t>
+          <t>137733.5714719296</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>315759.1912174677</t>
+          <t>177429.7686818144</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>2767484.0</t>
+          <t>1456124.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>227.292</t>
+          <t>189.182</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11873,51 +11873,51 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="AZ24" t="n">
         <v>14.42</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>76.06</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-106.41</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>3377167.0</t>
+          <t>2767484.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>2822775</v>
+        <v>3156726.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>2509841.5</t>
+          <t>2642563.3</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>1920541.68</v>
+        <v>1946447.4</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>514163</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>96835.51558879873</t>
+          <t>130516.0810701324</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>361592.6808677763</t>
+          <t>315759.1912174677</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>3377167.0</t>
+          <t>2767484.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>431.346</t>
+          <t>227.292</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,35 +12360,35 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.21</v>
+        <v>0.35</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>14.4</v>
+        <v>14.42</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.8</v>
+        <v>14.78</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
@@ -12397,14 +12397,14 @@
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-106.41</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>2521617.4</v>
+        <v>2822775</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>2376458.4</t>
+          <t>2509841.5</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>1900953.72</v>
+        <v>1920541.68</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>145159</t>
+          <t>312933</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>48697.84917443918</t>
+          <t>96835.51558879873</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>348831.8917657966</t>
+          <t>361592.6808677763</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,42 +12636,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>431.346</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>113.748</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,17 +12832,17 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.57</v>
+        <v>-0.21</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>14.38</v>
+        <v>14.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-107.88</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>1399497</v>
+        <v>2521617.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>1832854.3</t>
+          <t>2376458.4</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>1802723.72</v>
+        <v>1900953.72</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-433357</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-5871.97675126217</t>
+          <t>48697.84917443918</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-234.5173715241253</t>
+          <t>348831.8917657966</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,192 +13123,192 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>113.748</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-23.64</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-05-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2025-05-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2025-03-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2025-04-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-16.13</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>15.45</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
           <t>-0.69</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>116.163</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4.49</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2025-05-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2025-03-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-16.13</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>-0.34</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ27" t="n">
         <v>14.38</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.83</v>
+        <v>14.81</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-107.88</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>1661534.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>1881341.8</v>
+        <v>1399497</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>1800481.9</t>
+          <t>1832854.3</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>1834681.52</v>
+        <v>1802723.72</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>-433357</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-6896.969365759996</t>
+          <t>-5871.97675126217</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>6816.488052714849</t>
+          <t>-234.5173715241253</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>1661534.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>76.688</t>
+          <t>116.163</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-16.13</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,59 +13806,59 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.49</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.19</v>
+        <v>-0.47</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>14.36</v>
+        <v>14.38</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.86</v>
+        <v>14.83</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="BD28" t="n">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-108.59</t>
+          <t>-108.23</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>25804413.21931034</t>
+          <t>25775399.12396694</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1097726.0</t>
+          <t>1661534.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2128400</v>
+        <v>1881341.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>1681533.5</t>
+          <t>1800481.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>1860414.56</v>
+        <v>1834681.52</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>446866</t>
+          <t>80859</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-9390.32526002815</t>
+          <t>-6896.969365759996</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>13133.22837117384</t>
+          <t>6816.488052714849</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1097726.0</t>
+          <t>1661534.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -948,164 +948,164 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-2.96</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-30.00</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/02/18</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-30.00</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/05/21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/02/18</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>2025/11/11</t>
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.47</v>
+        <v>-3.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.43</v>
+        <v>3.33</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>84.82000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>81.34</v>
+        <v>82.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>71.43000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>68.88</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-14.91</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4.61</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>4506.0</t>
+          <t>5554.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>7801</v>
+        <v>5928.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6525.1</t>
+          <t>6384.9</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>3698.72</v>
+        <v>3776.84</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>-456</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>591.4911124595092</t>
+          <t>481.9857568994096</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-51.97830399980649</t>
+          <t>-120.2936986811383</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>4506.0</t>
+          <t>5554.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1460,27 +1460,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,51 +1646,51 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.79</v>
+        <v>-1.47</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.04</v>
+        <v>5.43</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>86.03999999999999</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>80.38</v>
+        <v>81.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>71.01000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>4.95</v>
+        <v>4.61</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7980</v>
+        <v>7801</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>7453.9</t>
+          <t>6525.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>3650.3</v>
+        <v>3698.72</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>708.4855518157484</t>
+          <t>591.4911124595092</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>159.757199259232</t>
+          <t>-51.97830399980649</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,61 +2123,61 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.05</v>
+        <v>-1.79</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.69</v>
+        <v>7.04</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>86.34</t>
+          <t>86.03999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>79.44</v>
+        <v>80.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>70.59</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5.31</v>
+        <v>4.95</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>8035.4</v>
+        <v>7980</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>8400.7</t>
+          <t>7453.9</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>3611.88</v>
+        <v>3650.3</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-365</t>
+          <t>526</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>808.2543431896604</t>
+          <t>708.4855518157484</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>628.1737325128852</t>
+          <t>159.757199259232</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,22 +2579,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,61 +2610,61 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>55.98</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.42</v>
+        <v>-0.05</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.26</v>
+        <v>8.69</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>86.34</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>78.40000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="BA5" t="n">
-        <v>70.14</v>
+        <v>70.59</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>68.36</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5.51</v>
+        <v>5.31</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.08</v>
+        <v>5.13</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>8004.6</v>
+        <v>8035.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8556.1</t>
+          <t>8400.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>3524.06</v>
+        <v>3611.88</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-551</t>
+          <t>-365</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>840.9962724036195</t>
+          <t>808.2543431896604</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>891.1197181426451</t>
+          <t>628.1737325128852</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.34</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>78.17</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.82</v>
+        <v>10.26</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>77.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>69.67</v>
+        <v>70.14</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>5.63</v>
+        <v>5.51</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.98</v>
+        <v>5.08</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>6841</v>
+        <v>8004.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8276.3</t>
+          <t>8556.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>3337.94</v>
+        <v>3524.06</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1435</t>
+          <t>-551</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>831.8829186328876</t>
+          <t>840.9962724036195</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>837.645421965779</t>
+          <t>891.1197181426451</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-17.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>81.36</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>78.17</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.99</v>
+        <v>0.18</v>
       </c>
       <c r="AV7" t="n">
-        <v>13.55</v>
+        <v>11.82</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>86.75999999999999</t>
+          <t>86.54</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>76.41</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>69.20999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>5.71</v>
+        <v>5.63</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.81</v>
+        <v>4.98</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>5249.2</v>
+        <v>6841</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8018.2</t>
+          <t>8276.3</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>3057.46</v>
+        <v>3337.94</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2769</t>
+          <t>-1435</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>830.8351907541801</t>
+          <t>831.8829186328876</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>225.5162337857628</t>
+          <t>837.645421965779</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-21.56</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>81.88</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.32</v>
+        <v>13.55</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>87.02000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>75.45999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="BA8" t="n">
-        <v>68.78</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>67.49</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>5.81</v>
+        <v>5.71</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.59</v>
+        <v>4.81</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>6927.8</v>
+        <v>5249.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8832.4</t>
+          <t>8018.2</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2979.9</v>
+        <v>3057.46</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-1904</t>
+          <t>-2769</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>940.893182930256</t>
+          <t>830.8351907541801</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>362.3489566076769</t>
+          <t>225.5162337857628</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,61 +4558,61 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>92.48</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>96.45</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.49</v>
+        <v>15.32</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.02000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>74.51000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>68.31999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>67.21</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-16.41</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>8766</v>
+        <v>6927.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>9092.1</t>
+          <t>8832.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2936.24</v>
+        <v>2979.9</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-1904</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1046.083042261634</t>
+          <t>940.893182930256</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>782.7403836172798</t>
+          <t>362.3489566076769</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>96.88</t>
+          <t>92.48</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>98.96</t>
+          <t>96.45</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.73</v>
+        <v>16.49</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>85.82000000000001</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>73.52</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>67.86</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.9</v>
+        <v>4.29</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-16.41</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>7926.309917355373</t>
+          <t>4554.411885245901</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9107.6</v>
+        <v>8766</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8739.4</t>
+          <t>9092.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2848.26</v>
+        <v>2936.24</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>-326</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1093.963525651517</t>
+          <t>1046.083042261634</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1017.737408501809</t>
+          <t>782.7403836172798</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>4376.0</t>
+          <t>6332.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>30.30</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,42 +5331,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1617.533</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1438.883</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>89.3</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5501,22 +5501,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>61.36</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>74.24</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0.77</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.01</v>
+        <v>0.59</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>88.61</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>90.06999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>95.91</t>
+          <t>95.58</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.68</v>
+        <v>-0.58</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.39</t>
+          <t>-108.02</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>128131031.0</t>
+          <t>146438373.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>146132156.6</v>
+        <v>164307718.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>120884303.1</t>
+          <t>123012191.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>140636943.88</v>
+        <v>140765943.3</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>25247853</t>
+          <t>41295526</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1278326.497674501</t>
+          <t>2632561.438157572</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>10564947.0950989</t>
+          <t>10080853.61081447</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>128131031.0</t>
+          <t>146438373.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2267.169</t>
+          <t>1438.883</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5988,22 +5988,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>74.24</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>88.61999999999999</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>88.47</v>
+        <v>88.61</v>
       </c>
       <c r="BA12" t="n">
-        <v>90.28</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>96.22</t>
+          <t>95.91</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.44</v>
+        <v>-0.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.76</v>
+        <v>-0.68</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-109.39</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>203737902.0</t>
+          <t>128131031.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>128239336.4</v>
+        <v>146132156.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>119757332.6</t>
+          <t>120884303.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>140693214.84</v>
+        <v>140636943.88</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>8482003</t>
+          <t>25247853</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-410149.9745844807</t>
+          <t>1278326.497674501</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>12840690.60496596</t>
+          <t>10564947.0950989</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>203737902.0</t>
+          <t>128131031.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,22 +6253,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3130.894</t>
+          <t>2267.169</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6475,22 +6475,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>61.36</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.49</v>
+        <v>-0.15</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>88.34999999999999</v>
+        <v>88.47</v>
       </c>
       <c r="BA13" t="n">
-        <v>90.5</v>
+        <v>90.28</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.22</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.55</v>
+        <v>-0.44</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.84</v>
+        <v>-0.76</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>282535630.0</t>
+          <t>203737902.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>104061466.2</v>
+        <v>128239336.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>108134512.2</t>
+          <t>119757332.6</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>140300951.66</v>
+        <v>140693214.84</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-4073046</t>
+          <t>8482003</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2819393.716320924</t>
+          <t>-410149.9745844807</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>7532420.490313008</t>
+          <t>12840690.60496596</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>282535630.0</t>
+          <t>203737902.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,27 +6740,27 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>700.544</t>
+          <t>3130.894</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6962,22 +6962,22 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.11</v>
+        <v>-0.49</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>88.18000000000001</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="BA14" t="n">
-        <v>90.73</v>
+        <v>90.5</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>96.64</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.87</v>
+        <v>-0.55</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>60695655.0</t>
+          <t>282535630.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>71583677.59999999</v>
+        <v>104061466.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>86365033.2</t>
+          <t>108134512.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>142652545.32</v>
+        <v>140300951.66</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-14781355</t>
+          <t>-4073046</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-4701541.75389073</t>
+          <t>-2819393.716320924</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-8762451.262416676</t>
+          <t>7532420.490313008</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>60695655.0</t>
+          <t>282535630.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>640.814</t>
+          <t>700.544</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7449,22 +7449,22 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,12 +7475,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7494,47 +7494,47 @@
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.78</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.7</v>
+        <v>-1.11</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>87.58000000000001</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>88.2</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="BA15" t="n">
-        <v>91.02</v>
+        <v>90.73</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>96.64</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-112.84</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>55560565.0</t>
+          <t>60695655.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>81716665.2</v>
+        <v>71583677.59999999</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>94062838.4</t>
+          <t>86365033.2</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>144519824.5</v>
+        <v>142652545.32</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-12346173</t>
+          <t>-14781355</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-3963194.570522375</t>
+          <t>-4701541.75389073</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-7959326.042658493</t>
+          <t>-8762451.262416676</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>55560565.0</t>
+          <t>60695655.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>441.13</t>
+          <t>640.814</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7936,22 +7936,22 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,17 +7962,17 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
@@ -7981,47 +7981,47 @@
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.2</v>
+        <v>-0.78</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.15</v>
+        <v>-0.7</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>88.20999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>91.27</v>
+        <v>91.02</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.77</v>
+        <v>-0.82</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-113.21</t>
+          <t>-112.84</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>38666930.0</t>
+          <t>55560565.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>95636449.59999999</v>
+        <v>81716665.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>94187240.9</t>
+          <t>94062838.4</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>145660623.92</v>
+        <v>144519824.5</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>1449208</t>
+          <t>-12346173</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-3236625.211952172</t>
+          <t>-3963194.570522375</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-5977554.441480413</t>
+          <t>-7959326.042658493</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>38666930.0</t>
+          <t>55560565.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>951.833</t>
+          <t>441.13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.45</v>
+        <v>-0.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.08000000000001</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>88.2</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>91.52</v>
+        <v>91.27</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.79</v>
+        <v>-0.77</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1</v>
+        <v>-0.95</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-113.85</t>
+          <t>-113.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>111275328.8</v>
+        <v>95636449.59999999</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>100026664.5</t>
+          <t>94187240.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>147996956.16</v>
+        <v>145660623.92</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>11248664</t>
+          <t>1449208</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2738274.442947037</t>
+          <t>-3236625.211952172</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-1122935.745458856</t>
+          <t>-5977554.441480413</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1363.614</t>
+          <t>951.833</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8910,22 +8910,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,51 +8951,51 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.38</v>
+        <v>-1.45</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AZ18" t="n">
         <v>88.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>91.77</v>
+        <v>91.52</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>97.41</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.74</v>
+        <v>-0.79</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-114.56</t>
+          <t>-113.85</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>112207558.2</v>
+        <v>111275328.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>105140473.3</t>
+          <t>100026664.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>151128209.54</v>
+        <v>147996956.16</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>7067084</t>
+          <t>11248664</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-3031972.387944888</t>
+          <t>-2738274.442947037</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1118593.561195478</t>
+          <t>-1122935.745458856</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="CT18" t="inlineStr">
+        <is>
           <t>87.2</t>
-        </is>
-      </c>
-      <c r="CT18" t="inlineStr">
-        <is>
-          <t>87.4</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1249.386</t>
+          <t>1363.614</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-17.29</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9397,22 +9397,22 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.41</v>
+        <v>-1.38</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>88.22</v>
+        <v>88.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>91.98</v>
+        <v>91.77</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>97.54</t>
+          <t>97.41</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.12</v>
+        <v>-1.05</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-115.64</t>
+          <t>-114.56</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>347501157.838843</t>
+          <t>437655919.164959</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>101146388.8</v>
+        <v>112207558.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>113417791.3</t>
+          <t>105140473.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>159052256.76</v>
+        <v>151128209.54</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-12271402</t>
+          <t>7067084</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-3786620.742334045</t>
+          <t>-3031972.387944888</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>284599.6578018218</t>
+          <t>1118593.561195478</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>111360593.0</t>
+          <t>120146687.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
           <t>90.1</t>
         </is>
       </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>219.266</t>
+          <t>154.401</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-12.94</t>
+          <t>-20.72</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>14.44</v>
+        <v>14.45</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.69</v>
+        <v>14.67</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>94.48</t>
+          <t>110.40</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-102.11</t>
+          <t>-101.65</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>3160120.0</t>
+          <t>2252696.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2175872.6</v>
+        <v>2072915</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>2499323.8</t>
+          <t>2614820.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2012189.46</v>
+        <v>2020646.96</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-323451</t>
+          <t>-541905</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>114810.8753269176</t>
+          <t>109889.0323171251</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>109896.2430211832</t>
+          <t>82818.89576326637</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>3160120.0</t>
+          <t>2252696.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>14.5</t>
         </is>
       </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>141.743</t>
+          <t>219.266</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-12.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>71.67</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.29</v>
+        <v>-1.3</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>14.42</v>
+        <v>14.44</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.71</v>
+        <v>14.69</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>112.33</t>
+          <t>94.48</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-102.61</t>
+          <t>-102.11</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>2051916.0</t>
+          <t>3160120.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2219282</v>
+        <v>2175872.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2370449.7</t>
+          <t>2499323.8</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>1963397.92</v>
+        <v>2012189.46</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-151167</t>
+          <t>-323451</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>115704.4448370511</t>
+          <t>114810.8753269176</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>47429.30185316503</t>
+          <t>109896.2430211832</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>2051916.0</t>
+          <t>3160120.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>97.727</t>
+          <t>141.743</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>71.67</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.14</v>
+        <v>-1.29</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.44</v>
+        <v>14.42</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.73</v>
+        <v>14.71</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>118.20</t>
+          <t>112.33</t>
         </is>
       </c>
       <c r="BD22" t="n">
         <v>0.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-103.34</t>
+          <t>-102.61</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>1443719.0</t>
+          <t>2051916.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>3078638.6</v>
+        <v>2219282</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2239067.8</t>
+          <t>2370449.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>1944320.84</v>
+        <v>1963397.92</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>839570</t>
+          <t>-151167</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>128118.1071977577</t>
+          <t>115704.4448370511</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>75233.05368981184</t>
+          <t>47429.30185316503</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>1443719.0</t>
+          <t>2051916.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>98.471</t>
+          <t>97.727</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
+          <t>83.33</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>97.22</t>
-        </is>
-      </c>
       <c r="AU23" t="n">
-        <v>0.75</v>
+        <v>-0.14</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.43</v>
+        <v>14.44</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.74</v>
+        <v>14.73</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>97.50</t>
+          <t>118.20</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-104.33</t>
+          <t>-103.34</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1456124.0</t>
+          <t>1443719.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3115644.6</v>
+        <v>3078638.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2498493.2</t>
+          <t>2239067.8</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>1944927.72</v>
+        <v>1944320.84</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>617151</t>
+          <t>839570</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>137733.5714719296</t>
+          <t>128118.1071977577</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>177429.7686818144</t>
+          <t>75233.05368981184</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1456124.0</t>
+          <t>1443719.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>189.182</t>
+          <t>98.471</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>1.72</v>
+        <v>0.75</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>14.42</v>
+        <v>14.43</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.76</v>
+        <v>14.74</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>76.06</t>
+          <t>97.50</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-104.33</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>2767484.0</t>
+          <t>1456124.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>3156726.6</v>
+        <v>3115644.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>2642563.3</t>
+          <t>2498493.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>1946447.4</v>
+        <v>1944927.72</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>514163</t>
+          <t>617151</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>130516.0810701324</t>
+          <t>137733.5714719296</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>315759.1912174677</t>
+          <t>177429.7686818144</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>2767484.0</t>
+          <t>1456124.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>227.292</t>
+          <t>189.182</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="AZ25" t="n">
         <v>14.42</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>76.06</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-106.41</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>3377167.0</t>
+          <t>2767484.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>2822775</v>
+        <v>3156726.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>2509841.5</t>
+          <t>2642563.3</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>1920541.68</v>
+        <v>1946447.4</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>514163</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>96835.51558879873</t>
+          <t>130516.0810701324</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>361592.6808677763</t>
+          <t>315759.1912174677</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>3377167.0</t>
+          <t>2767484.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>431.346</t>
+          <t>227.292</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,35 +12847,35 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.21</v>
+        <v>0.35</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>14.4</v>
+        <v>14.42</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.8</v>
+        <v>14.78</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
@@ -12884,14 +12884,14 @@
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-106.41</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2521617.4</v>
+        <v>2822775</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>2376458.4</t>
+          <t>2509841.5</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>1900953.72</v>
+        <v>1920541.68</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>145159</t>
+          <t>312933</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>48697.84917443918</t>
+          <t>96835.51558879873</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>348831.8917657966</t>
+          <t>361592.6808677763</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,42 +13123,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>431.346</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>113.748</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,17 +13319,17 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.57</v>
+        <v>-0.21</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.38</v>
+        <v>14.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-107.88</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>1399497</v>
+        <v>2521617.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>1832854.3</t>
+          <t>2376458.4</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>1802723.72</v>
+        <v>1900953.72</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-433357</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-5871.97675126217</t>
+          <t>48697.84917443918</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-234.5173715241253</t>
+          <t>348831.8917657966</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,192 +13610,192 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>113.748</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-23.64</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2025-05-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2025-05-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-03-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-04-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-16.13</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16.95</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>14.85</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>15.45</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2025-03-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
           <t>-0.69</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>116.163</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>4.49</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-05-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2025-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-03-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2025-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-16.13</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>14.85</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>2025-03-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>-0.34</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.47</v>
+        <v>-0.57</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ28" t="n">
         <v>14.38</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.83</v>
+        <v>14.81</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.99</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-108.23</t>
+          <t>-107.88</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>25775399.12396694</t>
+          <t>37310523.43954918</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1661534.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>1881341.8</v>
+        <v>1399497</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>1800481.9</t>
+          <t>1832854.3</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>1834681.52</v>
+        <v>1802723.72</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>80859</t>
+          <t>-433357</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-6896.969365759996</t>
+          <t>-5871.97675126217</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>6816.488052714849</t>
+          <t>-234.5173715241253</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1661534.0</t>
+          <t>1628749.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-8.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-3.32</v>
+        <v>-7.07</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.33</v>
+        <v>0.35</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.57</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>84.82000000000001</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>82.08</v>
+        <v>82.58</v>
       </c>
       <c r="BA2" t="n">
-        <v>71.81</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>69.25</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-14.91</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>5554.0</t>
+          <t>5468.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>5928.8</v>
+        <v>4983.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6384.9</t>
+          <t>6494.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>3776.84</v>
+        <v>3827.3</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-456</t>
+          <t>-1510</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>481.9857568994096</t>
+          <t>381.4406969931863</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-120.2936986811383</t>
+          <t>-171.5571324910416</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>5554.0</t>
+          <t>5468.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,149 +1450,149 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-6.49</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-3.26</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-2.96</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-30.00</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/02/18</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-30.00</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/05/21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/02/18</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>2025/11/11</t>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1646,51 +1646,51 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.47</v>
+        <v>-3.32</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.43</v>
+        <v>3.33</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>84.82000000000001</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>81.34</v>
+        <v>82.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>71.43000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-14.91</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>4.61</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>4506.0</t>
+          <t>5554.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7801</v>
+        <v>5928.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6525.1</t>
+          <t>6384.9</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>3698.72</v>
+        <v>3776.84</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>-456</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>591.4911124595092</t>
+          <t>481.9857568994096</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-51.97830399980649</t>
+          <t>-120.2936986811383</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>4506.0</t>
+          <t>5554.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1947,27 +1947,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,51 +2133,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.79</v>
+        <v>-1.47</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.04</v>
+        <v>5.43</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>86.03999999999999</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>80.38</v>
+        <v>81.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>71.01000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>4.95</v>
+        <v>4.61</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>7980</v>
+        <v>7801</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>7453.9</t>
+          <t>6525.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>3650.3</v>
+        <v>3698.72</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>708.4855518157484</t>
+          <t>591.4911124595092</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>159.757199259232</t>
+          <t>-51.97830399980649</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2357,22 +2357,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.05</v>
+        <v>-1.79</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.69</v>
+        <v>7.04</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>86.34</t>
+          <t>86.03999999999999</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>79.44</v>
+        <v>80.38</v>
       </c>
       <c r="BA5" t="n">
-        <v>70.59</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5.31</v>
+        <v>4.95</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>8035.4</v>
+        <v>7980</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>8400.7</t>
+          <t>7453.9</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>3611.88</v>
+        <v>3650.3</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-365</t>
+          <t>526</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>808.2543431896604</t>
+          <t>708.4855518157484</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>628.1737325128852</t>
+          <t>159.757199259232</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>55.98</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.42</v>
+        <v>-0.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.26</v>
+        <v>8.69</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>86.34</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>78.40000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="BA6" t="n">
-        <v>70.14</v>
+        <v>70.59</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>68.36</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>5.51</v>
+        <v>5.31</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.08</v>
+        <v>5.13</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>8004.6</v>
+        <v>8035.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>8556.1</t>
+          <t>8400.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>3524.06</v>
+        <v>3611.88</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-551</t>
+          <t>-365</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>840.9962724036195</t>
+          <t>808.2543431896604</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>891.1197181426451</t>
+          <t>628.1737325128852</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3331,27 +3331,27 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-12.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.34</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>78.17</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.82</v>
+        <v>10.26</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>77.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>69.67</v>
+        <v>70.14</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>5.63</v>
+        <v>5.51</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.98</v>
+        <v>5.08</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>6841</v>
+        <v>8004.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8276.3</t>
+          <t>8556.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>3337.94</v>
+        <v>3524.06</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1435</t>
+          <t>-551</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>831.8829186328876</t>
+          <t>840.9962724036195</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>837.645421965779</t>
+          <t>891.1197181426451</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-12.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-17.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>81.36</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>78.17</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.99</v>
+        <v>0.18</v>
       </c>
       <c r="AV8" t="n">
-        <v>13.55</v>
+        <v>11.82</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>86.75999999999999</t>
+          <t>86.54</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>76.41</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>69.20999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>5.71</v>
+        <v>5.63</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.81</v>
+        <v>4.98</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>5249.2</v>
+        <v>6841</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8018.2</t>
+          <t>8276.3</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>3057.46</v>
+        <v>3337.94</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2769</t>
+          <t>-1435</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>830.8351907541801</t>
+          <t>831.8829186328876</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>225.5162337857628</t>
+          <t>837.645421965779</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4305,17 +4305,17 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.56</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>77.22</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>81.88</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.32</v>
+        <v>13.55</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>87.02000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>75.45999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="BA9" t="n">
-        <v>68.78</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>67.49</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>5.81</v>
+        <v>5.71</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.59</v>
+        <v>4.81</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>6927.8</v>
+        <v>5249.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8832.4</t>
+          <t>8018.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2979.9</v>
+        <v>3057.46</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1904</t>
+          <t>-2769</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>940.893182930256</t>
+          <t>830.8351907541801</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>362.3489566076769</t>
+          <t>225.5162337857628</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>3181.0</t>
+          <t>5401.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4792,27 +4792,27 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-11.69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>92.48</t>
+          <t>77.22</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>96.45</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.49</v>
+        <v>15.32</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.02000000000001</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>74.51000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="BA10" t="n">
-        <v>68.31999999999999</v>
+        <v>68.78</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>67.21</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>5.84</v>
+        <v>5.81</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-16.41</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4554.411885245901</t>
+          <t>4561.871165644172</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>8766</v>
+        <v>6927.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>9092.1</t>
+          <t>8832.4</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2936.24</v>
+        <v>2979.9</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-326</t>
+          <t>-1904</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1046.083042261634</t>
+          <t>940.893182930256</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>782.7403836172798</t>
+          <t>362.3489566076769</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6332.0</t>
+          <t>3181.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>79.45</t>
+          <t>77.92</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1617.533</t>
+          <t>2804.117</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>47.99</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-15.14</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>79.55</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.59</v>
+        <v>1.48</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.11999999999999</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>88.76000000000001</v>
+        <v>88.81</v>
       </c>
       <c r="BA11" t="n">
-        <v>89.86</v>
+        <v>89.78</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>95.58</t>
+          <t>95.24</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>97.01</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-108.02</t>
+          <t>-106.46</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>146438373.0</t>
+          <t>257587665.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>164307718.2</v>
+        <v>203686120.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>123012191.7</t>
+          <t>137634898.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>140765943.3</v>
+        <v>135161086.88</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>41295526</t>
+          <t>66051221</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>2632561.438157572</t>
+          <t>4970038.714063331</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>10080853.61081447</t>
+          <t>17826163.731545</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>146438373.0</t>
+          <t>257587665.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>91.9</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1438.883</t>
+          <t>1617.533</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>7.82</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>61.36</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>74.24</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.77</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.01</v>
+        <v>0.59</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>88.61999999999999</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>88.61</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>90.06999999999999</v>
+        <v>89.86</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>95.91</t>
+          <t>95.58</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.68</v>
+        <v>-0.58</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-109.39</t>
+          <t>-108.02</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>128131031.0</t>
+          <t>146438373.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>146132156.6</v>
+        <v>164307718.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>120884303.1</t>
+          <t>123012191.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>140636943.88</v>
+        <v>140765943.3</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>25247853</t>
+          <t>41295526</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1278326.497674501</t>
+          <t>2632561.438157572</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>10564947.0950989</t>
+          <t>10080853.61081447</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>128131031.0</t>
+          <t>146438373.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>91.9</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2267.169</t>
+          <t>1438.883</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>53.79</t>
+          <t>74.24</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>88.61999999999999</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>88.47</v>
+        <v>88.61</v>
       </c>
       <c r="BA13" t="n">
-        <v>90.28</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>96.22</t>
+          <t>95.91</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.44</v>
+        <v>-0.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.76</v>
+        <v>-0.68</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-109.39</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>203737902.0</t>
+          <t>128131031.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>128239336.4</v>
+        <v>146132156.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>119757332.6</t>
+          <t>120884303.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>140693214.84</v>
+        <v>140636943.88</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>8482003</t>
+          <t>25247853</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-410149.9745844807</t>
+          <t>1278326.497674501</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>12840690.60496596</t>
+          <t>10564947.0950989</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>203737902.0</t>
+          <t>128131031.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,17 +6745,17 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3130.894</t>
+          <t>2267.169</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>61.36</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.49</v>
+        <v>-0.15</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>88.34999999999999</v>
+        <v>88.47</v>
       </c>
       <c r="BA14" t="n">
-        <v>90.5</v>
+        <v>90.28</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.22</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.55</v>
+        <v>-0.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.84</v>
+        <v>-0.76</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-111.70</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>282535630.0</t>
+          <t>203737902.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>104061466.2</v>
+        <v>128239336.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>108134512.2</t>
+          <t>119757332.6</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>140300951.66</v>
+        <v>140693214.84</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4073046</t>
+          <t>8482003</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2819393.716320924</t>
+          <t>-410149.9745844807</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>7532420.490313008</t>
+          <t>12840690.60496596</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>282535630.0</t>
+          <t>203737902.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>700.544</t>
+          <t>3130.894</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.11</v>
+        <v>-0.49</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>88.18000000000001</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>90.73</v>
+        <v>90.5</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>96.64</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>34.07</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.87</v>
+        <v>-0.55</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-112.70</t>
+          <t>-111.70</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>60695655.0</t>
+          <t>282535630.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>71583677.59999999</v>
+        <v>104061466.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>86365033.2</t>
+          <t>108134512.2</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>142652545.32</v>
+        <v>140300951.66</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-14781355</t>
+          <t>-4073046</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-4701541.75389073</t>
+          <t>-2819393.716320924</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-8762451.262416676</t>
+          <t>7532420.490313008</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>60695655.0</t>
+          <t>282535630.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>640.814</t>
+          <t>700.544</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.13</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,12 +7962,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7981,47 +7981,47 @@
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.78</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.7</v>
+        <v>-1.11</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>88.2</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>91.02</v>
+        <v>90.73</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.64</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-112.84</t>
+          <t>-112.70</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>55560565.0</t>
+          <t>60695655.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>81716665.2</v>
+        <v>71583677.59999999</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>94062838.4</t>
+          <t>86365033.2</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>144519824.5</v>
+        <v>142652545.32</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-12346173</t>
+          <t>-14781355</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-3963194.570522375</t>
+          <t>-4701541.75389073</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-7959326.042658493</t>
+          <t>-8762451.262416676</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>55560565.0</t>
+          <t>60695655.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>441.13</t>
+          <t>640.814</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-13.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,17 +8449,17 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
@@ -8468,47 +8468,47 @@
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.2</v>
+        <v>-0.78</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.15</v>
+        <v>-0.7</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>88.08000000000001</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>88.20999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>91.27</v>
+        <v>91.02</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.77</v>
+        <v>-0.82</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-113.21</t>
+          <t>-112.84</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>38666930.0</t>
+          <t>55560565.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>95636449.59999999</v>
+        <v>81716665.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>94187240.9</t>
+          <t>94062838.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>145660623.92</v>
+        <v>144519824.5</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>1449208</t>
+          <t>-12346173</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-3236625.211952172</t>
+          <t>-3963194.570522375</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-5977554.441480413</t>
+          <t>-7959326.042658493</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>38666930.0</t>
+          <t>55560565.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8730,7 +8730,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>951.833</t>
+          <t>441.13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.45</v>
+        <v>-0.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>88.08000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>88.2</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>91.52</v>
+        <v>91.27</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.79</v>
+        <v>-0.77</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1</v>
+        <v>-0.95</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-113.85</t>
+          <t>-113.21</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>111275328.8</v>
+        <v>95636449.59999999</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>100026664.5</t>
+          <t>94187240.9</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>147996956.16</v>
+        <v>145660623.92</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>11248664</t>
+          <t>1449208</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2738274.442947037</t>
+          <t>-3236625.211952172</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-1122935.745458856</t>
+          <t>-5977554.441480413</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>82848551.0</t>
+          <t>38666930.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1363.614</t>
+          <t>951.833</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,51 +9438,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.38</v>
+        <v>-1.45</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AZ19" t="n">
         <v>88.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>91.77</v>
+        <v>91.52</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>97.41</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.74</v>
+        <v>-0.79</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.05</v>
+        <v>-1</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-114.56</t>
+          <t>-113.85</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>437655919.164959</t>
+          <t>437551063.4969325</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>112207558.2</v>
+        <v>111275328.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>105140473.3</t>
+          <t>100026664.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>151128209.54</v>
+        <v>147996956.16</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>7067084</t>
+          <t>11248664</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-3031972.387944888</t>
+          <t>-2738274.442947037</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>1118593.561195478</t>
+          <t>-1122935.745458856</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>120146687.0</t>
+          <t>82848551.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
           <t>87.2</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>87.4</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>154.401</t>
+          <t>127.68</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-20.72</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-15.54</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,63 +9910,63 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="BA20" t="n">
-        <v>14.67</v>
+        <v>14.64</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>110.40</t>
+          <t>68.51</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BE20" t="n">
         <v>-0.03</v>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-101.65</t>
+          <t>-101.41</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2252696.0</t>
+          <t>1846714.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2072915</v>
+        <v>2151033</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>2614820.8</t>
+          <t>2633338.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2020646.96</v>
+        <v>1997531.62</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-541905</t>
+          <t>-482305</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>109889.0323171251</t>
+          <t>97805.43200505097</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>82818.89576326637</t>
+          <t>31345.6302886433</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2252696.0</t>
+          <t>1846714.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>219.266</t>
+          <t>154.401</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-12.94</t>
+          <t>-20.72</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.25</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>14.44</v>
+        <v>14.45</v>
       </c>
       <c r="BA21" t="n">
-        <v>14.69</v>
+        <v>14.67</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>94.48</t>
+          <t>110.40</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-102.11</t>
+          <t>-101.65</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>3160120.0</t>
+          <t>2252696.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2175872.6</v>
+        <v>2072915</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2499323.8</t>
+          <t>2614820.8</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2012189.46</v>
+        <v>2020646.96</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-323451</t>
+          <t>-541905</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>114810.8753269176</t>
+          <t>109889.0323171251</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>109896.2430211832</t>
+          <t>82818.89576326637</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>3160120.0</t>
+          <t>2252696.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
           <t>14.5</t>
         </is>
       </c>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>141.743</t>
+          <t>219.266</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-12.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.25</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>71.67</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-1.29</v>
+        <v>-1.3</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>14.42</v>
+        <v>14.44</v>
       </c>
       <c r="BA22" t="n">
-        <v>14.71</v>
+        <v>14.69</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>112.33</t>
+          <t>94.48</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-102.61</t>
+          <t>-102.11</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>2051916.0</t>
+          <t>3160120.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2219282</v>
+        <v>2175872.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2370449.7</t>
+          <t>2499323.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>1963397.92</v>
+        <v>2012189.46</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-151167</t>
+          <t>-323451</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>115704.4448370511</t>
+          <t>114810.8753269176</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>47429.30185316503</t>
+          <t>109896.2430211832</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>2051916.0</t>
+          <t>3160120.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>97.727</t>
+          <t>141.743</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>71.67</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.14</v>
+        <v>-1.29</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>14.44</v>
+        <v>14.42</v>
       </c>
       <c r="BA23" t="n">
-        <v>14.73</v>
+        <v>14.71</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>118.20</t>
+          <t>112.33</t>
         </is>
       </c>
       <c r="BD23" t="n">
         <v>0.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-103.34</t>
+          <t>-102.61</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1443719.0</t>
+          <t>2051916.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3078638.6</v>
+        <v>2219282</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2239067.8</t>
+          <t>2370449.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>1944320.84</v>
+        <v>1963397.92</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>839570</t>
+          <t>-151167</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>128118.1071977577</t>
+          <t>115704.4448370511</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>75233.05368981184</t>
+          <t>47429.30185316503</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1443719.0</t>
+          <t>2051916.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>98.471</t>
+          <t>97.727</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
+          <t>83.33</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
           <t>91.67</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
-        <is>
-          <t>97.22</t>
-        </is>
-      </c>
       <c r="AU24" t="n">
-        <v>0.75</v>
+        <v>-0.14</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>14.43</v>
+        <v>14.44</v>
       </c>
       <c r="BA24" t="n">
-        <v>14.74</v>
+        <v>14.73</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>97.50</t>
+          <t>118.20</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-104.33</t>
+          <t>-103.34</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>1456124.0</t>
+          <t>1443719.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>3115644.6</v>
+        <v>3078638.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>2498493.2</t>
+          <t>2239067.8</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>1944927.72</v>
+        <v>1944320.84</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>617151</t>
+          <t>839570</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>137733.5714719296</t>
+          <t>128118.1071977577</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>177429.7686818144</t>
+          <t>75233.05368981184</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>1456124.0</t>
+          <t>1443719.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>189.182</t>
+          <t>98.471</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-13.20</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.72</v>
+        <v>0.75</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>14.42</v>
+        <v>14.43</v>
       </c>
       <c r="BA25" t="n">
-        <v>14.76</v>
+        <v>14.74</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>76.06</t>
+          <t>97.50</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-105.38</t>
+          <t>-104.33</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>2767484.0</t>
+          <t>1456124.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>3156726.6</v>
+        <v>3115644.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>2642563.3</t>
+          <t>2498493.2</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>1946447.4</v>
+        <v>1944927.72</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>514163</t>
+          <t>617151</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>130516.0810701324</t>
+          <t>137733.5714719296</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>315759.1912174677</t>
+          <t>177429.7686818144</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>2767484.0</t>
+          <t>1456124.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>227.292</t>
+          <t>189.182</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-13.78</t>
+          <t>-13.20</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.35</v>
+        <v>0.87</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="AZ26" t="n">
         <v>14.42</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>76.06</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-106.41</t>
+          <t>-105.38</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>3377167.0</t>
+          <t>2767484.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2822775</v>
+        <v>3156726.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>2509841.5</t>
+          <t>2642563.3</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>1920541.68</v>
+        <v>1946447.4</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>514163</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>96835.51558879873</t>
+          <t>130516.0810701324</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>361592.6808677763</t>
+          <t>315759.1912174677</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>3377167.0</t>
+          <t>2767484.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,22 +13011,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>431.346</t>
+          <t>227.292</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-14.08</t>
+          <t>-13.78</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,35 +13334,35 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.21</v>
+        <v>0.35</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>14.4</v>
+        <v>14.42</v>
       </c>
       <c r="BA27" t="n">
-        <v>14.8</v>
+        <v>14.78</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
@@ -13371,14 +13371,14 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-107.25</t>
+          <t>-106.41</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2521617.4</v>
+        <v>2822775</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>2376458.4</t>
+          <t>2509841.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>1900953.72</v>
+        <v>1920541.68</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>145159</t>
+          <t>312933</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>48697.84917443918</t>
+          <t>96835.51558879873</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>348831.8917657966</t>
+          <t>361592.6808677763</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>6348699.0</t>
+          <t>3377167.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,42 +13610,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>431.346</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14.65</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>113.748</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-16.13</t>
+          <t>-14.08</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,17 +13806,17 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
@@ -13825,47 +13825,47 @@
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.57</v>
+        <v>-0.21</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>14.38</v>
+        <v>14.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.81</v>
+        <v>14.8</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>14.99</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-107.88</t>
+          <t>-107.25</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>37310523.43954918</t>
+          <t>37239888.56748466</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>1399497</v>
+        <v>2521617.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>1832854.3</t>
+          <t>2376458.4</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>1802723.72</v>
+        <v>1900953.72</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-433357</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-5871.97675126217</t>
+          <t>48697.84917443918</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-234.5173715241253</t>
+          <t>348831.8917657966</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1628749.0</t>
+          <t>6348699.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/金屬材料.xlsx
+++ b/Result/checksun_type/金屬材料.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.95</t>
+          <t>-24.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,61 +1149,61 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-3.64</v>
+        <v>-1.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>-2.1</v>
+        <v>-3.86</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>81.26</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>83</v>
+        <v>83.36</v>
       </c>
       <c r="BA2" t="n">
-        <v>72.34</v>
+        <v>72.62</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>69.39</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-35.88</t>
+          <t>-41.32</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.13</v>
+        <v>3.75</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-26.94</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>2753.0</t>
+          <t>5720.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>4237</v>
+        <v>4800.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>6136.2</t>
+          <t>6390.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>3838.98</v>
+        <v>3931.82</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1899</t>
+          <t>-1589</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>260.1763424025888</t>
+          <t>168.0357512025268</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-406.7776078456973</t>
+          <t>-338.7375003978141</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2753.0</t>
+          <t>5720.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.88</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-7.07</v>
+        <v>-3.64</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.35</v>
+        <v>-2.1</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>81.26</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>82.58</v>
+        <v>83</v>
       </c>
       <c r="BA3" t="n">
-        <v>72.06999999999999</v>
+        <v>72.34</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>69.25</t>
+          <t>69.39</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-27.86</t>
+          <t>-35.88</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>4.13</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>5468.0</t>
+          <t>2753.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>4983.6</v>
+        <v>4237</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6494.1</t>
+          <t>6136.2</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>3827.3</v>
+        <v>3838.98</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1510</t>
+          <t>-1899</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>381.4406969931863</t>
+          <t>260.1763424025888</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-171.5571324910416</t>
+          <t>-406.7776078456973</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>5468.0</t>
+          <t>2753.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>16.87</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-8.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,47 +2137,47 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-3.32</v>
+        <v>-7.07</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.33</v>
+        <v>0.35</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.57</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>84.82000000000001</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>82.08</v>
+        <v>82.58</v>
       </c>
       <c r="BA4" t="n">
-        <v>71.81</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>69.25</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-14.91</t>
+          <t>-27.86</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>5554.0</t>
+          <t>5468.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>5928.8</v>
+        <v>4983.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6384.9</t>
+          <t>6494.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>3776.84</v>
+        <v>3827.3</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-456</t>
+          <t>-1510</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>481.9857568994096</t>
+          <t>381.4406969931863</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-120.2936986811383</t>
+          <t>-171.5571324910416</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>5554.0</t>
+          <t>5468.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,149 +2424,149 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-3.93</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>67.2</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-7.92</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>67.2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-2.96</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-30.00</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/02/18</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-30.00</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/05/21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/06/17</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/02/18</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>91.2</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>2025/11/11</t>
@@ -2579,22 +2579,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,51 +2620,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.47</v>
+        <v>-3.32</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.43</v>
+        <v>3.33</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>84.82000000000001</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>81.34</v>
+        <v>82.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>71.43000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-14.91</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>4.61</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>4506.0</t>
+          <t>5554.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>7801</v>
+        <v>5928.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6525.1</t>
+          <t>6384.9</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>3698.72</v>
+        <v>3776.84</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>-456</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>591.4911124595092</t>
+          <t>481.9857568994096</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-51.97830399980649</t>
+          <t>-120.2936986811383</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>4506.0</t>
+          <t>5554.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.79</v>
+        <v>-1.47</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.04</v>
+        <v>5.43</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>13.87</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>86.03999999999999</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>80.38</v>
+        <v>81.34</v>
       </c>
       <c r="BA6" t="n">
-        <v>71.01000000000001</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>4.95</v>
+        <v>4.61</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>7980</v>
+        <v>7801</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>7453.9</t>
+          <t>6525.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>3650.3</v>
+        <v>3698.72</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>708.4855518157484</t>
+          <t>591.4911124595092</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>159.757199259232</t>
+          <t>-51.97830399980649</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>2904.0</t>
+          <t>4506.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-10.22</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>25.74</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>28.86</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.05</v>
+        <v>-1.79</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.69</v>
+        <v>7.04</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>86.34</t>
+          <t>86.03999999999999</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>79.44</v>
+        <v>80.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>70.59</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>68.62</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>5.31</v>
+        <v>4.95</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>8035.4</v>
+        <v>7980</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>8400.7</t>
+          <t>7453.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>3611.88</v>
+        <v>3650.3</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-365</t>
+          <t>526</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>808.2543431896604</t>
+          <t>708.4855518157484</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>628.1737325128852</t>
+          <t>159.757199259232</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>6486.0</t>
+          <t>2904.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>55.98</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.42</v>
+        <v>-0.05</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.26</v>
+        <v>8.69</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>86.44</t>
+          <t>86.34</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>78.40000000000001</v>
+        <v>79.44</v>
       </c>
       <c r="BA8" t="n">
-        <v>70.14</v>
+        <v>70.59</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>68.36</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>5.51</v>
+        <v>5.31</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.08</v>
+        <v>5.13</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>8004.6</v>
+        <v>8035.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>8556.1</t>
+          <t>8400.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>3524.06</v>
+        <v>3611.88</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-551</t>
+          <t>-365</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>840.9962724036195</t>
+          <t>808.2543431896604</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>891.1197181426451</t>
+          <t>628.1737325128852</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>10194.0</t>
+          <t>6486.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.34</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>31.81</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,61 +4558,61 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>65.52</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>78.17</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="AV9" t="n">
-        <v>11.82</v>
+        <v>10.26</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>77.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>69.67</v>
+        <v>70.14</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>5.63</v>
+        <v>5.51</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.98</v>
+        <v>5.08</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>6841</v>
+        <v>8004.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8276.3</t>
+          <t>8556.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>3337.94</v>
+        <v>3524.06</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-1435</t>
+          <t>-551</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>831.8829186328876</t>
+          <t>840.9962724036195</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>837.645421965779</t>
+          <t>891.1197181426451</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>14915.0</t>
+          <t>10194.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>29.40</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>81.18</t>
+          <t>81.86</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.71</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-17.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>31.81</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>81.36</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>78.17</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.99</v>
+        <v>0.18</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.55</v>
+        <v>11.82</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>86.75999999999999</t>
+          <t>86.54</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>76.41</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>69.20999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>67.49</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>5.71</v>
+        <v>5.63</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.81</v>
+        <v>4.98</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4560.988775510204</t>
+          <t>4569.174134419552</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>5249.2</v>
+        <v>6841</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8018.2</t>
+          <t>8276.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>3057.46</v>
+        <v>3337.94</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2769</t>
+          <t>-1435</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>830.8351907541801</t>
+          <t>831.8829186328876</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>225.5162337857628</t>
+          <t>837.645421965779</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5401.0</t>
+          <t>14915.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.53</t>